--- a/dashboard-output/PCS Archive Dashboard.xlsx
+++ b/dashboard-output/PCS Archive Dashboard.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0970949c4a8d45d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" r:id="Rb63127144f7c49d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Orders" sheetId="3" r:id="R3edcca488a664934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" r:id="R64e2b378a0ed4eab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" r:id="Ra2fb01f6a8b44010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R707b56d52b43496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" r:id="Rc5876a521c114536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Orders" sheetId="3" r:id="R706f1af73df847b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" r:id="R5dd4ba4613dd4e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" r:id="R4664ce9a3bc44d17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -323,7 +323,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard'!$A$18:$A$33</c:f>
+              <c:f>'Dashboard'!$A$18:$A$105</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -331,7 +331,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard'!$B$18:$B$33</c:f>
+              <c:f>'Dashboard'!$B$18:$B$105</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -430,7 +430,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc625408b2a1f4680"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd27bbdc4c751483e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -646,7 +646,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>PCS Archive Dashboard</x:v>
+        <x:v>PCS ARCHIVE — v1.0</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -683,7 +683,7 @@
         <x:v>Archived orders</x:v>
       </x:c>
       <x:c r="B5" s="20" t="n">
-        <x:v>32832</x:v>
+        <x:v>226862</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>Open issues</x:v>
@@ -708,7 +708,7 @@
         <x:v>Customer snapshot</x:v>
       </x:c>
       <x:c r="B7" s="20" t="n">
-        <x:v>97140</x:v>
+        <x:v>97209</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
         <x:v>Product snapshot</x:v>
@@ -915,99 +915,675 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>2026-01</x:v>
+        <x:v>2014-01</x:v>
       </x:c>
       <x:c r="B26" t="n">
-        <x:v>1984</x:v>
+        <x:v>3917</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
-        <x:v>2026-02</x:v>
+        <x:v>2014-02</x:v>
       </x:c>
       <x:c r="B27" t="n">
-        <x:v>1419</x:v>
+        <x:v>2821</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
-        <x:v>2026-03</x:v>
+        <x:v>2014-03</x:v>
       </x:c>
       <x:c r="B28" t="n">
-        <x:v>1560</x:v>
+        <x:v>4413</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
-        <x:v>2026-04</x:v>
+        <x:v>2014-04</x:v>
       </x:c>
       <x:c r="B29" t="n">
-        <x:v>1339</x:v>
+        <x:v>4044</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
-        <x:v>2026-05</x:v>
+        <x:v>2014-05</x:v>
       </x:c>
       <x:c r="B30" t="n">
-        <x:v>1744</x:v>
+        <x:v>2984</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
-        <x:v>2026-06</x:v>
+        <x:v>2014-06</x:v>
       </x:c>
       <x:c r="B31" t="n">
-        <x:v>1530</x:v>
+        <x:v>4024</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
-        <x:v>2026-07</x:v>
+        <x:v>2014-07</x:v>
       </x:c>
       <x:c r="B32" t="n">
-        <x:v>1983</x:v>
+        <x:v>4883</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
+        <x:v>2014-08</x:v>
+      </x:c>
+      <x:c r="B33" t="n">
+        <x:v>4973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>3170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>2014-10</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>2110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>2014-11</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>3223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>2014-12</x:v>
+      </x:c>
+      <x:c r="B37" t="n">
+        <x:v>3231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>2015-01</x:v>
+      </x:c>
+      <x:c r="B38" t="n">
+        <x:v>3966</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>2015-02</x:v>
+      </x:c>
+      <x:c r="B39" t="n">
+        <x:v>3282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>2015-03</x:v>
+      </x:c>
+      <x:c r="B40" t="n">
+        <x:v>3154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>2015-04</x:v>
+      </x:c>
+      <x:c r="B41" t="n">
+        <x:v>3434</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>2015-05</x:v>
+      </x:c>
+      <x:c r="B42" t="n">
+        <x:v>2723</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>2015-06</x:v>
+      </x:c>
+      <x:c r="B43" t="n">
+        <x:v>3172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>2015-07</x:v>
+      </x:c>
+      <x:c r="B44" t="n">
+        <x:v>3769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>2015-08</x:v>
+      </x:c>
+      <x:c r="B45" t="n">
+        <x:v>3755</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="B46" t="n">
+        <x:v>2544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>2015-10</x:v>
+      </x:c>
+      <x:c r="B47" t="n">
+        <x:v>2291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>2015-11</x:v>
+      </x:c>
+      <x:c r="B48" t="n">
+        <x:v>3270</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>2015-12</x:v>
+      </x:c>
+      <x:c r="B49" t="n">
+        <x:v>3440</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>2016-01</x:v>
+      </x:c>
+      <x:c r="B50" t="n">
+        <x:v>3345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>2016-02</x:v>
+      </x:c>
+      <x:c r="B51" t="n">
+        <x:v>2591</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>2016-03</x:v>
+      </x:c>
+      <x:c r="B52" t="n">
+        <x:v>3347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>2016-04</x:v>
+      </x:c>
+      <x:c r="B53" t="n">
+        <x:v>3182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>2016-05</x:v>
+      </x:c>
+      <x:c r="B54" t="n">
+        <x:v>2612</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>2016-06</x:v>
+      </x:c>
+      <x:c r="B55" t="n">
+        <x:v>3019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>2016-07</x:v>
+      </x:c>
+      <x:c r="B56" t="n">
+        <x:v>3726</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>2016-08</x:v>
+      </x:c>
+      <x:c r="B57" t="n">
+        <x:v>2997</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>2016-09</x:v>
+      </x:c>
+      <x:c r="B58" t="n">
+        <x:v>2264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>2016-10</x:v>
+      </x:c>
+      <x:c r="B59" t="n">
+        <x:v>2462</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>2016-11</x:v>
+      </x:c>
+      <x:c r="B60" t="n">
+        <x:v>2543</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>2016-12</x:v>
+      </x:c>
+      <x:c r="B61" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>2017-01</x:v>
+      </x:c>
+      <x:c r="B62" t="n">
+        <x:v>2986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>2017-02</x:v>
+      </x:c>
+      <x:c r="B63" t="n">
+        <x:v>2268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>2017-03</x:v>
+      </x:c>
+      <x:c r="B64" t="n">
+        <x:v>2523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>2017-04</x:v>
+      </x:c>
+      <x:c r="B65" t="n">
+        <x:v>2759</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>2017-05</x:v>
+      </x:c>
+      <x:c r="B66" t="n">
+        <x:v>1905</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>2017-06</x:v>
+      </x:c>
+      <x:c r="B67" t="n">
+        <x:v>2773</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>2017-07</x:v>
+      </x:c>
+      <x:c r="B68" t="n">
+        <x:v>2674</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>2017-08</x:v>
+      </x:c>
+      <x:c r="B69" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>2017-09</x:v>
+      </x:c>
+      <x:c r="B70" t="n">
+        <x:v>2114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>2017-10</x:v>
+      </x:c>
+      <x:c r="B71" t="n">
+        <x:v>1857</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>2017-11</x:v>
+      </x:c>
+      <x:c r="B72" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>2017-12</x:v>
+      </x:c>
+      <x:c r="B73" t="n">
+        <x:v>2709</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>2018-01</x:v>
+      </x:c>
+      <x:c r="B74" t="n">
+        <x:v>2768</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>2018-02</x:v>
+      </x:c>
+      <x:c r="B75" t="n">
+        <x:v>2316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>2018-03</x:v>
+      </x:c>
+      <x:c r="B76" t="n">
+        <x:v>3055</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>2018-04</x:v>
+      </x:c>
+      <x:c r="B77" t="n">
+        <x:v>2516</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>2018-05</x:v>
+      </x:c>
+      <x:c r="B78" t="n">
+        <x:v>2128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>2018-06</x:v>
+      </x:c>
+      <x:c r="B79" t="n">
+        <x:v>2889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>2018-07</x:v>
+      </x:c>
+      <x:c r="B80" t="n">
+        <x:v>2961</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>2018-08</x:v>
+      </x:c>
+      <x:c r="B81" t="n">
+        <x:v>2446</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>2018-09</x:v>
+      </x:c>
+      <x:c r="B82" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>2018-10</x:v>
+      </x:c>
+      <x:c r="B83" t="n">
+        <x:v>1667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>2018-11</x:v>
+      </x:c>
+      <x:c r="B84" t="n">
+        <x:v>2128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>2018-12</x:v>
+      </x:c>
+      <x:c r="B85" t="n">
+        <x:v>2128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>2025-01</x:v>
+      </x:c>
+      <x:c r="B86" t="n">
+        <x:v>1390</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>2025-02</x:v>
+      </x:c>
+      <x:c r="B87" t="n">
+        <x:v>1340</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="B88" t="n">
+        <x:v>1746</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>2025-04</x:v>
+      </x:c>
+      <x:c r="B89" t="n">
+        <x:v>1261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>2025-05</x:v>
+      </x:c>
+      <x:c r="B90" t="n">
+        <x:v>1328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>2025-06</x:v>
+      </x:c>
+      <x:c r="B91" t="n">
+        <x:v>1555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
+      <x:c r="B92" t="n">
+        <x:v>1534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>2025-08</x:v>
+      </x:c>
+      <x:c r="B93" t="n">
+        <x:v>1756</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>2025-09</x:v>
+      </x:c>
+      <x:c r="B94" t="n">
+        <x:v>1135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>2025-10</x:v>
+      </x:c>
+      <x:c r="B95" t="n">
+        <x:v>1451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>2025-11</x:v>
+      </x:c>
+      <x:c r="B96" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="B97" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="B98" t="n">
+        <x:v>1984</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="B99" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>2026-03</x:v>
+      </x:c>
+      <x:c r="B100" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="B101" t="n">
+        <x:v>1339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="B102" t="n">
+        <x:v>1744</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="B103" t="n">
+        <x:v>1530</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B104" t="n">
+        <x:v>1983</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="B33" t="n">
+      <x:c r="B105" t="n">
         <x:v>1515</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="31" t="str">
+    <x:row r="107">
+      <x:c r="A107" s="31" t="str">
         <x:v>Important: Order value and payments shown in this workbook come from order snapshots. They are not yet a reproduction of PCS cash-accounting reports, which require payment/refund transaction dates and allocation logic.</x:v>
       </x:c>
-      <x:c r="B34" s="31"/>
-      <x:c r="C34" s="31"/>
-      <x:c r="D34" s="31"/>
-      <x:c r="E34" s="31"/>
-      <x:c r="F34" s="31"/>
-      <x:c r="G34" s="31"/>
-      <x:c r="H34" s="31"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="31"/>
-      <x:c r="B35" s="31"/>
-      <x:c r="C35" s="31"/>
-      <x:c r="D35" s="31"/>
-      <x:c r="E35" s="31"/>
-      <x:c r="F35" s="31"/>
-      <x:c r="G35" s="31"/>
-      <x:c r="H35" s="31"/>
+      <x:c r="B107" s="31"/>
+      <x:c r="C107" s="31"/>
+      <x:c r="D107" s="31"/>
+      <x:c r="E107" s="31"/>
+      <x:c r="F107" s="31"/>
+      <x:c r="G107" s="31"/>
+      <x:c r="H107" s="31"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="31"/>
+      <x:c r="B108" s="31"/>
+      <x:c r="C108" s="31"/>
+      <x:c r="D108" s="31"/>
+      <x:c r="E108" s="31"/>
+      <x:c r="F108" s="31"/>
+      <x:c r="G108" s="31"/>
+      <x:c r="H108" s="31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H3"/>
     <x:mergeCell ref="D10:H10"/>
-    <x:mergeCell ref="A34:H35"/>
+    <x:mergeCell ref="A107:H108"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R415e64fb2c594e60"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28e709599e884234"/>
 </x:worksheet>
 </file>
 
@@ -1074,16 +1650,22 @@
         <x:v>2014</x:v>
       </x:c>
       <x:c r="B3" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C3" s="26" t="str"/>
-      <x:c r="D3" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C3" s="26" t="str">
+        <x:v>2014-01-01</x:v>
+      </x:c>
+      <x:c r="D3" s="26" t="str">
+        <x:v>2014-12-31</x:v>
+      </x:c>
       <x:c r="E3" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F3" s="26" t="str"/>
+        <x:v>43793</x:v>
+      </x:c>
+      <x:c r="F3" s="26" t="str">
+        <x:v>year-2014-through-2014-12-31</x:v>
+      </x:c>
       <x:c r="G3" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1091,16 +1673,22 @@
         <x:v>2015</x:v>
       </x:c>
       <x:c r="B4" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C4" s="26" t="str"/>
-      <x:c r="D4" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="str">
+        <x:v>2015-01-01</x:v>
+      </x:c>
+      <x:c r="D4" s="26" t="str">
+        <x:v>2015-12-31</x:v>
+      </x:c>
       <x:c r="E4" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="26" t="str"/>
+        <x:v>38800</x:v>
+      </x:c>
+      <x:c r="F4" s="26" t="str">
+        <x:v>year-2015-through-2015-12-31</x:v>
+      </x:c>
       <x:c r="G4" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1108,16 +1696,22 @@
         <x:v>2016</x:v>
       </x:c>
       <x:c r="B5" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="str"/>
-      <x:c r="D5" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C5" s="26" t="str">
+        <x:v>2016-01-01</x:v>
+      </x:c>
+      <x:c r="D5" s="26" t="str">
+        <x:v>2016-12-31</x:v>
+      </x:c>
       <x:c r="E5" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F5" s="26" t="str"/>
+        <x:v>34948</x:v>
+      </x:c>
+      <x:c r="F5" s="26" t="str">
+        <x:v>year-2016-through-2016-12-31</x:v>
+      </x:c>
       <x:c r="G5" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1125,16 +1719,22 @@
         <x:v>2017</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C6" s="26" t="str"/>
-      <x:c r="D6" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C6" s="26" t="str">
+        <x:v>2017-01-01</x:v>
+      </x:c>
+      <x:c r="D6" s="26" t="str">
+        <x:v>2017-12-31</x:v>
+      </x:c>
       <x:c r="E6" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="26" t="str"/>
+        <x:v>29568</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="str">
+        <x:v>year-2017-through-2017-12-31</x:v>
+      </x:c>
       <x:c r="G6" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1142,16 +1742,22 @@
         <x:v>2018</x:v>
       </x:c>
       <x:c r="B7" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C7" s="26" t="str"/>
-      <x:c r="D7" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C7" s="26" t="str">
+        <x:v>2018-01-01</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>2018-12-31</x:v>
+      </x:c>
       <x:c r="E7" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="26" t="str"/>
+        <x:v>29029</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="str">
+        <x:v>year-2018-through-2018-12-31</x:v>
+      </x:c>
       <x:c r="G7" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1261,16 +1867,22 @@
         <x:v>2025</x:v>
       </x:c>
       <x:c r="B14" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C14" s="26" t="str"/>
-      <x:c r="D14" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C14" s="26" t="str">
+        <x:v>2025-01-01</x:v>
+      </x:c>
+      <x:c r="D14" s="26" t="str">
+        <x:v>2025-12-31</x:v>
+      </x:c>
       <x:c r="E14" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="26" t="str"/>
+        <x:v>17892</x:v>
+      </x:c>
+      <x:c r="F14" s="26" t="str">
+        <x:v>year-2025-through-2025-12-31</x:v>
+      </x:c>
       <x:c r="G14" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1527,185 +2139,1841 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="26" t="str">
-        <x:v>2026-01</x:v>
+        <x:v>2014-01</x:v>
       </x:c>
       <x:c r="B10" s="34" t="n">
-        <x:v>1984</x:v>
+        <x:v>3917</x:v>
       </x:c>
       <x:c r="C10" s="33" t="n">
-        <x:v>149100.38</x:v>
+        <x:v>111322.27</x:v>
       </x:c>
       <x:c r="D10" s="33" t="n">
-        <x:v>102160.48000000013</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="33" t="n">
-        <x:v>54476.700000000055</x:v>
+        <x:v>112768.27</x:v>
       </x:c>
       <x:c r="F10" s="26" t="n">
-        <x:v>188</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G10" s="26" t="n">
-        <x:v>1383</x:v>
+        <x:v>2679</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="26" t="str">
-        <x:v>2026-02</x:v>
+        <x:v>2014-02</x:v>
       </x:c>
       <x:c r="B11" s="34" t="n">
-        <x:v>1419</x:v>
+        <x:v>2821</x:v>
       </x:c>
       <x:c r="C11" s="33" t="n">
-        <x:v>138263.76000000013</x:v>
+        <x:v>96973.52999999998</x:v>
       </x:c>
       <x:c r="D11" s="33" t="n">
-        <x:v>93983.34999999993</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="33" t="n">
-        <x:v>49906.04000000006</x:v>
+        <x:v>98075.52999999998</x:v>
       </x:c>
       <x:c r="F11" s="26" t="n">
-        <x:v>152</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G11" s="26" t="n">
-        <x:v>947</x:v>
+        <x:v>1893</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="26" t="str">
-        <x:v>2026-03</x:v>
+        <x:v>2014-03</x:v>
       </x:c>
       <x:c r="B12" s="34" t="n">
-        <x:v>1560</x:v>
+        <x:v>4413</x:v>
       </x:c>
       <x:c r="C12" s="33" t="n">
-        <x:v>102584.46000000022</x:v>
+        <x:v>133639.5</x:v>
       </x:c>
       <x:c r="D12" s="33" t="n">
-        <x:v>77206.12999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E12" s="33" t="n">
-        <x:v>30805.019999999982</x:v>
+        <x:v>135503.5</x:v>
       </x:c>
       <x:c r="F12" s="26" t="n">
-        <x:v>105</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G12" s="26" t="n">
-        <x:v>1090</x:v>
+        <x:v>3020</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="26" t="str">
-        <x:v>2026-04</x:v>
+        <x:v>2014-04</x:v>
       </x:c>
       <x:c r="B13" s="34" t="n">
-        <x:v>1339</x:v>
+        <x:v>4044</x:v>
       </x:c>
       <x:c r="C13" s="33" t="n">
-        <x:v>122029.22999999988</x:v>
+        <x:v>113733.69999999998</x:v>
       </x:c>
       <x:c r="D13" s="33" t="n">
-        <x:v>77013.54000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E13" s="33" t="n">
-        <x:v>49566.15000000005</x:v>
+        <x:v>114956.69999999998</x:v>
       </x:c>
       <x:c r="F13" s="26" t="n">
-        <x:v>131</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
-        <x:v>883</x:v>
+        <x:v>2635</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="26" t="str">
-        <x:v>2026-05</x:v>
+        <x:v>2014-05</x:v>
       </x:c>
       <x:c r="B14" s="34" t="n">
-        <x:v>1744</x:v>
+        <x:v>2984</x:v>
       </x:c>
       <x:c r="C14" s="33" t="n">
-        <x:v>102583.65999999997</x:v>
+        <x:v>102570.88999999998</x:v>
       </x:c>
       <x:c r="D14" s="33" t="n">
-        <x:v>74749.29999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="33" t="n">
-        <x:v>32273.119999999988</x:v>
+        <x:v>104223.88999999998</x:v>
       </x:c>
       <x:c r="F14" s="26" t="n">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G14" s="26" t="n">
-        <x:v>1319</x:v>
+        <x:v>1816</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="26" t="str">
-        <x:v>2026-06</x:v>
+        <x:v>2014-06</x:v>
       </x:c>
       <x:c r="B15" s="34" t="n">
-        <x:v>1530</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="C15" s="33" t="n">
-        <x:v>103851.23999999993</x:v>
+        <x:v>92212.04999999999</x:v>
       </x:c>
       <x:c r="D15" s="33" t="n">
-        <x:v>70398.12000000004</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="33" t="n">
-        <x:v>37944.56000000002</x:v>
+        <x:v>92877.00999999998</x:v>
       </x:c>
       <x:c r="F15" s="26" t="n">
-        <x:v>101</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G15" s="26" t="n">
-        <x:v>1065</x:v>
+        <x:v>2436</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="26" t="str">
-        <x:v>2026-07</x:v>
+        <x:v>2014-07</x:v>
       </x:c>
       <x:c r="B16" s="34" t="n">
-        <x:v>1983</x:v>
+        <x:v>4883</x:v>
       </x:c>
       <x:c r="C16" s="33" t="n">
-        <x:v>106224.69999999998</x:v>
+        <x:v>115218.16999999984</x:v>
       </x:c>
       <x:c r="D16" s="33" t="n">
-        <x:v>70944.62999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="33" t="n">
-        <x:v>39193.270000000004</x:v>
+        <x:v>116206.16999999981</x:v>
       </x:c>
       <x:c r="F16" s="26" t="n">
-        <x:v>104</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G16" s="26" t="n">
-        <x:v>1395</x:v>
+        <x:v>3130</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="26" t="str">
+        <x:v>2014-08</x:v>
+      </x:c>
+      <x:c r="B17" s="34" t="n">
+        <x:v>4973</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="n">
+        <x:v>108253.54999999996</x:v>
+      </x:c>
+      <x:c r="D17" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="33" t="n">
+        <x:v>109254.14999999995</x:v>
+      </x:c>
+      <x:c r="F17" s="26" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G17" s="26" t="n">
+        <x:v>3167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="26" t="str">
+        <x:v>2014-09</x:v>
+      </x:c>
+      <x:c r="B18" s="34" t="n">
+        <x:v>3170</x:v>
+      </x:c>
+      <x:c r="C18" s="33" t="n">
+        <x:v>102331.68999999992</x:v>
+      </x:c>
+      <x:c r="D18" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="33" t="n">
+        <x:v>104166.3899999999</x:v>
+      </x:c>
+      <x:c r="F18" s="26" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G18" s="26" t="n">
+        <x:v>1957</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="26" t="str">
+        <x:v>2014-10</x:v>
+      </x:c>
+      <x:c r="B19" s="34" t="n">
+        <x:v>2110</x:v>
+      </x:c>
+      <x:c r="C19" s="33" t="n">
+        <x:v>73439.72000000004</x:v>
+      </x:c>
+      <x:c r="D19" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="33" t="n">
+        <x:v>75025.92000000001</x:v>
+      </x:c>
+      <x:c r="F19" s="26" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G19" s="26" t="n">
+        <x:v>1128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="26" t="str">
+        <x:v>2014-11</x:v>
+      </x:c>
+      <x:c r="B20" s="34" t="n">
+        <x:v>3223</x:v>
+      </x:c>
+      <x:c r="C20" s="33" t="n">
+        <x:v>94972.49999999996</x:v>
+      </x:c>
+      <x:c r="D20" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="33" t="n">
+        <x:v>96404.14999999995</x:v>
+      </x:c>
+      <x:c r="F20" s="26" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G20" s="26" t="n">
+        <x:v>2072</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="26" t="str">
+        <x:v>2014-12</x:v>
+      </x:c>
+      <x:c r="B21" s="34" t="n">
+        <x:v>3231</x:v>
+      </x:c>
+      <x:c r="C21" s="33" t="n">
+        <x:v>119163.80000000003</x:v>
+      </x:c>
+      <x:c r="D21" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="33" t="n">
+        <x:v>120000.80000000003</x:v>
+      </x:c>
+      <x:c r="F21" s="26" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G21" s="26" t="n">
+        <x:v>2152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="26" t="str">
+        <x:v>2015-01</x:v>
+      </x:c>
+      <x:c r="B22" s="34" t="n">
+        <x:v>3966</x:v>
+      </x:c>
+      <x:c r="C22" s="33" t="n">
+        <x:v>126209.67000000004</x:v>
+      </x:c>
+      <x:c r="D22" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="33" t="n">
+        <x:v>127867.92000000004</x:v>
+      </x:c>
+      <x:c r="F22" s="26" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G22" s="26" t="n">
+        <x:v>2872</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="26" t="str">
+        <x:v>2015-02</x:v>
+      </x:c>
+      <x:c r="B23" s="34" t="n">
+        <x:v>3282</x:v>
+      </x:c>
+      <x:c r="C23" s="33" t="n">
+        <x:v>119157.46999999986</x:v>
+      </x:c>
+      <x:c r="D23" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="33" t="n">
+        <x:v>121158.48999999985</x:v>
+      </x:c>
+      <x:c r="F23" s="26" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G23" s="26" t="n">
+        <x:v>2341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="26" t="str">
+        <x:v>2015-03</x:v>
+      </x:c>
+      <x:c r="B24" s="34" t="n">
+        <x:v>3154</x:v>
+      </x:c>
+      <x:c r="C24" s="33" t="n">
+        <x:v>95796.39000000006</x:v>
+      </x:c>
+      <x:c r="D24" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="33" t="n">
+        <x:v>96979.71000000006</x:v>
+      </x:c>
+      <x:c r="F24" s="26" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G24" s="26" t="n">
+        <x:v>2113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="26" t="str">
+        <x:v>2015-04</x:v>
+      </x:c>
+      <x:c r="B25" s="34" t="n">
+        <x:v>3434</x:v>
+      </x:c>
+      <x:c r="C25" s="33" t="n">
+        <x:v>102491.52000000018</x:v>
+      </x:c>
+      <x:c r="D25" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="33" t="n">
+        <x:v>103708.14000000017</x:v>
+      </x:c>
+      <x:c r="F25" s="26" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G25" s="26" t="n">
+        <x:v>2399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="26" t="str">
+        <x:v>2015-05</x:v>
+      </x:c>
+      <x:c r="B26" s="34" t="n">
+        <x:v>2723</x:v>
+      </x:c>
+      <x:c r="C26" s="33" t="n">
+        <x:v>99462.44999999995</x:v>
+      </x:c>
+      <x:c r="D26" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="33" t="n">
+        <x:v>100966.99999999994</x:v>
+      </x:c>
+      <x:c r="F26" s="26" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G26" s="26" t="n">
+        <x:v>1766</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="26" t="str">
+        <x:v>2015-06</x:v>
+      </x:c>
+      <x:c r="B27" s="34" t="n">
+        <x:v>3172</x:v>
+      </x:c>
+      <x:c r="C27" s="33" t="n">
+        <x:v>72234.23000000007</x:v>
+      </x:c>
+      <x:c r="D27" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="33" t="n">
+        <x:v>73105.23000000008</x:v>
+      </x:c>
+      <x:c r="F27" s="26" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="G27" s="26" t="n">
+        <x:v>2079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="26" t="str">
+        <x:v>2015-07</x:v>
+      </x:c>
+      <x:c r="B28" s="34" t="n">
+        <x:v>3769</x:v>
+      </x:c>
+      <x:c r="C28" s="33" t="n">
+        <x:v>99487.10999999996</x:v>
+      </x:c>
+      <x:c r="D28" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="33" t="n">
+        <x:v>100760.10999999996</x:v>
+      </x:c>
+      <x:c r="F28" s="26" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G28" s="26" t="n">
+        <x:v>2642</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="26" t="str">
+        <x:v>2015-08</x:v>
+      </x:c>
+      <x:c r="B29" s="34" t="n">
+        <x:v>3755</x:v>
+      </x:c>
+      <x:c r="C29" s="33" t="n">
+        <x:v>93247.07000000005</x:v>
+      </x:c>
+      <x:c r="D29" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="33" t="n">
+        <x:v>94122.62000000004</x:v>
+      </x:c>
+      <x:c r="F29" s="26" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G29" s="26" t="n">
+        <x:v>2497</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="26" t="str">
+        <x:v>2015-09</x:v>
+      </x:c>
+      <x:c r="B30" s="34" t="n">
+        <x:v>2544</x:v>
+      </x:c>
+      <x:c r="C30" s="33" t="n">
+        <x:v>91189.8</x:v>
+      </x:c>
+      <x:c r="D30" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E30" s="33" t="n">
+        <x:v>92954.33</x:v>
+      </x:c>
+      <x:c r="F30" s="26" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G30" s="26" t="n">
+        <x:v>1607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="26" t="str">
+        <x:v>2015-10</x:v>
+      </x:c>
+      <x:c r="B31" s="34" t="n">
+        <x:v>2291</x:v>
+      </x:c>
+      <x:c r="C31" s="33" t="n">
+        <x:v>97424.86999999997</x:v>
+      </x:c>
+      <x:c r="D31" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="33" t="n">
+        <x:v>99307.48999999993</x:v>
+      </x:c>
+      <x:c r="F31" s="26" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G31" s="26" t="n">
+        <x:v>1329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="26" t="str">
+        <x:v>2015-11</x:v>
+      </x:c>
+      <x:c r="B32" s="34" t="n">
+        <x:v>3270</x:v>
+      </x:c>
+      <x:c r="C32" s="33" t="n">
+        <x:v>103323.46000000006</x:v>
+      </x:c>
+      <x:c r="D32" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E32" s="33" t="n">
+        <x:v>104970.16000000006</x:v>
+      </x:c>
+      <x:c r="F32" s="26" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G32" s="26" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="26" t="str">
+        <x:v>2015-12</x:v>
+      </x:c>
+      <x:c r="B33" s="34" t="n">
+        <x:v>3440</x:v>
+      </x:c>
+      <x:c r="C33" s="33" t="n">
+        <x:v>82803.80000000002</x:v>
+      </x:c>
+      <x:c r="D33" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" s="33" t="n">
+        <x:v>83720.71999999999</x:v>
+      </x:c>
+      <x:c r="F33" s="26" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G33" s="26" t="n">
+        <x:v>2249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="26" t="str">
+        <x:v>2016-01</x:v>
+      </x:c>
+      <x:c r="B34" s="34" t="n">
+        <x:v>3345</x:v>
+      </x:c>
+      <x:c r="C34" s="33" t="n">
+        <x:v>112195.22000000002</x:v>
+      </x:c>
+      <x:c r="D34" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="33" t="n">
+        <x:v>113901.96000000002</x:v>
+      </x:c>
+      <x:c r="F34" s="26" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G34" s="26" t="n">
+        <x:v>2237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="26" t="str">
+        <x:v>2016-02</x:v>
+      </x:c>
+      <x:c r="B35" s="34" t="n">
+        <x:v>2591</x:v>
+      </x:c>
+      <x:c r="C35" s="33" t="n">
+        <x:v>81708.20000000008</x:v>
+      </x:c>
+      <x:c r="D35" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="33" t="n">
+        <x:v>82858.70000000008</x:v>
+      </x:c>
+      <x:c r="F35" s="26" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G35" s="26" t="n">
+        <x:v>1685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="26" t="str">
+        <x:v>2016-03</x:v>
+      </x:c>
+      <x:c r="B36" s="34" t="n">
+        <x:v>3347</x:v>
+      </x:c>
+      <x:c r="C36" s="33" t="n">
+        <x:v>115199.53999999995</x:v>
+      </x:c>
+      <x:c r="D36" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="33" t="n">
+        <x:v>116729.35999999994</x:v>
+      </x:c>
+      <x:c r="F36" s="26" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G36" s="26" t="n">
+        <x:v>2366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="26" t="str">
+        <x:v>2016-04</x:v>
+      </x:c>
+      <x:c r="B37" s="34" t="n">
+        <x:v>3182</x:v>
+      </x:c>
+      <x:c r="C37" s="33" t="n">
+        <x:v>105275.06000000004</x:v>
+      </x:c>
+      <x:c r="D37" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="33" t="n">
+        <x:v>107128.84000000004</x:v>
+      </x:c>
+      <x:c r="F37" s="26" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G37" s="26" t="n">
+        <x:v>2170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="26" t="str">
+        <x:v>2016-05</x:v>
+      </x:c>
+      <x:c r="B38" s="34" t="n">
+        <x:v>2612</x:v>
+      </x:c>
+      <x:c r="C38" s="33" t="n">
+        <x:v>77579.46000000002</x:v>
+      </x:c>
+      <x:c r="D38" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="33" t="n">
+        <x:v>78662.96</x:v>
+      </x:c>
+      <x:c r="F38" s="26" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G38" s="26" t="n">
+        <x:v>1595</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="26" t="str">
+        <x:v>2016-06</x:v>
+      </x:c>
+      <x:c r="B39" s="34" t="n">
+        <x:v>3019</x:v>
+      </x:c>
+      <x:c r="C39" s="33" t="n">
+        <x:v>74209.96000000002</x:v>
+      </x:c>
+      <x:c r="D39" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="33" t="n">
+        <x:v>74786.51000000002</x:v>
+      </x:c>
+      <x:c r="F39" s="26" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G39" s="26" t="n">
+        <x:v>1868</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="26" t="str">
+        <x:v>2016-07</x:v>
+      </x:c>
+      <x:c r="B40" s="34" t="n">
+        <x:v>3726</x:v>
+      </x:c>
+      <x:c r="C40" s="33" t="n">
+        <x:v>95797.87999999998</x:v>
+      </x:c>
+      <x:c r="D40" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="33" t="n">
+        <x:v>96677.87999999998</x:v>
+      </x:c>
+      <x:c r="F40" s="26" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G40" s="26" t="n">
+        <x:v>2335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="26" t="str">
+        <x:v>2016-08</x:v>
+      </x:c>
+      <x:c r="B41" s="34" t="n">
+        <x:v>2997</x:v>
+      </x:c>
+      <x:c r="C41" s="33" t="n">
+        <x:v>75680.02</x:v>
+      </x:c>
+      <x:c r="D41" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E41" s="33" t="n">
+        <x:v>76320.90000000002</x:v>
+      </x:c>
+      <x:c r="F41" s="26" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G41" s="26" t="n">
+        <x:v>1691</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="26" t="str">
+        <x:v>2016-09</x:v>
+      </x:c>
+      <x:c r="B42" s="34" t="n">
+        <x:v>2264</x:v>
+      </x:c>
+      <x:c r="C42" s="33" t="n">
+        <x:v>84530.22000000006</x:v>
+      </x:c>
+      <x:c r="D42" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="33" t="n">
+        <x:v>86231.22000000006</x:v>
+      </x:c>
+      <x:c r="F42" s="26" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G42" s="26" t="n">
+        <x:v>1187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="26" t="str">
+        <x:v>2016-10</x:v>
+      </x:c>
+      <x:c r="B43" s="34" t="n">
+        <x:v>2462</x:v>
+      </x:c>
+      <x:c r="C43" s="33" t="n">
+        <x:v>83774.7600000001</x:v>
+      </x:c>
+      <x:c r="D43" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E43" s="33" t="n">
+        <x:v>85034.76000000008</x:v>
+      </x:c>
+      <x:c r="F43" s="26" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G43" s="26" t="n">
+        <x:v>1271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="26" t="str">
+        <x:v>2016-11</x:v>
+      </x:c>
+      <x:c r="B44" s="34" t="n">
+        <x:v>2543</x:v>
+      </x:c>
+      <x:c r="C44" s="33" t="n">
+        <x:v>79744.0200000002</x:v>
+      </x:c>
+      <x:c r="D44" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E44" s="33" t="n">
+        <x:v>80773.27000000021</x:v>
+      </x:c>
+      <x:c r="F44" s="26" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G44" s="26" t="n">
+        <x:v>1536</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="26" t="str">
+        <x:v>2016-12</x:v>
+      </x:c>
+      <x:c r="B45" s="34" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+      <x:c r="C45" s="33" t="n">
+        <x:v>77693.88999999998</x:v>
+      </x:c>
+      <x:c r="D45" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E45" s="33" t="n">
+        <x:v>78288.88999999997</x:v>
+      </x:c>
+      <x:c r="F45" s="26" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G45" s="26" t="n">
+        <x:v>1791</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="26" t="str">
+        <x:v>2017-01</x:v>
+      </x:c>
+      <x:c r="B46" s="34" t="n">
+        <x:v>2986</x:v>
+      </x:c>
+      <x:c r="C46" s="33" t="n">
+        <x:v>103803.7800000003</x:v>
+      </x:c>
+      <x:c r="D46" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E46" s="33" t="n">
+        <x:v>104681.8900000003</x:v>
+      </x:c>
+      <x:c r="F46" s="26" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G46" s="26" t="n">
+        <x:v>1999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="26" t="str">
+        <x:v>2017-02</x:v>
+      </x:c>
+      <x:c r="B47" s="34" t="n">
+        <x:v>2268</x:v>
+      </x:c>
+      <x:c r="C47" s="33" t="n">
+        <x:v>81197.91000000015</x:v>
+      </x:c>
+      <x:c r="D47" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E47" s="33" t="n">
+        <x:v>82177.91000000015</x:v>
+      </x:c>
+      <x:c r="F47" s="26" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G47" s="26" t="n">
+        <x:v>1315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="26" t="str">
+        <x:v>2017-03</x:v>
+      </x:c>
+      <x:c r="B48" s="34" t="n">
+        <x:v>2523</x:v>
+      </x:c>
+      <x:c r="C48" s="33" t="n">
+        <x:v>92110.16000000002</x:v>
+      </x:c>
+      <x:c r="D48" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E48" s="33" t="n">
+        <x:v>93631.53000000004</x:v>
+      </x:c>
+      <x:c r="F48" s="26" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G48" s="26" t="n">
+        <x:v>1470</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="26" t="str">
+        <x:v>2017-04</x:v>
+      </x:c>
+      <x:c r="B49" s="34" t="n">
+        <x:v>2759</x:v>
+      </x:c>
+      <x:c r="C49" s="33" t="n">
+        <x:v>82854.04000000036</x:v>
+      </x:c>
+      <x:c r="D49" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E49" s="33" t="n">
+        <x:v>83665.74000000034</x:v>
+      </x:c>
+      <x:c r="F49" s="26" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G49" s="26" t="n">
+        <x:v>1742</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="26" t="str">
+        <x:v>2017-05</x:v>
+      </x:c>
+      <x:c r="B50" s="34" t="n">
+        <x:v>1905</x:v>
+      </x:c>
+      <x:c r="C50" s="33" t="n">
+        <x:v>74757.59000000003</x:v>
+      </x:c>
+      <x:c r="D50" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E50" s="33" t="n">
+        <x:v>75836.80000000003</x:v>
+      </x:c>
+      <x:c r="F50" s="26" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G50" s="26" t="n">
+        <x:v>973</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="26" t="str">
+        <x:v>2017-06</x:v>
+      </x:c>
+      <x:c r="B51" s="34" t="n">
+        <x:v>2773</x:v>
+      </x:c>
+      <x:c r="C51" s="33" t="n">
+        <x:v>69821.05000000008</x:v>
+      </x:c>
+      <x:c r="D51" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E51" s="33" t="n">
+        <x:v>70316.05000000008</x:v>
+      </x:c>
+      <x:c r="F51" s="26" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G51" s="26" t="n">
+        <x:v>1621</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="26" t="str">
+        <x:v>2017-07</x:v>
+      </x:c>
+      <x:c r="B52" s="34" t="n">
+        <x:v>2674</x:v>
+      </x:c>
+      <x:c r="C52" s="33" t="n">
+        <x:v>68449.1200000001</x:v>
+      </x:c>
+      <x:c r="D52" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E52" s="33" t="n">
+        <x:v>69156.72000000009</x:v>
+      </x:c>
+      <x:c r="F52" s="26" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G52" s="26" t="n">
+        <x:v>1579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="26" t="str">
+        <x:v>2017-08</x:v>
+      </x:c>
+      <x:c r="B53" s="34" t="n">
+        <x:v>2496</x:v>
+      </x:c>
+      <x:c r="C53" s="33" t="n">
+        <x:v>74112.06000000007</x:v>
+      </x:c>
+      <x:c r="D53" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E53" s="33" t="n">
+        <x:v>75406.06000000006</x:v>
+      </x:c>
+      <x:c r="F53" s="26" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G53" s="26" t="n">
+        <x:v>1436</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="26" t="str">
+        <x:v>2017-09</x:v>
+      </x:c>
+      <x:c r="B54" s="34" t="n">
+        <x:v>2114</x:v>
+      </x:c>
+      <x:c r="C54" s="33" t="n">
+        <x:v>88468.27000000005</x:v>
+      </x:c>
+      <x:c r="D54" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E54" s="33" t="n">
+        <x:v>89797.07000000004</x:v>
+      </x:c>
+      <x:c r="F54" s="26" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G54" s="26" t="n">
+        <x:v>1250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="26" t="str">
+        <x:v>2017-10</x:v>
+      </x:c>
+      <x:c r="B55" s="34" t="n">
+        <x:v>1857</x:v>
+      </x:c>
+      <x:c r="C55" s="33" t="n">
+        <x:v>78380.04000000001</x:v>
+      </x:c>
+      <x:c r="D55" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E55" s="33" t="n">
+        <x:v>79925.75000000003</x:v>
+      </x:c>
+      <x:c r="F55" s="26" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G55" s="26" t="n">
+        <x:v>1044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="26" t="str">
+        <x:v>2017-11</x:v>
+      </x:c>
+      <x:c r="B56" s="34" t="n">
+        <x:v>2504</x:v>
+      </x:c>
+      <x:c r="C56" s="33" t="n">
+        <x:v>86151.58</x:v>
+      </x:c>
+      <x:c r="D56" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E56" s="33" t="n">
+        <x:v>87443.43000000002</x:v>
+      </x:c>
+      <x:c r="F56" s="26" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G56" s="26" t="n">
+        <x:v>1494</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="26" t="str">
+        <x:v>2017-12</x:v>
+      </x:c>
+      <x:c r="B57" s="34" t="n">
+        <x:v>2709</x:v>
+      </x:c>
+      <x:c r="C57" s="33" t="n">
+        <x:v>65928.73999999999</x:v>
+      </x:c>
+      <x:c r="D57" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E57" s="33" t="n">
+        <x:v>66757.13999999998</x:v>
+      </x:c>
+      <x:c r="F57" s="26" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G57" s="26" t="n">
+        <x:v>1603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="26" t="str">
+        <x:v>2018-01</x:v>
+      </x:c>
+      <x:c r="B58" s="34" t="n">
+        <x:v>2768</x:v>
+      </x:c>
+      <x:c r="C58" s="33" t="n">
+        <x:v>89537.56999999995</x:v>
+      </x:c>
+      <x:c r="D58" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E58" s="33" t="n">
+        <x:v>91159.36999999995</x:v>
+      </x:c>
+      <x:c r="F58" s="26" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G58" s="26" t="n">
+        <x:v>1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="26" t="str">
+        <x:v>2018-02</x:v>
+      </x:c>
+      <x:c r="B59" s="34" t="n">
+        <x:v>2316</x:v>
+      </x:c>
+      <x:c r="C59" s="33" t="n">
+        <x:v>71206.81000000001</x:v>
+      </x:c>
+      <x:c r="D59" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E59" s="33" t="n">
+        <x:v>72207.87000000004</x:v>
+      </x:c>
+      <x:c r="F59" s="26" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G59" s="26" t="n">
+        <x:v>1233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="26" t="str">
+        <x:v>2018-03</x:v>
+      </x:c>
+      <x:c r="B60" s="34" t="n">
+        <x:v>3055</x:v>
+      </x:c>
+      <x:c r="C60" s="33" t="n">
+        <x:v>84901.87000000007</x:v>
+      </x:c>
+      <x:c r="D60" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E60" s="33" t="n">
+        <x:v>85838.87000000008</x:v>
+      </x:c>
+      <x:c r="F60" s="26" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G60" s="26" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="26" t="str">
+        <x:v>2018-04</x:v>
+      </x:c>
+      <x:c r="B61" s="34" t="n">
+        <x:v>2516</x:v>
+      </x:c>
+      <x:c r="C61" s="33" t="n">
+        <x:v>78674.64000000001</x:v>
+      </x:c>
+      <x:c r="D61" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E61" s="33" t="n">
+        <x:v>79640.81000000004</x:v>
+      </x:c>
+      <x:c r="F61" s="26" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G61" s="26" t="n">
+        <x:v>1450</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="26" t="str">
+        <x:v>2018-05</x:v>
+      </x:c>
+      <x:c r="B62" s="34" t="n">
+        <x:v>2128</x:v>
+      </x:c>
+      <x:c r="C62" s="33" t="n">
+        <x:v>73960.40999999997</x:v>
+      </x:c>
+      <x:c r="D62" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E62" s="33" t="n">
+        <x:v>74972.15999999999</x:v>
+      </x:c>
+      <x:c r="F62" s="26" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G62" s="26" t="n">
+        <x:v>1134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="26" t="str">
+        <x:v>2018-06</x:v>
+      </x:c>
+      <x:c r="B63" s="34" t="n">
+        <x:v>2889</x:v>
+      </x:c>
+      <x:c r="C63" s="33" t="n">
+        <x:v>70470.71000000004</x:v>
+      </x:c>
+      <x:c r="D63" s="33" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E63" s="33" t="n">
+        <x:v>70568.71000000004</x:v>
+      </x:c>
+      <x:c r="F63" s="26" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G63" s="26" t="n">
+        <x:v>1667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="26" t="str">
+        <x:v>2018-07</x:v>
+      </x:c>
+      <x:c r="B64" s="34" t="n">
+        <x:v>2961</x:v>
+      </x:c>
+      <x:c r="C64" s="33" t="n">
+        <x:v>62861.060000000005</x:v>
+      </x:c>
+      <x:c r="D64" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E64" s="33" t="n">
+        <x:v>63607.02</x:v>
+      </x:c>
+      <x:c r="F64" s="26" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="n">
+        <x:v>1573</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="26" t="str">
+        <x:v>2018-08</x:v>
+      </x:c>
+      <x:c r="B65" s="34" t="n">
+        <x:v>2446</x:v>
+      </x:c>
+      <x:c r="C65" s="33" t="n">
+        <x:v>63266.77000000003</x:v>
+      </x:c>
+      <x:c r="D65" s="33" t="n">
+        <x:v>825</x:v>
+      </x:c>
+      <x:c r="E65" s="33" t="n">
+        <x:v>63115.02000000003</x:v>
+      </x:c>
+      <x:c r="F65" s="26" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G65" s="26" t="n">
+        <x:v>1335</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="26" t="str">
+        <x:v>2018-09</x:v>
+      </x:c>
+      <x:c r="B66" s="34" t="n">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="C66" s="33" t="n">
+        <x:v>73911.30000000002</x:v>
+      </x:c>
+      <x:c r="D66" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E66" s="33" t="n">
+        <x:v>74922.34</x:v>
+      </x:c>
+      <x:c r="F66" s="26" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G66" s="26" t="n">
+        <x:v>1052</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="26" t="str">
+        <x:v>2018-10</x:v>
+      </x:c>
+      <x:c r="B67" s="34" t="n">
+        <x:v>1667</x:v>
+      </x:c>
+      <x:c r="C67" s="33" t="n">
+        <x:v>77344.0599999999</x:v>
+      </x:c>
+      <x:c r="D67" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E67" s="33" t="n">
+        <x:v>78594.70999999988</x:v>
+      </x:c>
+      <x:c r="F67" s="26" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="G67" s="26" t="n">
+        <x:v>757</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="26" t="str">
+        <x:v>2018-11</x:v>
+      </x:c>
+      <x:c r="B68" s="34" t="n">
+        <x:v>2128</x:v>
+      </x:c>
+      <x:c r="C68" s="33" t="n">
+        <x:v>61502.85000000002</x:v>
+      </x:c>
+      <x:c r="D68" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E68" s="33" t="n">
+        <x:v>61865.85000000002</x:v>
+      </x:c>
+      <x:c r="F68" s="26" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G68" s="26" t="n">
+        <x:v>1139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="26" t="str">
+        <x:v>2018-12</x:v>
+      </x:c>
+      <x:c r="B69" s="34" t="n">
+        <x:v>2128</x:v>
+      </x:c>
+      <x:c r="C69" s="33" t="n">
+        <x:v>68233.31999999996</x:v>
+      </x:c>
+      <x:c r="D69" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E69" s="33" t="n">
+        <x:v>68707.31999999996</x:v>
+      </x:c>
+      <x:c r="F69" s="26" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G69" s="26" t="n">
+        <x:v>1076</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="26" t="str">
+        <x:v>2025-01</x:v>
+      </x:c>
+      <x:c r="B70" s="34" t="n">
+        <x:v>1390</x:v>
+      </x:c>
+      <x:c r="C70" s="33" t="n">
+        <x:v>100043.95999999993</x:v>
+      </x:c>
+      <x:c r="D70" s="33" t="n">
+        <x:v>70591.29000000002</x:v>
+      </x:c>
+      <x:c r="E70" s="33" t="n">
+        <x:v>34009.259999999995</x:v>
+      </x:c>
+      <x:c r="F70" s="26" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="G70" s="26" t="n">
+        <x:v>817</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="26" t="str">
+        <x:v>2025-02</x:v>
+      </x:c>
+      <x:c r="B71" s="34" t="n">
+        <x:v>1340</x:v>
+      </x:c>
+      <x:c r="C71" s="33" t="n">
+        <x:v>105039.38999999993</x:v>
+      </x:c>
+      <x:c r="D71" s="33" t="n">
+        <x:v>72370.19000000005</x:v>
+      </x:c>
+      <x:c r="E71" s="33" t="n">
+        <x:v>36972.74</x:v>
+      </x:c>
+      <x:c r="F71" s="26" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G71" s="26" t="n">
+        <x:v>854</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="26" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="B72" s="34" t="n">
+        <x:v>1746</x:v>
+      </x:c>
+      <x:c r="C72" s="33" t="n">
+        <x:v>100210.16999999991</x:v>
+      </x:c>
+      <x:c r="D72" s="33" t="n">
+        <x:v>74212.62000000002</x:v>
+      </x:c>
+      <x:c r="E72" s="33" t="n">
+        <x:v>30890.780000000002</x:v>
+      </x:c>
+      <x:c r="F72" s="26" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G72" s="26" t="n">
+        <x:v>1247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="26" t="str">
+        <x:v>2025-04</x:v>
+      </x:c>
+      <x:c r="B73" s="34" t="n">
+        <x:v>1261</x:v>
+      </x:c>
+      <x:c r="C73" s="33" t="n">
+        <x:v>82392.03</x:v>
+      </x:c>
+      <x:c r="D73" s="33" t="n">
+        <x:v>66855.51000000004</x:v>
+      </x:c>
+      <x:c r="E73" s="33" t="n">
+        <x:v>23890.599999999995</x:v>
+      </x:c>
+      <x:c r="F73" s="26" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G73" s="26" t="n">
+        <x:v>922</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="26" t="str">
+        <x:v>2025-05</x:v>
+      </x:c>
+      <x:c r="B74" s="34" t="n">
+        <x:v>1328</x:v>
+      </x:c>
+      <x:c r="C74" s="33" t="n">
+        <x:v>95579.69999999998</x:v>
+      </x:c>
+      <x:c r="D74" s="33" t="n">
+        <x:v>68913.3400000001</x:v>
+      </x:c>
+      <x:c r="E74" s="33" t="n">
+        <x:v>31153.629999999997</x:v>
+      </x:c>
+      <x:c r="F74" s="26" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G74" s="26" t="n">
+        <x:v>829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="26" t="str">
+        <x:v>2025-06</x:v>
+      </x:c>
+      <x:c r="B75" s="34" t="n">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="C75" s="33" t="n">
+        <x:v>80711.41999999991</x:v>
+      </x:c>
+      <x:c r="D75" s="33" t="n">
+        <x:v>57309.340000000084</x:v>
+      </x:c>
+      <x:c r="E75" s="33" t="n">
+        <x:v>26586.11999999999</x:v>
+      </x:c>
+      <x:c r="F75" s="26" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G75" s="26" t="n">
+        <x:v>1091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="26" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
+      <x:c r="B76" s="34" t="n">
+        <x:v>1534</x:v>
+      </x:c>
+      <x:c r="C76" s="33" t="n">
+        <x:v>78359.51999999981</x:v>
+      </x:c>
+      <x:c r="D76" s="33" t="n">
+        <x:v>63316.92000000007</x:v>
+      </x:c>
+      <x:c r="E76" s="33" t="n">
+        <x:v>18990.549999999992</x:v>
+      </x:c>
+      <x:c r="F76" s="26" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G76" s="26" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="26" t="str">
+        <x:v>2025-08</x:v>
+      </x:c>
+      <x:c r="B77" s="34" t="n">
+        <x:v>1756</x:v>
+      </x:c>
+      <x:c r="C77" s="33" t="n">
+        <x:v>87986.43999999994</x:v>
+      </x:c>
+      <x:c r="D77" s="33" t="n">
+        <x:v>64088.150000000045</x:v>
+      </x:c>
+      <x:c r="E77" s="33" t="n">
+        <x:v>27595.49999999999</x:v>
+      </x:c>
+      <x:c r="F77" s="26" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G77" s="26" t="n">
+        <x:v>1098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="26" t="str">
+        <x:v>2025-09</x:v>
+      </x:c>
+      <x:c r="B78" s="34" t="n">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="C78" s="33" t="n">
+        <x:v>104107.17999999993</x:v>
+      </x:c>
+      <x:c r="D78" s="33" t="n">
+        <x:v>70536.09000000004</x:v>
+      </x:c>
+      <x:c r="E78" s="33" t="n">
+        <x:v>38085.810000000005</x:v>
+      </x:c>
+      <x:c r="F78" s="26" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G78" s="26" t="n">
+        <x:v>683</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="26" t="str">
+        <x:v>2025-10</x:v>
+      </x:c>
+      <x:c r="B79" s="34" t="n">
+        <x:v>1451</x:v>
+      </x:c>
+      <x:c r="C79" s="33" t="n">
+        <x:v>110215.05999999981</x:v>
+      </x:c>
+      <x:c r="D79" s="33" t="n">
+        <x:v>78497.12000000001</x:v>
+      </x:c>
+      <x:c r="E79" s="33" t="n">
+        <x:v>37514.35999999999</x:v>
+      </x:c>
+      <x:c r="F79" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="G79" s="26" t="n">
+        <x:v>944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="26" t="str">
+        <x:v>2025-11</x:v>
+      </x:c>
+      <x:c r="B80" s="34" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="C80" s="33" t="n">
+        <x:v>119581.76000000021</x:v>
+      </x:c>
+      <x:c r="D80" s="33" t="n">
+        <x:v>89808.17</x:v>
+      </x:c>
+      <x:c r="E80" s="33" t="n">
+        <x:v>35829.27999999999</x:v>
+      </x:c>
+      <x:c r="F80" s="26" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G80" s="26" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="26" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="B81" s="34" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+      <x:c r="C81" s="33" t="n">
+        <x:v>83350.15000000005</x:v>
+      </x:c>
+      <x:c r="D81" s="33" t="n">
+        <x:v>63093.38999999999</x:v>
+      </x:c>
+      <x:c r="E81" s="33" t="n">
+        <x:v>23736.889999999996</x:v>
+      </x:c>
+      <x:c r="F81" s="26" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="G81" s="26" t="n">
+        <x:v>924</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="26" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="B82" s="34" t="n">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="C82" s="33" t="n">
+        <x:v>149100.38</x:v>
+      </x:c>
+      <x:c r="D82" s="33" t="n">
+        <x:v>102160.48000000013</x:v>
+      </x:c>
+      <x:c r="E82" s="33" t="n">
+        <x:v>54476.700000000055</x:v>
+      </x:c>
+      <x:c r="F82" s="26" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="G82" s="26" t="n">
+        <x:v>1383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="26" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="B83" s="34" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+      <x:c r="C83" s="33" t="n">
+        <x:v>138263.76000000013</x:v>
+      </x:c>
+      <x:c r="D83" s="33" t="n">
+        <x:v>93983.34999999993</x:v>
+      </x:c>
+      <x:c r="E83" s="33" t="n">
+        <x:v>49906.04000000006</x:v>
+      </x:c>
+      <x:c r="F83" s="26" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="G83" s="26" t="n">
+        <x:v>947</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="26" t="str">
+        <x:v>2026-03</x:v>
+      </x:c>
+      <x:c r="B84" s="34" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="C84" s="33" t="n">
+        <x:v>102584.46000000022</x:v>
+      </x:c>
+      <x:c r="D84" s="33" t="n">
+        <x:v>77206.12999999999</x:v>
+      </x:c>
+      <x:c r="E84" s="33" t="n">
+        <x:v>30805.019999999982</x:v>
+      </x:c>
+      <x:c r="F84" s="26" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G84" s="26" t="n">
+        <x:v>1090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="26" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="B85" s="34" t="n">
+        <x:v>1339</x:v>
+      </x:c>
+      <x:c r="C85" s="33" t="n">
+        <x:v>122029.22999999988</x:v>
+      </x:c>
+      <x:c r="D85" s="33" t="n">
+        <x:v>77013.54000000002</x:v>
+      </x:c>
+      <x:c r="E85" s="33" t="n">
+        <x:v>49566.15000000005</x:v>
+      </x:c>
+      <x:c r="F85" s="26" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="G85" s="26" t="n">
+        <x:v>883</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="26" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="B86" s="34" t="n">
+        <x:v>1744</x:v>
+      </x:c>
+      <x:c r="C86" s="33" t="n">
+        <x:v>102583.65999999997</x:v>
+      </x:c>
+      <x:c r="D86" s="33" t="n">
+        <x:v>74749.29999999999</x:v>
+      </x:c>
+      <x:c r="E86" s="33" t="n">
+        <x:v>32273.119999999988</x:v>
+      </x:c>
+      <x:c r="F86" s="26" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G86" s="26" t="n">
+        <x:v>1319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="26" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="B87" s="34" t="n">
+        <x:v>1530</x:v>
+      </x:c>
+      <x:c r="C87" s="33" t="n">
+        <x:v>103851.23999999993</x:v>
+      </x:c>
+      <x:c r="D87" s="33" t="n">
+        <x:v>70398.12000000004</x:v>
+      </x:c>
+      <x:c r="E87" s="33" t="n">
+        <x:v>37944.56000000002</x:v>
+      </x:c>
+      <x:c r="F87" s="26" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="G87" s="26" t="n">
+        <x:v>1065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="26" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B88" s="34" t="n">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="C88" s="33" t="n">
+        <x:v>106224.69999999998</x:v>
+      </x:c>
+      <x:c r="D88" s="33" t="n">
+        <x:v>70944.62999999999</x:v>
+      </x:c>
+      <x:c r="E88" s="33" t="n">
+        <x:v>39193.270000000004</x:v>
+      </x:c>
+      <x:c r="F88" s="26" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G88" s="26" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="26" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="B17" s="34" t="n">
+      <x:c r="B89" s="34" t="n">
         <x:v>1515</x:v>
       </x:c>
-      <x:c r="C17" s="33" t="n">
+      <x:c r="C89" s="33" t="n">
         <x:v>90997.97999999997</x:v>
       </x:c>
-      <x:c r="D17" s="33" t="n">
+      <x:c r="D89" s="33" t="n">
         <x:v>49903.659999999996</x:v>
       </x:c>
-      <x:c r="E17" s="33" t="n">
+      <x:c r="E89" s="33" t="n">
         <x:v>44044.72000000004</x:v>
       </x:c>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="F89" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G17" s="26" t="n">
+      <x:c r="G89" s="26" t="n">
         <x:v>963</x:v>
       </x:c>
     </x:row>

--- a/dashboard-output/PCS Archive Dashboard.xlsx
+++ b/dashboard-output/PCS Archive Dashboard.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raff344ae72cc4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" r:id="Rc93fcdc3a00b4ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Orders" sheetId="3" r:id="Rcac2219ef4d141ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" r:id="R840b8c8439804078"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" r:id="R55fb3101ab1e4b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R05a4b6ee39464a0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" r:id="Rfb466ff09ffd4206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Orders" sheetId="3" r:id="R92856029ec3c4121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" r:id="R8ff697a30a5f411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" r:id="R2f93abb85a234684"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -324,7 +324,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard'!$A$18:$A$105</c:f>
+              <c:f>'Dashboard'!$A$18:$A$177</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -332,7 +332,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard'!$B$18:$B$105</c:f>
+              <c:f>'Dashboard'!$B$18:$B$177</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -417,7 +417,7 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:r>
-              <a:t>Archived order value by month*</a:t>
+              <a:t>PCS revenue by payment month</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -432,14 +432,14 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Revenue*</c:v>
+            <c:v>PCS revenue</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Dashboard'!$A$18:$A$105</c:f>
+              <c:f>'Dashboard'!$A$18:$A$177</c:f>
               <c:strCache>
                 <c:ptCount val="0"/>
               </c:strCache>
@@ -447,7 +447,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Dashboard'!$C$18:$C$105</c:f>
+              <c:f>'Dashboard'!$C$18:$C$177</c:f>
               <c:numCache>
                 <c:formatCode>$#,##0</c:formatCode>
                 <c:ptCount val="0"/>
@@ -546,7 +546,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31bf880a167c49cf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8f06949d1374f87"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -576,7 +576,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb8ccacce343e4f1c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38fc9fe3494b46d9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -792,7 +792,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>PCS ARCHIVE — v1.1</x:v>
+        <x:v>PCS ARCHIVE — v1.3</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -829,7 +829,7 @@
         <x:v>Archived orders</x:v>
       </x:c>
       <x:c r="B5" s="20" t="n">
-        <x:v>226862</x:v>
+        <x:v>253216</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>Open issues</x:v>
@@ -938,19 +938,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="28" t="str">
-        <x:v>Revenue by Month*</x:v>
+        <x:v>Revenue by Month</x:v>
       </x:c>
       <x:c r="E13" s="28" t="str">
-        <x:v>Archived order totals</x:v>
+        <x:v>PCS payment report</x:v>
       </x:c>
       <x:c r="F13" s="28" t="str">
-        <x:v>Available with caveat</x:v>
+        <x:v>Authoritative</x:v>
       </x:c>
       <x:c r="G13" s="28" t="str">
-        <x:v>Payment transactions for cash basis</x:v>
+        <x:v>Refresh report after new period</x:v>
       </x:c>
       <x:c r="H13" s="28" t="str">
-        <x:v>Yes*</x:v>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -995,7 +995,7 @@
         <x:v>Orders</x:v>
       </x:c>
       <x:c r="C17" s="24" t="str">
-        <x:v>Revenue*</x:v>
+        <x:v>PCS revenue</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1005,9 +1005,7 @@
       <x:c r="B18" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C18" s="29" t="n">
-        <x:v>1001.89</x:v>
-      </x:c>
+      <x:c r="C18" s="29"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
@@ -1016,9 +1014,7 @@
       <x:c r="B19" s="21" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C19" s="29" t="n">
-        <x:v>1973</x:v>
-      </x:c>
+      <x:c r="C19" s="29"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
@@ -1027,9 +1023,7 @@
       <x:c r="B20" s="21" t="n">
         <x:v>648</x:v>
       </x:c>
-      <x:c r="C20" s="29" t="n">
-        <x:v>11978.96</x:v>
-      </x:c>
+      <x:c r="C20" s="29"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
@@ -1038,9 +1032,7 @@
       <x:c r="B21" s="21" t="n">
         <x:v>4972</x:v>
       </x:c>
-      <x:c r="C21" s="29" t="n">
-        <x:v>121933.56</x:v>
-      </x:c>
+      <x:c r="C21" s="29"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
@@ -1049,9 +1041,7 @@
       <x:c r="B22" s="21" t="n">
         <x:v>3376</x:v>
       </x:c>
-      <x:c r="C22" s="29" t="n">
-        <x:v>113854.65999999999</x:v>
-      </x:c>
+      <x:c r="C22" s="29"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str">
@@ -1060,9 +1050,7 @@
       <x:c r="B23" s="21" t="n">
         <x:v>2761</x:v>
       </x:c>
-      <x:c r="C23" s="29" t="n">
-        <x:v>89589.28</x:v>
-      </x:c>
+      <x:c r="C23" s="29"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str">
@@ -1071,9 +1059,7 @@
       <x:c r="B24" s="21" t="n">
         <x:v>3952</x:v>
       </x:c>
-      <x:c r="C24" s="29" t="n">
-        <x:v>110533.26999999999</x:v>
-      </x:c>
+      <x:c r="C24" s="29"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
@@ -1082,9 +1068,7 @@
       <x:c r="B25" s="21" t="n">
         <x:v>4034</x:v>
       </x:c>
-      <x:c r="C25" s="29" t="n">
-        <x:v>87068.74999999999</x:v>
-      </x:c>
+      <x:c r="C25" s="29"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
@@ -1093,9 +1077,7 @@
       <x:c r="B26" s="21" t="n">
         <x:v>3917</x:v>
       </x:c>
-      <x:c r="C26" s="29" t="n">
-        <x:v>111322.27</x:v>
-      </x:c>
+      <x:c r="C26" s="29"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
@@ -1104,9 +1086,7 @@
       <x:c r="B27" s="21" t="n">
         <x:v>2821</x:v>
       </x:c>
-      <x:c r="C27" s="29" t="n">
-        <x:v>96973.52999999998</x:v>
-      </x:c>
+      <x:c r="C27" s="29"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str">
@@ -1115,9 +1095,7 @@
       <x:c r="B28" s="21" t="n">
         <x:v>4413</x:v>
       </x:c>
-      <x:c r="C28" s="29" t="n">
-        <x:v>133639.5</x:v>
-      </x:c>
+      <x:c r="C28" s="29"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str">
@@ -1126,9 +1104,7 @@
       <x:c r="B29" s="21" t="n">
         <x:v>4044</x:v>
       </x:c>
-      <x:c r="C29" s="29" t="n">
-        <x:v>113733.69999999998</x:v>
-      </x:c>
+      <x:c r="C29" s="29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str">
@@ -1137,9 +1113,7 @@
       <x:c r="B30" s="21" t="n">
         <x:v>2984</x:v>
       </x:c>
-      <x:c r="C30" s="29" t="n">
-        <x:v>102570.88999999998</x:v>
-      </x:c>
+      <x:c r="C30" s="29"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str">
@@ -1148,9 +1122,7 @@
       <x:c r="B31" s="21" t="n">
         <x:v>4024</x:v>
       </x:c>
-      <x:c r="C31" s="29" t="n">
-        <x:v>92212.04999999999</x:v>
-      </x:c>
+      <x:c r="C31" s="29"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str">
@@ -1159,9 +1131,7 @@
       <x:c r="B32" s="21" t="n">
         <x:v>4883</x:v>
       </x:c>
-      <x:c r="C32" s="29" t="n">
-        <x:v>115218.16999999984</x:v>
-      </x:c>
+      <x:c r="C32" s="29"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str">
@@ -1170,9 +1140,7 @@
       <x:c r="B33" s="21" t="n">
         <x:v>4973</x:v>
       </x:c>
-      <x:c r="C33" s="29" t="n">
-        <x:v>108253.54999999996</x:v>
-      </x:c>
+      <x:c r="C33" s="29"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str">
@@ -1181,9 +1149,7 @@
       <x:c r="B34" s="21" t="n">
         <x:v>3170</x:v>
       </x:c>
-      <x:c r="C34" s="29" t="n">
-        <x:v>102331.68999999992</x:v>
-      </x:c>
+      <x:c r="C34" s="29"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str">
@@ -1192,9 +1158,7 @@
       <x:c r="B35" s="21" t="n">
         <x:v>2110</x:v>
       </x:c>
-      <x:c r="C35" s="29" t="n">
-        <x:v>73439.72000000004</x:v>
-      </x:c>
+      <x:c r="C35" s="29"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str">
@@ -1203,9 +1167,7 @@
       <x:c r="B36" s="21" t="n">
         <x:v>3223</x:v>
       </x:c>
-      <x:c r="C36" s="29" t="n">
-        <x:v>94972.49999999996</x:v>
-      </x:c>
+      <x:c r="C36" s="29"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
@@ -1214,9 +1176,7 @@
       <x:c r="B37" s="21" t="n">
         <x:v>3231</x:v>
       </x:c>
-      <x:c r="C37" s="29" t="n">
-        <x:v>119163.80000000003</x:v>
-      </x:c>
+      <x:c r="C37" s="29"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
@@ -1225,9 +1185,7 @@
       <x:c r="B38" s="21" t="n">
         <x:v>3966</x:v>
       </x:c>
-      <x:c r="C38" s="29" t="n">
-        <x:v>126209.67000000004</x:v>
-      </x:c>
+      <x:c r="C38" s="29"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str">
@@ -1236,9 +1194,7 @@
       <x:c r="B39" s="21" t="n">
         <x:v>3282</x:v>
       </x:c>
-      <x:c r="C39" s="29" t="n">
-        <x:v>119157.46999999986</x:v>
-      </x:c>
+      <x:c r="C39" s="29"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str">
@@ -1247,9 +1203,7 @@
       <x:c r="B40" s="21" t="n">
         <x:v>3154</x:v>
       </x:c>
-      <x:c r="C40" s="29" t="n">
-        <x:v>95796.39000000006</x:v>
-      </x:c>
+      <x:c r="C40" s="29"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str">
@@ -1258,9 +1212,7 @@
       <x:c r="B41" s="21" t="n">
         <x:v>3434</x:v>
       </x:c>
-      <x:c r="C41" s="29" t="n">
-        <x:v>102491.52000000018</x:v>
-      </x:c>
+      <x:c r="C41" s="29"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
@@ -1269,9 +1221,7 @@
       <x:c r="B42" s="21" t="n">
         <x:v>2723</x:v>
       </x:c>
-      <x:c r="C42" s="29" t="n">
-        <x:v>99462.44999999995</x:v>
-      </x:c>
+      <x:c r="C42" s="29"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
@@ -1280,9 +1230,7 @@
       <x:c r="B43" s="21" t="n">
         <x:v>3172</x:v>
       </x:c>
-      <x:c r="C43" s="29" t="n">
-        <x:v>72234.23000000007</x:v>
-      </x:c>
+      <x:c r="C43" s="29"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
@@ -1291,9 +1239,7 @@
       <x:c r="B44" s="21" t="n">
         <x:v>3769</x:v>
       </x:c>
-      <x:c r="C44" s="29" t="n">
-        <x:v>99487.10999999996</x:v>
-      </x:c>
+      <x:c r="C44" s="29"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
@@ -1302,9 +1248,7 @@
       <x:c r="B45" s="21" t="n">
         <x:v>3755</x:v>
       </x:c>
-      <x:c r="C45" s="29" t="n">
-        <x:v>93247.07000000005</x:v>
-      </x:c>
+      <x:c r="C45" s="29"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
@@ -1313,9 +1257,7 @@
       <x:c r="B46" s="21" t="n">
         <x:v>2544</x:v>
       </x:c>
-      <x:c r="C46" s="29" t="n">
-        <x:v>91189.8</x:v>
-      </x:c>
+      <x:c r="C46" s="29"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
@@ -1324,9 +1266,7 @@
       <x:c r="B47" s="21" t="n">
         <x:v>2291</x:v>
       </x:c>
-      <x:c r="C47" s="29" t="n">
-        <x:v>97424.86999999997</x:v>
-      </x:c>
+      <x:c r="C47" s="29"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
@@ -1335,9 +1275,7 @@
       <x:c r="B48" s="21" t="n">
         <x:v>3270</x:v>
       </x:c>
-      <x:c r="C48" s="29" t="n">
-        <x:v>103323.46000000006</x:v>
-      </x:c>
+      <x:c r="C48" s="29"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
@@ -1346,9 +1284,7 @@
       <x:c r="B49" s="21" t="n">
         <x:v>3440</x:v>
       </x:c>
-      <x:c r="C49" s="29" t="n">
-        <x:v>82803.80000000002</x:v>
-      </x:c>
+      <x:c r="C49" s="29"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -1357,9 +1293,7 @@
       <x:c r="B50" s="21" t="n">
         <x:v>3345</x:v>
       </x:c>
-      <x:c r="C50" s="29" t="n">
-        <x:v>112195.22000000002</x:v>
-      </x:c>
+      <x:c r="C50" s="29"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -1368,9 +1302,7 @@
       <x:c r="B51" s="21" t="n">
         <x:v>2591</x:v>
       </x:c>
-      <x:c r="C51" s="29" t="n">
-        <x:v>81708.20000000008</x:v>
-      </x:c>
+      <x:c r="C51" s="29"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
@@ -1379,9 +1311,7 @@
       <x:c r="B52" s="21" t="n">
         <x:v>3347</x:v>
       </x:c>
-      <x:c r="C52" s="29" t="n">
-        <x:v>115199.53999999995</x:v>
-      </x:c>
+      <x:c r="C52" s="29"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
@@ -1390,9 +1320,7 @@
       <x:c r="B53" s="21" t="n">
         <x:v>3182</x:v>
       </x:c>
-      <x:c r="C53" s="29" t="n">
-        <x:v>105275.06000000004</x:v>
-      </x:c>
+      <x:c r="C53" s="29"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
@@ -1401,9 +1329,7 @@
       <x:c r="B54" s="21" t="n">
         <x:v>2612</x:v>
       </x:c>
-      <x:c r="C54" s="29" t="n">
-        <x:v>77579.46000000002</x:v>
-      </x:c>
+      <x:c r="C54" s="29"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
@@ -1413,7 +1339,7 @@
         <x:v>3019</x:v>
       </x:c>
       <x:c r="C55" s="29" t="n">
-        <x:v>74209.96000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1424,7 +1350,7 @@
         <x:v>3726</x:v>
       </x:c>
       <x:c r="C56" s="29" t="n">
-        <x:v>95797.87999999998</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -1435,7 +1361,7 @@
         <x:v>2997</x:v>
       </x:c>
       <x:c r="C57" s="29" t="n">
-        <x:v>75680.02</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -1446,7 +1372,7 @@
         <x:v>2264</x:v>
       </x:c>
       <x:c r="C58" s="29" t="n">
-        <x:v>84530.22000000006</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -1457,7 +1383,7 @@
         <x:v>2462</x:v>
       </x:c>
       <x:c r="C59" s="29" t="n">
-        <x:v>83774.7600000001</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -1468,7 +1394,7 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C60" s="29" t="n">
-        <x:v>79744.0200000002</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -1479,7 +1405,7 @@
         <x:v>2860</x:v>
       </x:c>
       <x:c r="C61" s="29" t="n">
-        <x:v>77693.88999999998</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1490,7 +1416,7 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="C62" s="29" t="n">
-        <x:v>103803.7800000003</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1501,7 +1427,7 @@
         <x:v>2268</x:v>
       </x:c>
       <x:c r="C63" s="29" t="n">
-        <x:v>81197.91000000015</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1512,7 +1438,7 @@
         <x:v>2523</x:v>
       </x:c>
       <x:c r="C64" s="29" t="n">
-        <x:v>92110.16000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -1523,7 +1449,7 @@
         <x:v>2759</x:v>
       </x:c>
       <x:c r="C65" s="29" t="n">
-        <x:v>82854.04000000036</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -1534,7 +1460,7 @@
         <x:v>1905</x:v>
       </x:c>
       <x:c r="C66" s="29" t="n">
-        <x:v>74757.59000000003</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -1545,7 +1471,7 @@
         <x:v>2773</x:v>
       </x:c>
       <x:c r="C67" s="29" t="n">
-        <x:v>69821.05000000008</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -1556,7 +1482,7 @@
         <x:v>2674</x:v>
       </x:c>
       <x:c r="C68" s="29" t="n">
-        <x:v>68449.1200000001</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -1567,7 +1493,7 @@
         <x:v>2496</x:v>
       </x:c>
       <x:c r="C69" s="29" t="n">
-        <x:v>74112.06000000007</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -1578,7 +1504,7 @@
         <x:v>2114</x:v>
       </x:c>
       <x:c r="C70" s="29" t="n">
-        <x:v>88468.27000000005</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -1589,7 +1515,7 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="C71" s="29" t="n">
-        <x:v>78380.04000000001</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -1600,7 +1526,7 @@
         <x:v>2504</x:v>
       </x:c>
       <x:c r="C72" s="29" t="n">
-        <x:v>86151.58</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -1611,7 +1537,7 @@
         <x:v>2709</x:v>
       </x:c>
       <x:c r="C73" s="29" t="n">
-        <x:v>65928.73999999999</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -1622,7 +1548,7 @@
         <x:v>2768</x:v>
       </x:c>
       <x:c r="C74" s="29" t="n">
-        <x:v>89537.56999999995</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -1633,7 +1559,7 @@
         <x:v>2316</x:v>
       </x:c>
       <x:c r="C75" s="29" t="n">
-        <x:v>71206.81000000001</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -1644,7 +1570,7 @@
         <x:v>3055</x:v>
       </x:c>
       <x:c r="C76" s="29" t="n">
-        <x:v>84901.87000000007</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -1655,7 +1581,7 @@
         <x:v>2516</x:v>
       </x:c>
       <x:c r="C77" s="29" t="n">
-        <x:v>78674.64000000001</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -1666,7 +1592,7 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="C78" s="29" t="n">
-        <x:v>73960.40999999997</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -1677,7 +1603,7 @@
         <x:v>2889</x:v>
       </x:c>
       <x:c r="C79" s="29" t="n">
-        <x:v>70470.71000000004</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -1688,7 +1614,7 @@
         <x:v>2961</x:v>
       </x:c>
       <x:c r="C80" s="29" t="n">
-        <x:v>62861.060000000005</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -1699,7 +1625,7 @@
         <x:v>2446</x:v>
       </x:c>
       <x:c r="C81" s="29" t="n">
-        <x:v>63266.77000000003</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -1710,7 +1636,7 @@
         <x:v>2027</x:v>
       </x:c>
       <x:c r="C82" s="29" t="n">
-        <x:v>73911.30000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -1721,7 +1647,7 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="C83" s="29" t="n">
-        <x:v>77344.0599999999</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -1732,7 +1658,7 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="C84" s="29" t="n">
-        <x:v>61502.85000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -1743,260 +1669,932 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="C85" s="29" t="n">
-        <x:v>68233.31999999996</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>2025-01</x:v>
+        <x:v>2019-01</x:v>
       </x:c>
       <x:c r="B86" s="21" t="n">
-        <x:v>1390</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="C86" s="29" t="n">
-        <x:v>100043.95999999993</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>2025-02</x:v>
+        <x:v>2019-02</x:v>
       </x:c>
       <x:c r="B87" s="21" t="n">
-        <x:v>1340</x:v>
+        <x:v>2126</x:v>
       </x:c>
       <x:c r="C87" s="29" t="n">
-        <x:v>105039.38999999993</x:v>
+        <x:v>29303.59</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>2025-03</x:v>
+        <x:v>2019-03</x:v>
       </x:c>
       <x:c r="B88" s="21" t="n">
-        <x:v>1746</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="C88" s="29" t="n">
-        <x:v>100210.16999999991</x:v>
+        <x:v>59336.62</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>2025-04</x:v>
+        <x:v>2019-04</x:v>
       </x:c>
       <x:c r="B89" s="21" t="n">
-        <x:v>1261</x:v>
+        <x:v>1966</x:v>
       </x:c>
       <x:c r="C89" s="29" t="n">
-        <x:v>82392.03</x:v>
+        <x:v>37093.03</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>2025-05</x:v>
+        <x:v>2019-05</x:v>
       </x:c>
       <x:c r="B90" s="21" t="n">
-        <x:v>1328</x:v>
+        <x:v>1828</x:v>
       </x:c>
       <x:c r="C90" s="29" t="n">
-        <x:v>95579.69999999998</x:v>
+        <x:v>36639.27</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>2025-06</x:v>
+        <x:v>2019-06</x:v>
       </x:c>
       <x:c r="B91" s="21" t="n">
-        <x:v>1555</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="C91" s="29" t="n">
-        <x:v>80711.41999999991</x:v>
+        <x:v>51453.51</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>2025-07</x:v>
+        <x:v>2019-07</x:v>
       </x:c>
       <x:c r="B92" s="21" t="n">
-        <x:v>1534</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="C92" s="29" t="n">
-        <x:v>78359.51999999981</x:v>
+        <x:v>53820.3</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>2025-08</x:v>
+        <x:v>2019-08</x:v>
       </x:c>
       <x:c r="B93" s="21" t="n">
-        <x:v>1756</x:v>
+        <x:v>2068</x:v>
       </x:c>
       <x:c r="C93" s="29" t="n">
-        <x:v>87986.43999999994</x:v>
+        <x:v>40673.59</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="str">
-        <x:v>2025-09</x:v>
+        <x:v>2019-09</x:v>
       </x:c>
       <x:c r="B94" s="21" t="n">
-        <x:v>1135</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="C94" s="29" t="n">
-        <x:v>104107.17999999993</x:v>
+        <x:v>42218.04</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
-        <x:v>2025-10</x:v>
+        <x:v>2019-10</x:v>
       </x:c>
       <x:c r="B95" s="21" t="n">
-        <x:v>1451</x:v>
+        <x:v>1756</x:v>
       </x:c>
       <x:c r="C95" s="29" t="n">
-        <x:v>110215.05999999981</x:v>
+        <x:v>37782.11</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
-        <x:v>2025-11</x:v>
+        <x:v>2019-11</x:v>
       </x:c>
       <x:c r="B96" s="21" t="n">
-        <x:v>2001</x:v>
+        <x:v>2351</x:v>
       </x:c>
       <x:c r="C96" s="29" t="n">
-        <x:v>119581.76000000021</x:v>
+        <x:v>54892.13</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="str">
-        <x:v>2025-12</x:v>
+        <x:v>2019-12</x:v>
       </x:c>
       <x:c r="B97" s="21" t="n">
-        <x:v>1395</x:v>
+        <x:v>1940</x:v>
       </x:c>
       <x:c r="C97" s="29" t="n">
-        <x:v>83350.15000000005</x:v>
+        <x:v>53225.62</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="str">
-        <x:v>2026-01</x:v>
-      </x:c>
-      <x:c r="B98" s="21" t="n">
-        <x:v>1984</x:v>
-      </x:c>
+        <x:v>2020-01</x:v>
+      </x:c>
+      <x:c r="B98" s="21"/>
       <x:c r="C98" s="29" t="n">
-        <x:v>149100.38</x:v>
+        <x:v>52243.19</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="str">
-        <x:v>2026-02</x:v>
-      </x:c>
-      <x:c r="B99" s="21" t="n">
-        <x:v>1419</x:v>
-      </x:c>
+        <x:v>2020-02</x:v>
+      </x:c>
+      <x:c r="B99" s="21"/>
       <x:c r="C99" s="29" t="n">
-        <x:v>138263.76000000013</x:v>
+        <x:v>57234.17</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="str">
-        <x:v>2026-03</x:v>
-      </x:c>
-      <x:c r="B100" s="21" t="n">
-        <x:v>1560</x:v>
-      </x:c>
+        <x:v>2020-03</x:v>
+      </x:c>
+      <x:c r="B100" s="21"/>
       <x:c r="C100" s="29" t="n">
-        <x:v>102584.46000000022</x:v>
+        <x:v>19211.36</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="str">
-        <x:v>2026-04</x:v>
-      </x:c>
-      <x:c r="B101" s="21" t="n">
-        <x:v>1339</x:v>
-      </x:c>
+        <x:v>2020-04</x:v>
+      </x:c>
+      <x:c r="B101" s="21"/>
       <x:c r="C101" s="29" t="n">
-        <x:v>122029.22999999988</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="str">
-        <x:v>2026-05</x:v>
-      </x:c>
-      <x:c r="B102" s="21" t="n">
-        <x:v>1744</x:v>
-      </x:c>
+        <x:v>2020-05</x:v>
+      </x:c>
+      <x:c r="B102" s="21"/>
       <x:c r="C102" s="29" t="n">
-        <x:v>102583.65999999997</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="str">
-        <x:v>2026-06</x:v>
-      </x:c>
-      <x:c r="B103" s="21" t="n">
-        <x:v>1530</x:v>
-      </x:c>
+        <x:v>2020-06</x:v>
+      </x:c>
+      <x:c r="B103" s="21"/>
       <x:c r="C103" s="29" t="n">
-        <x:v>103851.23999999993</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="str">
-        <x:v>2026-07</x:v>
-      </x:c>
-      <x:c r="B104" s="21" t="n">
-        <x:v>1983</x:v>
-      </x:c>
+        <x:v>2020-07</x:v>
+      </x:c>
+      <x:c r="B104" s="21"/>
       <x:c r="C104" s="29" t="n">
-        <x:v>106224.69999999998</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="str">
+        <x:v>2020-08</x:v>
+      </x:c>
+      <x:c r="B105" s="21"/>
+      <x:c r="C105" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>2020-09</x:v>
+      </x:c>
+      <x:c r="B106" s="21"/>
+      <x:c r="C106" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>2020-10</x:v>
+      </x:c>
+      <x:c r="B107" s="21"/>
+      <x:c r="C107" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>2020-11</x:v>
+      </x:c>
+      <x:c r="B108" s="21"/>
+      <x:c r="C108" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>2020-12</x:v>
+      </x:c>
+      <x:c r="B109" s="21"/>
+      <x:c r="C109" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>2021-01</x:v>
+      </x:c>
+      <x:c r="B110" s="21"/>
+      <x:c r="C110" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>2021-02</x:v>
+      </x:c>
+      <x:c r="B111" s="21"/>
+      <x:c r="C111" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>2021-03</x:v>
+      </x:c>
+      <x:c r="B112" s="21"/>
+      <x:c r="C112" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>2021-04</x:v>
+      </x:c>
+      <x:c r="B113" s="21"/>
+      <x:c r="C113" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>2021-05</x:v>
+      </x:c>
+      <x:c r="B114" s="21"/>
+      <x:c r="C114" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>2021-06</x:v>
+      </x:c>
+      <x:c r="B115" s="21"/>
+      <x:c r="C115" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>2021-07</x:v>
+      </x:c>
+      <x:c r="B116" s="21"/>
+      <x:c r="C116" s="29" t="n">
+        <x:v>27983.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>2021-08</x:v>
+      </x:c>
+      <x:c r="B117" s="21"/>
+      <x:c r="C117" s="29" t="n">
+        <x:v>39607.48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>2021-09</x:v>
+      </x:c>
+      <x:c r="B118" s="21"/>
+      <x:c r="C118" s="29" t="n">
+        <x:v>43726.61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>2021-10</x:v>
+      </x:c>
+      <x:c r="B119" s="21"/>
+      <x:c r="C119" s="29" t="n">
+        <x:v>42424.46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>2021-11</x:v>
+      </x:c>
+      <x:c r="B120" s="21"/>
+      <x:c r="C120" s="29" t="n">
+        <x:v>52804.11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>2021-12</x:v>
+      </x:c>
+      <x:c r="B121" s="21"/>
+      <x:c r="C121" s="29" t="n">
+        <x:v>46125.72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>2022-01</x:v>
+      </x:c>
+      <x:c r="B122" s="21"/>
+      <x:c r="C122" s="29" t="n">
+        <x:v>38598.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>2022-02</x:v>
+      </x:c>
+      <x:c r="B123" s="21"/>
+      <x:c r="C123" s="29" t="n">
+        <x:v>44002.91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>2022-03</x:v>
+      </x:c>
+      <x:c r="B124" s="21"/>
+      <x:c r="C124" s="29" t="n">
+        <x:v>45419.66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>2022-04</x:v>
+      </x:c>
+      <x:c r="B125" s="21"/>
+      <x:c r="C125" s="29" t="n">
+        <x:v>57246.72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>2022-05</x:v>
+      </x:c>
+      <x:c r="B126" s="21"/>
+      <x:c r="C126" s="29" t="n">
+        <x:v>55471.19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>2022-06</x:v>
+      </x:c>
+      <x:c r="B127" s="21"/>
+      <x:c r="C127" s="29" t="n">
+        <x:v>48342.62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>2022-07</x:v>
+      </x:c>
+      <x:c r="B128" s="21"/>
+      <x:c r="C128" s="29" t="n">
+        <x:v>50473.48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>2022-08</x:v>
+      </x:c>
+      <x:c r="B129" s="21"/>
+      <x:c r="C129" s="29" t="n">
+        <x:v>46993.93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>2022-09</x:v>
+      </x:c>
+      <x:c r="B130" s="21"/>
+      <x:c r="C130" s="29" t="n">
+        <x:v>48420.96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>2022-10</x:v>
+      </x:c>
+      <x:c r="B131" s="21"/>
+      <x:c r="C131" s="29" t="n">
+        <x:v>44148.91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>2022-11</x:v>
+      </x:c>
+      <x:c r="B132" s="21"/>
+      <x:c r="C132" s="29" t="n">
+        <x:v>38502.71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="B133" s="21"/>
+      <x:c r="C133" s="29" t="n">
+        <x:v>57061.19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>2023-01</x:v>
+      </x:c>
+      <x:c r="B134" s="21"/>
+      <x:c r="C134" s="29" t="n">
+        <x:v>65471.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>2023-02</x:v>
+      </x:c>
+      <x:c r="B135" s="21"/>
+      <x:c r="C135" s="29" t="n">
+        <x:v>49450.61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>2023-03</x:v>
+      </x:c>
+      <x:c r="B136" s="21"/>
+      <x:c r="C136" s="29" t="n">
+        <x:v>59382.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>2023-04</x:v>
+      </x:c>
+      <x:c r="B137" s="21"/>
+      <x:c r="C137" s="29" t="n">
+        <x:v>52384.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>2023-05</x:v>
+      </x:c>
+      <x:c r="B138" s="21"/>
+      <x:c r="C138" s="29" t="n">
+        <x:v>47233.95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>2023-06</x:v>
+      </x:c>
+      <x:c r="B139" s="21"/>
+      <x:c r="C139" s="29" t="n">
+        <x:v>46617.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>2023-07</x:v>
+      </x:c>
+      <x:c r="B140" s="21"/>
+      <x:c r="C140" s="29" t="n">
+        <x:v>42925.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>2023-08</x:v>
+      </x:c>
+      <x:c r="B141" s="21"/>
+      <x:c r="C141" s="29" t="n">
+        <x:v>48134.28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>2023-09</x:v>
+      </x:c>
+      <x:c r="B142" s="21"/>
+      <x:c r="C142" s="29" t="n">
+        <x:v>45644.01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>2023-10</x:v>
+      </x:c>
+      <x:c r="B143" s="21"/>
+      <x:c r="C143" s="29" t="n">
+        <x:v>39293.39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>2023-11</x:v>
+      </x:c>
+      <x:c r="B144" s="21"/>
+      <x:c r="C144" s="29" t="n">
+        <x:v>43559.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>2023-12</x:v>
+      </x:c>
+      <x:c r="B145" s="21"/>
+      <x:c r="C145" s="29" t="n">
+        <x:v>53937.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="B146" s="21"/>
+      <x:c r="C146" s="29" t="n">
+        <x:v>45101.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>2024-02</x:v>
+      </x:c>
+      <x:c r="B147" s="21"/>
+      <x:c r="C147" s="29" t="n">
+        <x:v>37841.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="B148" s="21"/>
+      <x:c r="C148" s="29" t="n">
+        <x:v>54103.46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>2024-04</x:v>
+      </x:c>
+      <x:c r="B149" s="21"/>
+      <x:c r="C149" s="29" t="n">
+        <x:v>52305.56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>2024-05</x:v>
+      </x:c>
+      <x:c r="B150" s="21"/>
+      <x:c r="C150" s="29" t="n">
+        <x:v>35087.16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>2024-06</x:v>
+      </x:c>
+      <x:c r="B151" s="21"/>
+      <x:c r="C151" s="29" t="n">
+        <x:v>50304.99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>2024-07</x:v>
+      </x:c>
+      <x:c r="B152" s="21"/>
+      <x:c r="C152" s="29" t="n">
+        <x:v>45182.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>2024-08</x:v>
+      </x:c>
+      <x:c r="B153" s="21"/>
+      <x:c r="C153" s="29" t="n">
+        <x:v>47744.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>2024-09</x:v>
+      </x:c>
+      <x:c r="B154" s="21"/>
+      <x:c r="C154" s="29" t="n">
+        <x:v>49822.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>2024-10</x:v>
+      </x:c>
+      <x:c r="B155" s="21"/>
+      <x:c r="C155" s="29" t="n">
+        <x:v>39943.64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>2024-11</x:v>
+      </x:c>
+      <x:c r="B156" s="21"/>
+      <x:c r="C156" s="29" t="n">
+        <x:v>69410.62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="B157" s="21"/>
+      <x:c r="C157" s="29" t="n">
+        <x:v>53803.11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>2025-01</x:v>
+      </x:c>
+      <x:c r="B158" s="21" t="n">
+        <x:v>1390</x:v>
+      </x:c>
+      <x:c r="C158" s="29" t="n">
+        <x:v>58737.16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>2025-02</x:v>
+      </x:c>
+      <x:c r="B159" s="21" t="n">
+        <x:v>1340</x:v>
+      </x:c>
+      <x:c r="C159" s="29" t="n">
+        <x:v>60012.92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="B160" s="21" t="n">
+        <x:v>1746</x:v>
+      </x:c>
+      <x:c r="C160" s="29" t="n">
+        <x:v>75285.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>2025-04</x:v>
+      </x:c>
+      <x:c r="B161" s="21" t="n">
+        <x:v>1261</x:v>
+      </x:c>
+      <x:c r="C161" s="29" t="n">
+        <x:v>56861.59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>2025-05</x:v>
+      </x:c>
+      <x:c r="B162" s="21" t="n">
+        <x:v>1328</x:v>
+      </x:c>
+      <x:c r="C162" s="29" t="n">
+        <x:v>65343.65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>2025-06</x:v>
+      </x:c>
+      <x:c r="B163" s="21" t="n">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="C163" s="29" t="n">
+        <x:v>70212.23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
+      <x:c r="B164" s="21" t="n">
+        <x:v>1534</x:v>
+      </x:c>
+      <x:c r="C164" s="29" t="n">
+        <x:v>62343.79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="str">
+        <x:v>2025-08</x:v>
+      </x:c>
+      <x:c r="B165" s="21" t="n">
+        <x:v>1756</x:v>
+      </x:c>
+      <x:c r="C165" s="29" t="n">
+        <x:v>65130.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="str">
+        <x:v>2025-09</x:v>
+      </x:c>
+      <x:c r="B166" s="21" t="n">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="C166" s="29" t="n">
+        <x:v>55867.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="str">
+        <x:v>2025-10</x:v>
+      </x:c>
+      <x:c r="B167" s="21" t="n">
+        <x:v>1451</x:v>
+      </x:c>
+      <x:c r="C167" s="29" t="n">
+        <x:v>73243.68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="str">
+        <x:v>2025-11</x:v>
+      </x:c>
+      <x:c r="B168" s="21" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="C168" s="29" t="n">
+        <x:v>93390.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="B169" s="21" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+      <x:c r="C169" s="29" t="n">
+        <x:v>74946.73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="B170" s="21" t="n">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="C170" s="29" t="n">
+        <x:v>90714.78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="B171" s="21" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+      <x:c r="C171" s="29" t="n">
+        <x:v>73355.41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>2026-03</x:v>
+      </x:c>
+      <x:c r="B172" s="21" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="C172" s="29" t="n">
+        <x:v>76859.81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="B173" s="21" t="n">
+        <x:v>1339</x:v>
+      </x:c>
+      <x:c r="C173" s="29" t="n">
+        <x:v>68859.93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="B174" s="21" t="n">
+        <x:v>1744</x:v>
+      </x:c>
+      <x:c r="C174" s="29" t="n">
+        <x:v>86575.36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="B175" s="21" t="n">
+        <x:v>1530</x:v>
+      </x:c>
+      <x:c r="C175" s="29" t="n">
+        <x:v>77399.09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B176" s="21" t="n">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="C176" s="29" t="n">
+        <x:v>77329.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="B105" s="21" t="n">
+      <x:c r="B177" s="21" t="n">
         <x:v>1515</x:v>
       </x:c>
-      <x:c r="C105" s="29" t="n">
-        <x:v>90997.97999999997</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107">
-      <x:c r="A107" s="32" t="str">
-        <x:v>Important: Order value and payments shown in this workbook come from order snapshots. They are not yet a reproduction of PCS cash-accounting reports, which require payment/refund transaction dates and allocation logic.</x:v>
-      </x:c>
-      <x:c r="B107" s="32"/>
-      <x:c r="C107" s="32"/>
-      <x:c r="D107" s="32"/>
-      <x:c r="E107" s="32"/>
-      <x:c r="F107" s="32"/>
-      <x:c r="G107" s="32"/>
-      <x:c r="H107" s="32"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="A108" s="32"/>
-      <x:c r="B108" s="32"/>
-      <x:c r="C108" s="32"/>
-      <x:c r="D108" s="32"/>
-      <x:c r="E108" s="32"/>
-      <x:c r="F108" s="32"/>
-      <x:c r="G108" s="32"/>
-      <x:c r="H108" s="32"/>
+      <x:c r="C177" s="29" t="n">
+        <x:v>73182.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="32" t="str">
+        <x:v>Revenue comes from the PCS Revenue By Month report and represents total payments taken by payment month through August 27, 2026. Order counts come from completed archive exports; blank order counts indicate years not yet collected.</x:v>
+      </x:c>
+      <x:c r="B179" s="32"/>
+      <x:c r="C179" s="32"/>
+      <x:c r="D179" s="32"/>
+      <x:c r="E179" s="32"/>
+      <x:c r="F179" s="32"/>
+      <x:c r="G179" s="32"/>
+      <x:c r="H179" s="32"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="32"/>
+      <x:c r="B180" s="32"/>
+      <x:c r="C180" s="32"/>
+      <x:c r="D180" s="32"/>
+      <x:c r="E180" s="32"/>
+      <x:c r="F180" s="32"/>
+      <x:c r="G180" s="32"/>
+      <x:c r="H180" s="32"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H3"/>
     <x:mergeCell ref="D10:H10"/>
-    <x:mergeCell ref="A107:H108"/>
+    <x:mergeCell ref="A179:H180"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R560f52e0b8b7452d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2746d3b588bd4f0f"/>
 </x:worksheet>
 </file>
 
@@ -2178,16 +2776,22 @@
         <x:v>2019</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C8" s="26" t="str"/>
-      <x:c r="D8" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C8" s="26" t="str">
+        <x:v>2019-01-01</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>2019-12-31</x:v>
+      </x:c>
       <x:c r="E8" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="26" t="str"/>
+        <x:v>26354</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="str">
+        <x:v>year-2019-through-2019-12-31</x:v>
+      </x:c>
       <x:c r="G8" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2341,6 +2945,9 @@
     <x:col min="5" max="5" width="19" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="19" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2351,18 +2958,27 @@
         <x:v>Orders</x:v>
       </x:c>
       <x:c r="C1" s="25" t="str">
+        <x:v>PCS revenue</x:v>
+      </x:c>
+      <x:c r="D1" s="25" t="str">
+        <x:v>Archived net payments*</x:v>
+      </x:c>
+      <x:c r="E1" s="25" t="str">
+        <x:v>Archived payments*</x:v>
+      </x:c>
+      <x:c r="F1" s="25" t="str">
+        <x:v>Archived refunds*</x:v>
+      </x:c>
+      <x:c r="G1" s="25" t="str">
         <x:v>Order value*</x:v>
       </x:c>
-      <x:c r="D1" s="25" t="str">
-        <x:v>Payments on orders*</x:v>
-      </x:c>
-      <x:c r="E1" s="25" t="str">
+      <x:c r="H1" s="25" t="str">
         <x:v>Balance due</x:v>
       </x:c>
-      <x:c r="F1" s="25" t="str">
+      <x:c r="I1" s="25" t="str">
         <x:v>Cancelled</x:v>
       </x:c>
-      <x:c r="G1" s="25" t="str">
+      <x:c r="J1" s="25" t="str">
         <x:v>Closed</x:v>
       </x:c>
     </x:row>
@@ -2373,19 +2989,26 @@
       <x:c r="B2" s="35" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C2" s="34" t="n">
+      <x:c r="C2" s="34"/>
+      <x:c r="D2" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="34" t="n">
         <x:v>1001.89</x:v>
       </x:c>
-      <x:c r="D2" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E2" s="34" t="n">
+      <x:c r="H2" s="34" t="n">
         <x:v>1001.89</x:v>
       </x:c>
-      <x:c r="F2" s="26" t="n">
+      <x:c r="I2" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G2" s="26" t="n">
+      <x:c r="J2" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2396,19 +3019,26 @@
       <x:c r="B3" s="35" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C3" s="34" t="n">
+      <x:c r="C3" s="34"/>
+      <x:c r="D3" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" s="34" t="n">
         <x:v>1973</x:v>
       </x:c>
-      <x:c r="D3" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E3" s="34" t="n">
+      <x:c r="H3" s="34" t="n">
         <x:v>1973</x:v>
       </x:c>
-      <x:c r="F3" s="26" t="n">
+      <x:c r="I3" s="26" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G3" s="26" t="n">
+      <x:c r="J3" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -2419,19 +3049,26 @@
       <x:c r="B4" s="35" t="n">
         <x:v>648</x:v>
       </x:c>
-      <x:c r="C4" s="34" t="n">
+      <x:c r="C4" s="34"/>
+      <x:c r="D4" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="34" t="n">
         <x:v>11978.96</x:v>
       </x:c>
-      <x:c r="D4" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E4" s="34" t="n">
+      <x:c r="H4" s="34" t="n">
         <x:v>12038.96</x:v>
       </x:c>
-      <x:c r="F4" s="26" t="n">
+      <x:c r="I4" s="26" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G4" s="26" t="n">
+      <x:c r="J4" s="26" t="n">
         <x:v>463</x:v>
       </x:c>
     </x:row>
@@ -2442,19 +3079,26 @@
       <x:c r="B5" s="35" t="n">
         <x:v>4972</x:v>
       </x:c>
-      <x:c r="C5" s="34" t="n">
+      <x:c r="C5" s="34"/>
+      <x:c r="D5" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="34" t="n">
         <x:v>121933.56</x:v>
       </x:c>
-      <x:c r="D5" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="34" t="n">
+      <x:c r="H5" s="34" t="n">
         <x:v>123387.06</x:v>
       </x:c>
-      <x:c r="F5" s="26" t="n">
+      <x:c r="I5" s="26" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G5" s="26" t="n">
+      <x:c r="J5" s="26" t="n">
         <x:v>3927</x:v>
       </x:c>
     </x:row>
@@ -2465,19 +3109,26 @@
       <x:c r="B6" s="35" t="n">
         <x:v>3376</x:v>
       </x:c>
-      <x:c r="C6" s="34" t="n">
+      <x:c r="C6" s="34"/>
+      <x:c r="D6" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="34" t="n">
         <x:v>113854.65999999999</x:v>
       </x:c>
-      <x:c r="D6" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="34" t="n">
+      <x:c r="H6" s="34" t="n">
         <x:v>114944.65999999999</x:v>
       </x:c>
-      <x:c r="F6" s="26" t="n">
+      <x:c r="I6" s="26" t="n">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G6" s="26" t="n">
+      <x:c r="J6" s="26" t="n">
         <x:v>2804</x:v>
       </x:c>
     </x:row>
@@ -2488,19 +3139,26 @@
       <x:c r="B7" s="35" t="n">
         <x:v>2761</x:v>
       </x:c>
-      <x:c r="C7" s="34" t="n">
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="34" t="n">
         <x:v>89589.28</x:v>
       </x:c>
-      <x:c r="D7" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="34" t="n">
+      <x:c r="H7" s="34" t="n">
         <x:v>90979.28</x:v>
       </x:c>
-      <x:c r="F7" s="26" t="n">
+      <x:c r="I7" s="26" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G7" s="26" t="n">
+      <x:c r="J7" s="26" t="n">
         <x:v>2014</x:v>
       </x:c>
     </x:row>
@@ -2511,19 +3169,26 @@
       <x:c r="B8" s="35" t="n">
         <x:v>3952</x:v>
       </x:c>
-      <x:c r="C8" s="34" t="n">
+      <x:c r="C8" s="34"/>
+      <x:c r="D8" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="n">
         <x:v>110533.26999999999</x:v>
       </x:c>
-      <x:c r="D8" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="34" t="n">
+      <x:c r="H8" s="34" t="n">
         <x:v>111339.26999999999</x:v>
       </x:c>
-      <x:c r="F8" s="26" t="n">
+      <x:c r="I8" s="26" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G8" s="26" t="n">
+      <x:c r="J8" s="26" t="n">
         <x:v>2790</x:v>
       </x:c>
     </x:row>
@@ -2534,19 +3199,26 @@
       <x:c r="B9" s="35" t="n">
         <x:v>4034</x:v>
       </x:c>
-      <x:c r="C9" s="34" t="n">
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="n">
         <x:v>87068.74999999999</x:v>
       </x:c>
-      <x:c r="D9" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="34" t="n">
+      <x:c r="H9" s="34" t="n">
         <x:v>87835.24999999999</x:v>
       </x:c>
-      <x:c r="F9" s="26" t="n">
+      <x:c r="I9" s="26" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G9" s="26" t="n">
+      <x:c r="J9" s="26" t="n">
         <x:v>2524</x:v>
       </x:c>
     </x:row>
@@ -2557,19 +3229,26 @@
       <x:c r="B10" s="35" t="n">
         <x:v>3917</x:v>
       </x:c>
-      <x:c r="C10" s="34" t="n">
-        <x:v>111322.27</x:v>
-      </x:c>
+      <x:c r="C10" s="34"/>
       <x:c r="D10" s="34" t="n">
         <x:v>17</x:v>
       </x:c>
       <x:c r="E10" s="34" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="34" t="n">
+        <x:v>111322.27</x:v>
+      </x:c>
+      <x:c r="H10" s="34" t="n">
         <x:v>112768.27</x:v>
       </x:c>
-      <x:c r="F10" s="26" t="n">
+      <x:c r="I10" s="26" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G10" s="26" t="n">
+      <x:c r="J10" s="26" t="n">
         <x:v>2679</x:v>
       </x:c>
     </x:row>
@@ -2580,19 +3259,26 @@
       <x:c r="B11" s="35" t="n">
         <x:v>2821</x:v>
       </x:c>
-      <x:c r="C11" s="34" t="n">
+      <x:c r="C11" s="34"/>
+      <x:c r="D11" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="34" t="n">
         <x:v>96973.52999999998</x:v>
       </x:c>
-      <x:c r="D11" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="34" t="n">
+      <x:c r="H11" s="34" t="n">
         <x:v>98075.52999999998</x:v>
       </x:c>
-      <x:c r="F11" s="26" t="n">
+      <x:c r="I11" s="26" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G11" s="26" t="n">
+      <x:c r="J11" s="26" t="n">
         <x:v>1893</x:v>
       </x:c>
     </x:row>
@@ -2603,19 +3289,26 @@
       <x:c r="B12" s="35" t="n">
         <x:v>4413</x:v>
       </x:c>
-      <x:c r="C12" s="34" t="n">
+      <x:c r="C12" s="34"/>
+      <x:c r="D12" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="34" t="n">
         <x:v>133639.5</x:v>
       </x:c>
-      <x:c r="D12" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="34" t="n">
+      <x:c r="H12" s="34" t="n">
         <x:v>135503.5</x:v>
       </x:c>
-      <x:c r="F12" s="26" t="n">
+      <x:c r="I12" s="26" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G12" s="26" t="n">
+      <x:c r="J12" s="26" t="n">
         <x:v>3020</x:v>
       </x:c>
     </x:row>
@@ -2626,19 +3319,26 @@
       <x:c r="B13" s="35" t="n">
         <x:v>4044</x:v>
       </x:c>
-      <x:c r="C13" s="34" t="n">
+      <x:c r="C13" s="34"/>
+      <x:c r="D13" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="34" t="n">
         <x:v>113733.69999999998</x:v>
       </x:c>
-      <x:c r="D13" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="34" t="n">
+      <x:c r="H13" s="34" t="n">
         <x:v>114956.69999999998</x:v>
       </x:c>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="I13" s="26" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="n">
+      <x:c r="J13" s="26" t="n">
         <x:v>2635</x:v>
       </x:c>
     </x:row>
@@ -2649,19 +3349,26 @@
       <x:c r="B14" s="35" t="n">
         <x:v>2984</x:v>
       </x:c>
-      <x:c r="C14" s="34" t="n">
+      <x:c r="C14" s="34"/>
+      <x:c r="D14" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="34" t="n">
         <x:v>102570.88999999998</x:v>
       </x:c>
-      <x:c r="D14" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="34" t="n">
+      <x:c r="H14" s="34" t="n">
         <x:v>104223.88999999998</x:v>
       </x:c>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="I14" s="26" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G14" s="26" t="n">
+      <x:c r="J14" s="26" t="n">
         <x:v>1816</x:v>
       </x:c>
     </x:row>
@@ -2672,19 +3379,26 @@
       <x:c r="B15" s="35" t="n">
         <x:v>4024</x:v>
       </x:c>
-      <x:c r="C15" s="34" t="n">
+      <x:c r="C15" s="34"/>
+      <x:c r="D15" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="34" t="n">
         <x:v>92212.04999999999</x:v>
       </x:c>
-      <x:c r="D15" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="34" t="n">
+      <x:c r="H15" s="34" t="n">
         <x:v>92877.00999999998</x:v>
       </x:c>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="I15" s="26" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="G15" s="26" t="n">
+      <x:c r="J15" s="26" t="n">
         <x:v>2436</x:v>
       </x:c>
     </x:row>
@@ -2695,19 +3409,26 @@
       <x:c r="B16" s="35" t="n">
         <x:v>4883</x:v>
       </x:c>
-      <x:c r="C16" s="34" t="n">
+      <x:c r="C16" s="34"/>
+      <x:c r="D16" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="34" t="n">
         <x:v>115218.16999999984</x:v>
       </x:c>
-      <x:c r="D16" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="34" t="n">
+      <x:c r="H16" s="34" t="n">
         <x:v>116206.16999999981</x:v>
       </x:c>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="I16" s="26" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G16" s="26" t="n">
+      <x:c r="J16" s="26" t="n">
         <x:v>3130</x:v>
       </x:c>
     </x:row>
@@ -2718,19 +3439,26 @@
       <x:c r="B17" s="35" t="n">
         <x:v>4973</x:v>
       </x:c>
-      <x:c r="C17" s="34" t="n">
+      <x:c r="C17" s="34"/>
+      <x:c r="D17" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="34" t="n">
         <x:v>108253.54999999996</x:v>
       </x:c>
-      <x:c r="D17" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="34" t="n">
+      <x:c r="H17" s="34" t="n">
         <x:v>109254.14999999995</x:v>
       </x:c>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="I17" s="26" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G17" s="26" t="n">
+      <x:c r="J17" s="26" t="n">
         <x:v>3167</x:v>
       </x:c>
     </x:row>
@@ -2741,19 +3469,26 @@
       <x:c r="B18" s="35" t="n">
         <x:v>3170</x:v>
       </x:c>
-      <x:c r="C18" s="34" t="n">
+      <x:c r="C18" s="34"/>
+      <x:c r="D18" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="34" t="n">
         <x:v>102331.68999999992</x:v>
       </x:c>
-      <x:c r="D18" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E18" s="34" t="n">
+      <x:c r="H18" s="34" t="n">
         <x:v>104166.3899999999</x:v>
       </x:c>
-      <x:c r="F18" s="26" t="n">
+      <x:c r="I18" s="26" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G18" s="26" t="n">
+      <x:c r="J18" s="26" t="n">
         <x:v>1957</x:v>
       </x:c>
     </x:row>
@@ -2764,19 +3499,26 @@
       <x:c r="B19" s="35" t="n">
         <x:v>2110</x:v>
       </x:c>
-      <x:c r="C19" s="34" t="n">
+      <x:c r="C19" s="34"/>
+      <x:c r="D19" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="34" t="n">
         <x:v>73439.72000000004</x:v>
       </x:c>
-      <x:c r="D19" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="34" t="n">
+      <x:c r="H19" s="34" t="n">
         <x:v>75025.92000000001</x:v>
       </x:c>
-      <x:c r="F19" s="26" t="n">
+      <x:c r="I19" s="26" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G19" s="26" t="n">
+      <x:c r="J19" s="26" t="n">
         <x:v>1128</x:v>
       </x:c>
     </x:row>
@@ -2787,19 +3529,26 @@
       <x:c r="B20" s="35" t="n">
         <x:v>3223</x:v>
       </x:c>
-      <x:c r="C20" s="34" t="n">
+      <x:c r="C20" s="34"/>
+      <x:c r="D20" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="34" t="n">
         <x:v>94972.49999999996</x:v>
       </x:c>
-      <x:c r="D20" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="34" t="n">
+      <x:c r="H20" s="34" t="n">
         <x:v>96404.14999999995</x:v>
       </x:c>
-      <x:c r="F20" s="26" t="n">
+      <x:c r="I20" s="26" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G20" s="26" t="n">
+      <x:c r="J20" s="26" t="n">
         <x:v>2072</x:v>
       </x:c>
     </x:row>
@@ -2810,19 +3559,26 @@
       <x:c r="B21" s="35" t="n">
         <x:v>3231</x:v>
       </x:c>
-      <x:c r="C21" s="34" t="n">
+      <x:c r="C21" s="34"/>
+      <x:c r="D21" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="34" t="n">
         <x:v>119163.80000000003</x:v>
       </x:c>
-      <x:c r="D21" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E21" s="34" t="n">
+      <x:c r="H21" s="34" t="n">
         <x:v>120000.80000000003</x:v>
       </x:c>
-      <x:c r="F21" s="26" t="n">
+      <x:c r="I21" s="26" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G21" s="26" t="n">
+      <x:c r="J21" s="26" t="n">
         <x:v>2152</x:v>
       </x:c>
     </x:row>
@@ -2833,19 +3589,26 @@
       <x:c r="B22" s="35" t="n">
         <x:v>3966</x:v>
       </x:c>
-      <x:c r="C22" s="34" t="n">
+      <x:c r="C22" s="34"/>
+      <x:c r="D22" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="34" t="n">
         <x:v>126209.67000000004</x:v>
       </x:c>
-      <x:c r="D22" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E22" s="34" t="n">
+      <x:c r="H22" s="34" t="n">
         <x:v>127867.92000000004</x:v>
       </x:c>
-      <x:c r="F22" s="26" t="n">
+      <x:c r="I22" s="26" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G22" s="26" t="n">
+      <x:c r="J22" s="26" t="n">
         <x:v>2872</x:v>
       </x:c>
     </x:row>
@@ -2856,19 +3619,26 @@
       <x:c r="B23" s="35" t="n">
         <x:v>3282</x:v>
       </x:c>
-      <x:c r="C23" s="34" t="n">
+      <x:c r="C23" s="34"/>
+      <x:c r="D23" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F23" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="34" t="n">
         <x:v>119157.46999999986</x:v>
       </x:c>
-      <x:c r="D23" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E23" s="34" t="n">
+      <x:c r="H23" s="34" t="n">
         <x:v>121158.48999999985</x:v>
       </x:c>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="I23" s="26" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G23" s="26" t="n">
+      <x:c r="J23" s="26" t="n">
         <x:v>2341</x:v>
       </x:c>
     </x:row>
@@ -2879,19 +3649,26 @@
       <x:c r="B24" s="35" t="n">
         <x:v>3154</x:v>
       </x:c>
-      <x:c r="C24" s="34" t="n">
+      <x:c r="C24" s="34"/>
+      <x:c r="D24" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="34" t="n">
         <x:v>95796.39000000006</x:v>
       </x:c>
-      <x:c r="D24" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E24" s="34" t="n">
+      <x:c r="H24" s="34" t="n">
         <x:v>96979.71000000006</x:v>
       </x:c>
-      <x:c r="F24" s="26" t="n">
+      <x:c r="I24" s="26" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G24" s="26" t="n">
+      <x:c r="J24" s="26" t="n">
         <x:v>2113</x:v>
       </x:c>
     </x:row>
@@ -2902,19 +3679,26 @@
       <x:c r="B25" s="35" t="n">
         <x:v>3434</x:v>
       </x:c>
-      <x:c r="C25" s="34" t="n">
+      <x:c r="C25" s="34"/>
+      <x:c r="D25" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="34" t="n">
         <x:v>102491.52000000018</x:v>
       </x:c>
-      <x:c r="D25" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E25" s="34" t="n">
+      <x:c r="H25" s="34" t="n">
         <x:v>103708.14000000017</x:v>
       </x:c>
-      <x:c r="F25" s="26" t="n">
+      <x:c r="I25" s="26" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G25" s="26" t="n">
+      <x:c r="J25" s="26" t="n">
         <x:v>2399</x:v>
       </x:c>
     </x:row>
@@ -2925,19 +3709,26 @@
       <x:c r="B26" s="35" t="n">
         <x:v>2723</x:v>
       </x:c>
-      <x:c r="C26" s="34" t="n">
+      <x:c r="C26" s="34"/>
+      <x:c r="D26" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="34" t="n">
         <x:v>99462.44999999995</x:v>
       </x:c>
-      <x:c r="D26" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="34" t="n">
+      <x:c r="H26" s="34" t="n">
         <x:v>100966.99999999994</x:v>
       </x:c>
-      <x:c r="F26" s="26" t="n">
+      <x:c r="I26" s="26" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="G26" s="26" t="n">
+      <x:c r="J26" s="26" t="n">
         <x:v>1766</x:v>
       </x:c>
     </x:row>
@@ -2948,19 +3739,26 @@
       <x:c r="B27" s="35" t="n">
         <x:v>3172</x:v>
       </x:c>
-      <x:c r="C27" s="34" t="n">
+      <x:c r="C27" s="34"/>
+      <x:c r="D27" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="34" t="n">
         <x:v>72234.23000000007</x:v>
       </x:c>
-      <x:c r="D27" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E27" s="34" t="n">
+      <x:c r="H27" s="34" t="n">
         <x:v>73105.23000000008</x:v>
       </x:c>
-      <x:c r="F27" s="26" t="n">
+      <x:c r="I27" s="26" t="n">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="G27" s="26" t="n">
+      <x:c r="J27" s="26" t="n">
         <x:v>2079</x:v>
       </x:c>
     </x:row>
@@ -2971,19 +3769,26 @@
       <x:c r="B28" s="35" t="n">
         <x:v>3769</x:v>
       </x:c>
-      <x:c r="C28" s="34" t="n">
+      <x:c r="C28" s="34"/>
+      <x:c r="D28" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" s="34" t="n">
         <x:v>99487.10999999996</x:v>
       </x:c>
-      <x:c r="D28" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E28" s="34" t="n">
+      <x:c r="H28" s="34" t="n">
         <x:v>100760.10999999996</x:v>
       </x:c>
-      <x:c r="F28" s="26" t="n">
+      <x:c r="I28" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G28" s="26" t="n">
+      <x:c r="J28" s="26" t="n">
         <x:v>2642</x:v>
       </x:c>
     </x:row>
@@ -2994,19 +3799,26 @@
       <x:c r="B29" s="35" t="n">
         <x:v>3755</x:v>
       </x:c>
-      <x:c r="C29" s="34" t="n">
+      <x:c r="C29" s="34"/>
+      <x:c r="D29" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" s="34" t="n">
         <x:v>93247.07000000005</x:v>
       </x:c>
-      <x:c r="D29" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E29" s="34" t="n">
+      <x:c r="H29" s="34" t="n">
         <x:v>94122.62000000004</x:v>
       </x:c>
-      <x:c r="F29" s="26" t="n">
+      <x:c r="I29" s="26" t="n">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G29" s="26" t="n">
+      <x:c r="J29" s="26" t="n">
         <x:v>2497</x:v>
       </x:c>
     </x:row>
@@ -3017,19 +3829,26 @@
       <x:c r="B30" s="35" t="n">
         <x:v>2544</x:v>
       </x:c>
-      <x:c r="C30" s="34" t="n">
+      <x:c r="C30" s="34"/>
+      <x:c r="D30" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E30" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F30" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="34" t="n">
         <x:v>91189.8</x:v>
       </x:c>
-      <x:c r="D30" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E30" s="34" t="n">
+      <x:c r="H30" s="34" t="n">
         <x:v>92954.33</x:v>
       </x:c>
-      <x:c r="F30" s="26" t="n">
+      <x:c r="I30" s="26" t="n">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G30" s="26" t="n">
+      <x:c r="J30" s="26" t="n">
         <x:v>1607</x:v>
       </x:c>
     </x:row>
@@ -3040,19 +3859,26 @@
       <x:c r="B31" s="35" t="n">
         <x:v>2291</x:v>
       </x:c>
-      <x:c r="C31" s="34" t="n">
+      <x:c r="C31" s="34"/>
+      <x:c r="D31" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F31" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G31" s="34" t="n">
         <x:v>97424.86999999997</x:v>
       </x:c>
-      <x:c r="D31" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E31" s="34" t="n">
+      <x:c r="H31" s="34" t="n">
         <x:v>99307.48999999993</x:v>
       </x:c>
-      <x:c r="F31" s="26" t="n">
+      <x:c r="I31" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G31" s="26" t="n">
+      <x:c r="J31" s="26" t="n">
         <x:v>1329</x:v>
       </x:c>
     </x:row>
@@ -3063,19 +3889,26 @@
       <x:c r="B32" s="35" t="n">
         <x:v>3270</x:v>
       </x:c>
-      <x:c r="C32" s="34" t="n">
+      <x:c r="C32" s="34"/>
+      <x:c r="D32" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E32" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F32" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="34" t="n">
         <x:v>103323.46000000006</x:v>
       </x:c>
-      <x:c r="D32" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E32" s="34" t="n">
+      <x:c r="H32" s="34" t="n">
         <x:v>104970.16000000006</x:v>
       </x:c>
-      <x:c r="F32" s="26" t="n">
+      <x:c r="I32" s="26" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G32" s="26" t="n">
+      <x:c r="J32" s="26" t="n">
         <x:v>2200</x:v>
       </x:c>
     </x:row>
@@ -3086,19 +3919,26 @@
       <x:c r="B33" s="35" t="n">
         <x:v>3440</x:v>
       </x:c>
-      <x:c r="C33" s="34" t="n">
+      <x:c r="C33" s="34"/>
+      <x:c r="D33" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F33" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" s="34" t="n">
         <x:v>82803.80000000002</x:v>
       </x:c>
-      <x:c r="D33" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E33" s="34" t="n">
+      <x:c r="H33" s="34" t="n">
         <x:v>83720.71999999999</x:v>
       </x:c>
-      <x:c r="F33" s="26" t="n">
+      <x:c r="I33" s="26" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G33" s="26" t="n">
+      <x:c r="J33" s="26" t="n">
         <x:v>2249</x:v>
       </x:c>
     </x:row>
@@ -3109,19 +3949,26 @@
       <x:c r="B34" s="35" t="n">
         <x:v>3345</x:v>
       </x:c>
-      <x:c r="C34" s="34" t="n">
+      <x:c r="C34" s="34"/>
+      <x:c r="D34" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G34" s="34" t="n">
         <x:v>112195.22000000002</x:v>
       </x:c>
-      <x:c r="D34" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E34" s="34" t="n">
+      <x:c r="H34" s="34" t="n">
         <x:v>113901.96000000002</x:v>
       </x:c>
-      <x:c r="F34" s="26" t="n">
+      <x:c r="I34" s="26" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G34" s="26" t="n">
+      <x:c r="J34" s="26" t="n">
         <x:v>2237</x:v>
       </x:c>
     </x:row>
@@ -3132,19 +3979,26 @@
       <x:c r="B35" s="35" t="n">
         <x:v>2591</x:v>
       </x:c>
-      <x:c r="C35" s="34" t="n">
+      <x:c r="C35" s="34"/>
+      <x:c r="D35" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F35" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G35" s="34" t="n">
         <x:v>81708.20000000008</x:v>
       </x:c>
-      <x:c r="D35" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="34" t="n">
+      <x:c r="H35" s="34" t="n">
         <x:v>82858.70000000008</x:v>
       </x:c>
-      <x:c r="F35" s="26" t="n">
+      <x:c r="I35" s="26" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="G35" s="26" t="n">
+      <x:c r="J35" s="26" t="n">
         <x:v>1685</x:v>
       </x:c>
     </x:row>
@@ -3155,19 +4009,26 @@
       <x:c r="B36" s="35" t="n">
         <x:v>3347</x:v>
       </x:c>
-      <x:c r="C36" s="34" t="n">
+      <x:c r="C36" s="34"/>
+      <x:c r="D36" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F36" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="34" t="n">
         <x:v>115199.53999999995</x:v>
       </x:c>
-      <x:c r="D36" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E36" s="34" t="n">
+      <x:c r="H36" s="34" t="n">
         <x:v>116729.35999999994</x:v>
       </x:c>
-      <x:c r="F36" s="26" t="n">
+      <x:c r="I36" s="26" t="n">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G36" s="26" t="n">
+      <x:c r="J36" s="26" t="n">
         <x:v>2366</x:v>
       </x:c>
     </x:row>
@@ -3178,19 +4039,26 @@
       <x:c r="B37" s="35" t="n">
         <x:v>3182</x:v>
       </x:c>
-      <x:c r="C37" s="34" t="n">
+      <x:c r="C37" s="34"/>
+      <x:c r="D37" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G37" s="34" t="n">
         <x:v>105275.06000000004</x:v>
       </x:c>
-      <x:c r="D37" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="34" t="n">
+      <x:c r="H37" s="34" t="n">
         <x:v>107128.84000000004</x:v>
       </x:c>
-      <x:c r="F37" s="26" t="n">
+      <x:c r="I37" s="26" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G37" s="26" t="n">
+      <x:c r="J37" s="26" t="n">
         <x:v>2170</x:v>
       </x:c>
     </x:row>
@@ -3201,19 +4069,26 @@
       <x:c r="B38" s="35" t="n">
         <x:v>2612</x:v>
       </x:c>
-      <x:c r="C38" s="34" t="n">
+      <x:c r="C38" s="34"/>
+      <x:c r="D38" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F38" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G38" s="34" t="n">
         <x:v>77579.46000000002</x:v>
       </x:c>
-      <x:c r="D38" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E38" s="34" t="n">
+      <x:c r="H38" s="34" t="n">
         <x:v>78662.96</x:v>
       </x:c>
-      <x:c r="F38" s="26" t="n">
+      <x:c r="I38" s="26" t="n">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G38" s="26" t="n">
+      <x:c r="J38" s="26" t="n">
         <x:v>1595</x:v>
       </x:c>
     </x:row>
@@ -3225,18 +4100,27 @@
         <x:v>3019</x:v>
       </x:c>
       <x:c r="C39" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F39" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" s="34" t="n">
         <x:v>74209.96000000002</x:v>
       </x:c>
-      <x:c r="D39" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E39" s="34" t="n">
+      <x:c r="H39" s="34" t="n">
         <x:v>74786.51000000002</x:v>
       </x:c>
-      <x:c r="F39" s="26" t="n">
+      <x:c r="I39" s="26" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G39" s="26" t="n">
+      <x:c r="J39" s="26" t="n">
         <x:v>1868</x:v>
       </x:c>
     </x:row>
@@ -3248,18 +4132,27 @@
         <x:v>3726</x:v>
       </x:c>
       <x:c r="C40" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="34" t="n">
         <x:v>95797.87999999998</x:v>
       </x:c>
-      <x:c r="D40" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E40" s="34" t="n">
+      <x:c r="H40" s="34" t="n">
         <x:v>96677.87999999998</x:v>
       </x:c>
-      <x:c r="F40" s="26" t="n">
+      <x:c r="I40" s="26" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G40" s="26" t="n">
+      <x:c r="J40" s="26" t="n">
         <x:v>2335</x:v>
       </x:c>
     </x:row>
@@ -3271,18 +4164,27 @@
         <x:v>2997</x:v>
       </x:c>
       <x:c r="C41" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E41" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F41" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G41" s="34" t="n">
         <x:v>75680.02</x:v>
       </x:c>
-      <x:c r="D41" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E41" s="34" t="n">
+      <x:c r="H41" s="34" t="n">
         <x:v>76320.90000000002</x:v>
       </x:c>
-      <x:c r="F41" s="26" t="n">
+      <x:c r="I41" s="26" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G41" s="26" t="n">
+      <x:c r="J41" s="26" t="n">
         <x:v>1691</x:v>
       </x:c>
     </x:row>
@@ -3294,18 +4196,27 @@
         <x:v>2264</x:v>
       </x:c>
       <x:c r="C42" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F42" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="34" t="n">
         <x:v>84530.22000000006</x:v>
       </x:c>
-      <x:c r="D42" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E42" s="34" t="n">
+      <x:c r="H42" s="34" t="n">
         <x:v>86231.22000000006</x:v>
       </x:c>
-      <x:c r="F42" s="26" t="n">
+      <x:c r="I42" s="26" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G42" s="26" t="n">
+      <x:c r="J42" s="26" t="n">
         <x:v>1187</x:v>
       </x:c>
     </x:row>
@@ -3317,18 +4228,27 @@
         <x:v>2462</x:v>
       </x:c>
       <x:c r="C43" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E43" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F43" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G43" s="34" t="n">
         <x:v>83774.7600000001</x:v>
       </x:c>
-      <x:c r="D43" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E43" s="34" t="n">
+      <x:c r="H43" s="34" t="n">
         <x:v>85034.76000000008</x:v>
       </x:c>
-      <x:c r="F43" s="26" t="n">
+      <x:c r="I43" s="26" t="n">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="G43" s="26" t="n">
+      <x:c r="J43" s="26" t="n">
         <x:v>1271</x:v>
       </x:c>
     </x:row>
@@ -3340,18 +4260,27 @@
         <x:v>2543</x:v>
       </x:c>
       <x:c r="C44" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E44" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G44" s="34" t="n">
         <x:v>79744.0200000002</x:v>
       </x:c>
-      <x:c r="D44" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E44" s="34" t="n">
+      <x:c r="H44" s="34" t="n">
         <x:v>80773.27000000021</x:v>
       </x:c>
-      <x:c r="F44" s="26" t="n">
+      <x:c r="I44" s="26" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G44" s="26" t="n">
+      <x:c r="J44" s="26" t="n">
         <x:v>1536</x:v>
       </x:c>
     </x:row>
@@ -3363,18 +4292,27 @@
         <x:v>2860</x:v>
       </x:c>
       <x:c r="C45" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D45" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E45" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" s="34" t="n">
         <x:v>77693.88999999998</x:v>
       </x:c>
-      <x:c r="D45" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E45" s="34" t="n">
+      <x:c r="H45" s="34" t="n">
         <x:v>78288.88999999997</x:v>
       </x:c>
-      <x:c r="F45" s="26" t="n">
+      <x:c r="I45" s="26" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G45" s="26" t="n">
+      <x:c r="J45" s="26" t="n">
         <x:v>1791</x:v>
       </x:c>
     </x:row>
@@ -3386,18 +4324,27 @@
         <x:v>2986</x:v>
       </x:c>
       <x:c r="C46" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D46" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E46" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F46" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G46" s="34" t="n">
         <x:v>103803.7800000003</x:v>
       </x:c>
-      <x:c r="D46" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E46" s="34" t="n">
+      <x:c r="H46" s="34" t="n">
         <x:v>104681.8900000003</x:v>
       </x:c>
-      <x:c r="F46" s="26" t="n">
+      <x:c r="I46" s="26" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G46" s="26" t="n">
+      <x:c r="J46" s="26" t="n">
         <x:v>1999</x:v>
       </x:c>
     </x:row>
@@ -3409,18 +4356,27 @@
         <x:v>2268</x:v>
       </x:c>
       <x:c r="C47" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D47" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E47" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F47" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G47" s="34" t="n">
         <x:v>81197.91000000015</x:v>
       </x:c>
-      <x:c r="D47" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E47" s="34" t="n">
+      <x:c r="H47" s="34" t="n">
         <x:v>82177.91000000015</x:v>
       </x:c>
-      <x:c r="F47" s="26" t="n">
+      <x:c r="I47" s="26" t="n">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G47" s="26" t="n">
+      <x:c r="J47" s="26" t="n">
         <x:v>1315</x:v>
       </x:c>
     </x:row>
@@ -3432,18 +4388,27 @@
         <x:v>2523</x:v>
       </x:c>
       <x:c r="C48" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D48" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E48" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F48" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G48" s="34" t="n">
         <x:v>92110.16000000002</x:v>
       </x:c>
-      <x:c r="D48" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E48" s="34" t="n">
+      <x:c r="H48" s="34" t="n">
         <x:v>93631.53000000004</x:v>
       </x:c>
-      <x:c r="F48" s="26" t="n">
+      <x:c r="I48" s="26" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="G48" s="26" t="n">
+      <x:c r="J48" s="26" t="n">
         <x:v>1470</x:v>
       </x:c>
     </x:row>
@@ -3455,18 +4420,27 @@
         <x:v>2759</x:v>
       </x:c>
       <x:c r="C49" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D49" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E49" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F49" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G49" s="34" t="n">
         <x:v>82854.04000000036</x:v>
       </x:c>
-      <x:c r="D49" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E49" s="34" t="n">
+      <x:c r="H49" s="34" t="n">
         <x:v>83665.74000000034</x:v>
       </x:c>
-      <x:c r="F49" s="26" t="n">
+      <x:c r="I49" s="26" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="G49" s="26" t="n">
+      <x:c r="J49" s="26" t="n">
         <x:v>1742</x:v>
       </x:c>
     </x:row>
@@ -3478,18 +4452,27 @@
         <x:v>1905</x:v>
       </x:c>
       <x:c r="C50" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D50" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E50" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F50" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G50" s="34" t="n">
         <x:v>74757.59000000003</x:v>
       </x:c>
-      <x:c r="D50" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E50" s="34" t="n">
+      <x:c r="H50" s="34" t="n">
         <x:v>75836.80000000003</x:v>
       </x:c>
-      <x:c r="F50" s="26" t="n">
+      <x:c r="I50" s="26" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G50" s="26" t="n">
+      <x:c r="J50" s="26" t="n">
         <x:v>973</x:v>
       </x:c>
     </x:row>
@@ -3501,18 +4484,27 @@
         <x:v>2773</x:v>
       </x:c>
       <x:c r="C51" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D51" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E51" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F51" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G51" s="34" t="n">
         <x:v>69821.05000000008</x:v>
       </x:c>
-      <x:c r="D51" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E51" s="34" t="n">
+      <x:c r="H51" s="34" t="n">
         <x:v>70316.05000000008</x:v>
       </x:c>
-      <x:c r="F51" s="26" t="n">
+      <x:c r="I51" s="26" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G51" s="26" t="n">
+      <x:c r="J51" s="26" t="n">
         <x:v>1621</x:v>
       </x:c>
     </x:row>
@@ -3524,18 +4516,27 @@
         <x:v>2674</x:v>
       </x:c>
       <x:c r="C52" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D52" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E52" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F52" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G52" s="34" t="n">
         <x:v>68449.1200000001</x:v>
       </x:c>
-      <x:c r="D52" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E52" s="34" t="n">
+      <x:c r="H52" s="34" t="n">
         <x:v>69156.72000000009</x:v>
       </x:c>
-      <x:c r="F52" s="26" t="n">
+      <x:c r="I52" s="26" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="G52" s="26" t="n">
+      <x:c r="J52" s="26" t="n">
         <x:v>1579</x:v>
       </x:c>
     </x:row>
@@ -3547,18 +4548,27 @@
         <x:v>2496</x:v>
       </x:c>
       <x:c r="C53" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D53" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E53" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F53" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G53" s="34" t="n">
         <x:v>74112.06000000007</x:v>
       </x:c>
-      <x:c r="D53" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E53" s="34" t="n">
+      <x:c r="H53" s="34" t="n">
         <x:v>75406.06000000006</x:v>
       </x:c>
-      <x:c r="F53" s="26" t="n">
+      <x:c r="I53" s="26" t="n">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G53" s="26" t="n">
+      <x:c r="J53" s="26" t="n">
         <x:v>1436</x:v>
       </x:c>
     </x:row>
@@ -3570,18 +4580,27 @@
         <x:v>2114</x:v>
       </x:c>
       <x:c r="C54" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D54" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E54" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F54" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G54" s="34" t="n">
         <x:v>88468.27000000005</x:v>
       </x:c>
-      <x:c r="D54" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E54" s="34" t="n">
+      <x:c r="H54" s="34" t="n">
         <x:v>89797.07000000004</x:v>
       </x:c>
-      <x:c r="F54" s="26" t="n">
+      <x:c r="I54" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G54" s="26" t="n">
+      <x:c r="J54" s="26" t="n">
         <x:v>1250</x:v>
       </x:c>
     </x:row>
@@ -3593,18 +4612,27 @@
         <x:v>1857</x:v>
       </x:c>
       <x:c r="C55" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D55" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E55" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F55" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G55" s="34" t="n">
         <x:v>78380.04000000001</x:v>
       </x:c>
-      <x:c r="D55" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E55" s="34" t="n">
+      <x:c r="H55" s="34" t="n">
         <x:v>79925.75000000003</x:v>
       </x:c>
-      <x:c r="F55" s="26" t="n">
+      <x:c r="I55" s="26" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G55" s="26" t="n">
+      <x:c r="J55" s="26" t="n">
         <x:v>1044</x:v>
       </x:c>
     </x:row>
@@ -3616,18 +4644,27 @@
         <x:v>2504</x:v>
       </x:c>
       <x:c r="C56" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D56" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E56" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F56" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G56" s="34" t="n">
         <x:v>86151.58</x:v>
       </x:c>
-      <x:c r="D56" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E56" s="34" t="n">
+      <x:c r="H56" s="34" t="n">
         <x:v>87443.43000000002</x:v>
       </x:c>
-      <x:c r="F56" s="26" t="n">
+      <x:c r="I56" s="26" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G56" s="26" t="n">
+      <x:c r="J56" s="26" t="n">
         <x:v>1494</x:v>
       </x:c>
     </x:row>
@@ -3639,18 +4676,27 @@
         <x:v>2709</x:v>
       </x:c>
       <x:c r="C57" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D57" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E57" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F57" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G57" s="34" t="n">
         <x:v>65928.73999999999</x:v>
       </x:c>
-      <x:c r="D57" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E57" s="34" t="n">
+      <x:c r="H57" s="34" t="n">
         <x:v>66757.13999999998</x:v>
       </x:c>
-      <x:c r="F57" s="26" t="n">
+      <x:c r="I57" s="26" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G57" s="26" t="n">
+      <x:c r="J57" s="26" t="n">
         <x:v>1603</x:v>
       </x:c>
     </x:row>
@@ -3662,18 +4708,27 @@
         <x:v>2768</x:v>
       </x:c>
       <x:c r="C58" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D58" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E58" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F58" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G58" s="34" t="n">
         <x:v>89537.56999999995</x:v>
       </x:c>
-      <x:c r="D58" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E58" s="34" t="n">
+      <x:c r="H58" s="34" t="n">
         <x:v>91159.36999999995</x:v>
       </x:c>
-      <x:c r="F58" s="26" t="n">
+      <x:c r="I58" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G58" s="26" t="n">
+      <x:c r="J58" s="26" t="n">
         <x:v>1563</x:v>
       </x:c>
     </x:row>
@@ -3685,18 +4740,27 @@
         <x:v>2316</x:v>
       </x:c>
       <x:c r="C59" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D59" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E59" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F59" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G59" s="34" t="n">
         <x:v>71206.81000000001</x:v>
       </x:c>
-      <x:c r="D59" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E59" s="34" t="n">
+      <x:c r="H59" s="34" t="n">
         <x:v>72207.87000000004</x:v>
       </x:c>
-      <x:c r="F59" s="26" t="n">
+      <x:c r="I59" s="26" t="n">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G59" s="26" t="n">
+      <x:c r="J59" s="26" t="n">
         <x:v>1233</x:v>
       </x:c>
     </x:row>
@@ -3708,18 +4772,27 @@
         <x:v>3055</x:v>
       </x:c>
       <x:c r="C60" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D60" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E60" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F60" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G60" s="34" t="n">
         <x:v>84901.87000000007</x:v>
       </x:c>
-      <x:c r="D60" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E60" s="34" t="n">
+      <x:c r="H60" s="34" t="n">
         <x:v>85838.87000000008</x:v>
       </x:c>
-      <x:c r="F60" s="26" t="n">
+      <x:c r="I60" s="26" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G60" s="26" t="n">
+      <x:c r="J60" s="26" t="n">
         <x:v>1800</x:v>
       </x:c>
     </x:row>
@@ -3731,18 +4804,27 @@
         <x:v>2516</x:v>
       </x:c>
       <x:c r="C61" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D61" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E61" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F61" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G61" s="34" t="n">
         <x:v>78674.64000000001</x:v>
       </x:c>
-      <x:c r="D61" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E61" s="34" t="n">
+      <x:c r="H61" s="34" t="n">
         <x:v>79640.81000000004</x:v>
       </x:c>
-      <x:c r="F61" s="26" t="n">
+      <x:c r="I61" s="26" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G61" s="26" t="n">
+      <x:c r="J61" s="26" t="n">
         <x:v>1450</x:v>
       </x:c>
     </x:row>
@@ -3754,18 +4836,27 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="C62" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D62" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E62" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F62" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G62" s="34" t="n">
         <x:v>73960.40999999997</x:v>
       </x:c>
-      <x:c r="D62" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E62" s="34" t="n">
+      <x:c r="H62" s="34" t="n">
         <x:v>74972.15999999999</x:v>
       </x:c>
-      <x:c r="F62" s="26" t="n">
+      <x:c r="I62" s="26" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G62" s="26" t="n">
+      <x:c r="J62" s="26" t="n">
         <x:v>1134</x:v>
       </x:c>
     </x:row>
@@ -3777,18 +4868,27 @@
         <x:v>2889</x:v>
       </x:c>
       <x:c r="C63" s="34" t="n">
-        <x:v>70470.71000000004</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D63" s="34" t="n">
         <x:v>500</x:v>
       </x:c>
       <x:c r="E63" s="34" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="F63" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G63" s="34" t="n">
+        <x:v>70470.71000000004</x:v>
+      </x:c>
+      <x:c r="H63" s="34" t="n">
         <x:v>70568.71000000004</x:v>
       </x:c>
-      <x:c r="F63" s="26" t="n">
+      <x:c r="I63" s="26" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G63" s="26" t="n">
+      <x:c r="J63" s="26" t="n">
         <x:v>1667</x:v>
       </x:c>
     </x:row>
@@ -3800,18 +4900,27 @@
         <x:v>2961</x:v>
       </x:c>
       <x:c r="C64" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D64" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E64" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F64" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G64" s="34" t="n">
         <x:v>62861.060000000005</x:v>
       </x:c>
-      <x:c r="D64" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E64" s="34" t="n">
+      <x:c r="H64" s="34" t="n">
         <x:v>63607.02</x:v>
       </x:c>
-      <x:c r="F64" s="26" t="n">
+      <x:c r="I64" s="26" t="n">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G64" s="26" t="n">
+      <x:c r="J64" s="26" t="n">
         <x:v>1573</x:v>
       </x:c>
     </x:row>
@@ -3823,18 +4932,27 @@
         <x:v>2446</x:v>
       </x:c>
       <x:c r="C65" s="34" t="n">
-        <x:v>63266.77000000003</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D65" s="34" t="n">
         <x:v>825</x:v>
       </x:c>
       <x:c r="E65" s="34" t="n">
+        <x:v>825</x:v>
+      </x:c>
+      <x:c r="F65" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G65" s="34" t="n">
+        <x:v>63266.77000000003</x:v>
+      </x:c>
+      <x:c r="H65" s="34" t="n">
         <x:v>63115.02000000003</x:v>
       </x:c>
-      <x:c r="F65" s="26" t="n">
+      <x:c r="I65" s="26" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G65" s="26" t="n">
+      <x:c r="J65" s="26" t="n">
         <x:v>1335</x:v>
       </x:c>
     </x:row>
@@ -3846,18 +4964,27 @@
         <x:v>2027</x:v>
       </x:c>
       <x:c r="C66" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D66" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E66" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F66" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G66" s="34" t="n">
         <x:v>73911.30000000002</x:v>
       </x:c>
-      <x:c r="D66" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E66" s="34" t="n">
+      <x:c r="H66" s="34" t="n">
         <x:v>74922.34</x:v>
       </x:c>
-      <x:c r="F66" s="26" t="n">
+      <x:c r="I66" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G66" s="26" t="n">
+      <x:c r="J66" s="26" t="n">
         <x:v>1052</x:v>
       </x:c>
     </x:row>
@@ -3869,18 +4996,27 @@
         <x:v>1667</x:v>
       </x:c>
       <x:c r="C67" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D67" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E67" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F67" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G67" s="34" t="n">
         <x:v>77344.0599999999</x:v>
       </x:c>
-      <x:c r="D67" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E67" s="34" t="n">
+      <x:c r="H67" s="34" t="n">
         <x:v>78594.70999999988</x:v>
       </x:c>
-      <x:c r="F67" s="26" t="n">
+      <x:c r="I67" s="26" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G67" s="26" t="n">
+      <x:c r="J67" s="26" t="n">
         <x:v>757</x:v>
       </x:c>
     </x:row>
@@ -3892,18 +5028,27 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="C68" s="34" t="n">
-        <x:v>61502.85000000002</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D68" s="34" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E68" s="34" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F68" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G68" s="34" t="n">
+        <x:v>61502.85000000002</x:v>
+      </x:c>
+      <x:c r="H68" s="34" t="n">
         <x:v>61865.85000000002</x:v>
       </x:c>
-      <x:c r="F68" s="26" t="n">
+      <x:c r="I68" s="26" t="n">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="G68" s="26" t="n">
+      <x:c r="J68" s="26" t="n">
         <x:v>1139</x:v>
       </x:c>
     </x:row>
@@ -3915,478 +5060,2011 @@
         <x:v>2128</x:v>
       </x:c>
       <x:c r="C69" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D69" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E69" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F69" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G69" s="34" t="n">
         <x:v>68233.31999999996</x:v>
       </x:c>
-      <x:c r="D69" s="34" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E69" s="34" t="n">
+      <x:c r="H69" s="34" t="n">
         <x:v>68707.31999999996</x:v>
       </x:c>
-      <x:c r="F69" s="26" t="n">
+      <x:c r="I69" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G69" s="26" t="n">
+      <x:c r="J69" s="26" t="n">
         <x:v>1076</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="26" t="str">
-        <x:v>2025-01</x:v>
+        <x:v>2019-01</x:v>
       </x:c>
       <x:c r="B70" s="35" t="n">
-        <x:v>1390</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="C70" s="34" t="n">
-        <x:v>100043.95999999993</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D70" s="34" t="n">
-        <x:v>70591.29000000002</x:v>
+        <x:v>6938.15</x:v>
       </x:c>
       <x:c r="E70" s="34" t="n">
-        <x:v>34009.259999999995</x:v>
-      </x:c>
-      <x:c r="F70" s="26" t="n">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="G70" s="26" t="n">
-        <x:v>817</x:v>
+        <x:v>7187.61</x:v>
+      </x:c>
+      <x:c r="F70" s="34" t="n">
+        <x:v>249.45999999999998</x:v>
+      </x:c>
+      <x:c r="G70" s="34" t="n">
+        <x:v>95468.83999999992</x:v>
+      </x:c>
+      <x:c r="H70" s="34" t="n">
+        <x:v>89580.74999999997</x:v>
+      </x:c>
+      <x:c r="I70" s="26" t="n">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="J70" s="26" t="n">
+        <x:v>1379</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="26" t="str">
-        <x:v>2025-02</x:v>
+        <x:v>2019-02</x:v>
       </x:c>
       <x:c r="B71" s="35" t="n">
-        <x:v>1340</x:v>
+        <x:v>2126</x:v>
       </x:c>
       <x:c r="C71" s="34" t="n">
-        <x:v>105039.38999999993</x:v>
+        <x:v>29303.59</x:v>
       </x:c>
       <x:c r="D71" s="34" t="n">
-        <x:v>72370.19000000005</x:v>
+        <x:v>34741.24000000001</x:v>
       </x:c>
       <x:c r="E71" s="34" t="n">
-        <x:v>36972.74</x:v>
-      </x:c>
-      <x:c r="F71" s="26" t="n">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G71" s="26" t="n">
-        <x:v>854</x:v>
+        <x:v>36103.66000000001</x:v>
+      </x:c>
+      <x:c r="F71" s="34" t="n">
+        <x:v>1362.4200000000003</x:v>
+      </x:c>
+      <x:c r="G71" s="34" t="n">
+        <x:v>81965.6100000001</x:v>
+      </x:c>
+      <x:c r="H71" s="34" t="n">
+        <x:v>48072.549999999996</x:v>
+      </x:c>
+      <x:c r="I71" s="26" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="J71" s="26" t="n">
+        <x:v>1171</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="26" t="str">
-        <x:v>2025-03</x:v>
+        <x:v>2019-03</x:v>
       </x:c>
       <x:c r="B72" s="35" t="n">
-        <x:v>1746</x:v>
+        <x:v>2771</x:v>
       </x:c>
       <x:c r="C72" s="34" t="n">
-        <x:v>100210.16999999991</x:v>
+        <x:v>59336.62</x:v>
       </x:c>
       <x:c r="D72" s="34" t="n">
-        <x:v>74212.62000000002</x:v>
+        <x:v>60417.000000000065</x:v>
       </x:c>
       <x:c r="E72" s="34" t="n">
-        <x:v>30890.780000000002</x:v>
-      </x:c>
-      <x:c r="F72" s="26" t="n">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G72" s="26" t="n">
-        <x:v>1247</x:v>
+        <x:v>63933.17000000005</x:v>
+      </x:c>
+      <x:c r="F72" s="34" t="n">
+        <x:v>3516.1699999999996</x:v>
+      </x:c>
+      <x:c r="G72" s="34" t="n">
+        <x:v>92993.32000000007</x:v>
+      </x:c>
+      <x:c r="H72" s="34" t="n">
+        <x:v>33751.22000000001</x:v>
+      </x:c>
+      <x:c r="I72" s="26" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J72" s="26" t="n">
+        <x:v>1494</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="26" t="str">
-        <x:v>2025-04</x:v>
+        <x:v>2019-04</x:v>
       </x:c>
       <x:c r="B73" s="35" t="n">
-        <x:v>1261</x:v>
+        <x:v>1966</x:v>
       </x:c>
       <x:c r="C73" s="34" t="n">
-        <x:v>82392.03</x:v>
+        <x:v>37093.03</x:v>
       </x:c>
       <x:c r="D73" s="34" t="n">
-        <x:v>66855.51000000004</x:v>
+        <x:v>43047.28000000007</x:v>
       </x:c>
       <x:c r="E73" s="34" t="n">
-        <x:v>23890.599999999995</x:v>
-      </x:c>
-      <x:c r="F73" s="26" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G73" s="26" t="n">
-        <x:v>922</x:v>
+        <x:v>45065.91000000002</x:v>
+      </x:c>
+      <x:c r="F73" s="34" t="n">
+        <x:v>2018.6300000000006</x:v>
+      </x:c>
+      <x:c r="G73" s="34" t="n">
+        <x:v>62311.400000000096</x:v>
+      </x:c>
+      <x:c r="H73" s="34" t="n">
+        <x:v>19614.390000000003</x:v>
+      </x:c>
+      <x:c r="I73" s="26" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J73" s="26" t="n">
+        <x:v>1045</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="26" t="str">
-        <x:v>2025-05</x:v>
+        <x:v>2019-05</x:v>
       </x:c>
       <x:c r="B74" s="35" t="n">
-        <x:v>1328</x:v>
+        <x:v>1828</x:v>
       </x:c>
       <x:c r="C74" s="34" t="n">
-        <x:v>95579.69999999998</x:v>
+        <x:v>36639.27</x:v>
       </x:c>
       <x:c r="D74" s="34" t="n">
-        <x:v>68913.3400000001</x:v>
+        <x:v>39041.10999999999</x:v>
       </x:c>
       <x:c r="E74" s="34" t="n">
-        <x:v>31153.629999999997</x:v>
-      </x:c>
-      <x:c r="F74" s="26" t="n">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="G74" s="26" t="n">
-        <x:v>829</x:v>
+        <x:v>41250.57</x:v>
+      </x:c>
+      <x:c r="F74" s="34" t="n">
+        <x:v>2209.4600000000005</x:v>
+      </x:c>
+      <x:c r="G74" s="34" t="n">
+        <x:v>55027.909999999996</x:v>
+      </x:c>
+      <x:c r="H74" s="34" t="n">
+        <x:v>16618.35</x:v>
+      </x:c>
+      <x:c r="I74" s="26" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J74" s="26" t="n">
+        <x:v>972</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="26" t="str">
-        <x:v>2025-06</x:v>
+        <x:v>2019-06</x:v>
       </x:c>
       <x:c r="B75" s="35" t="n">
-        <x:v>1555</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="C75" s="34" t="n">
-        <x:v>80711.41999999991</x:v>
+        <x:v>51453.51</x:v>
       </x:c>
       <x:c r="D75" s="34" t="n">
-        <x:v>57309.340000000084</x:v>
+        <x:v>42631.72000000002</x:v>
       </x:c>
       <x:c r="E75" s="34" t="n">
-        <x:v>26586.11999999999</x:v>
-      </x:c>
-      <x:c r="F75" s="26" t="n">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="G75" s="26" t="n">
-        <x:v>1091</x:v>
+        <x:v>46436.90000000001</x:v>
+      </x:c>
+      <x:c r="F75" s="34" t="n">
+        <x:v>3805.179999999996</x:v>
+      </x:c>
+      <x:c r="G75" s="34" t="n">
+        <x:v>58314.11000000007</x:v>
+      </x:c>
+      <x:c r="H75" s="34" t="n">
+        <x:v>16052.090000000002</x:v>
+      </x:c>
+      <x:c r="I75" s="26" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J75" s="26" t="n">
+        <x:v>1392</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="26" t="str">
-        <x:v>2025-07</x:v>
+        <x:v>2019-07</x:v>
       </x:c>
       <x:c r="B76" s="35" t="n">
-        <x:v>1534</x:v>
+        <x:v>2514</x:v>
       </x:c>
       <x:c r="C76" s="34" t="n">
-        <x:v>78359.51999999981</x:v>
+        <x:v>53820.3</x:v>
       </x:c>
       <x:c r="D76" s="34" t="n">
-        <x:v>63316.92000000007</x:v>
+        <x:v>48517.24999999993</x:v>
       </x:c>
       <x:c r="E76" s="34" t="n">
-        <x:v>18990.549999999992</x:v>
-      </x:c>
-      <x:c r="F76" s="26" t="n">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="G76" s="26" t="n">
-        <x:v>1027</x:v>
+        <x:v>52158.95999999995</x:v>
+      </x:c>
+      <x:c r="F76" s="34" t="n">
+        <x:v>3641.7100000000028</x:v>
+      </x:c>
+      <x:c r="G76" s="34" t="n">
+        <x:v>60577.85999999987</x:v>
+      </x:c>
+      <x:c r="H76" s="34" t="n">
+        <x:v>12958.509999999998</x:v>
+      </x:c>
+      <x:c r="I76" s="26" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J76" s="26" t="n">
+        <x:v>1422</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="26" t="str">
-        <x:v>2025-08</x:v>
+        <x:v>2019-08</x:v>
       </x:c>
       <x:c r="B77" s="35" t="n">
-        <x:v>1756</x:v>
+        <x:v>2068</x:v>
       </x:c>
       <x:c r="C77" s="34" t="n">
-        <x:v>87986.43999999994</x:v>
+        <x:v>40673.59</x:v>
       </x:c>
       <x:c r="D77" s="34" t="n">
-        <x:v>64088.150000000045</x:v>
+        <x:v>42641.13999999999</x:v>
       </x:c>
       <x:c r="E77" s="34" t="n">
-        <x:v>27595.49999999999</x:v>
-      </x:c>
-      <x:c r="F77" s="26" t="n">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="G77" s="26" t="n">
-        <x:v>1098</x:v>
+        <x:v>45569.72999999999</x:v>
+      </x:c>
+      <x:c r="F77" s="34" t="n">
+        <x:v>2928.590000000003</x:v>
+      </x:c>
+      <x:c r="G77" s="34" t="n">
+        <x:v>55850.99999999996</x:v>
+      </x:c>
+      <x:c r="H77" s="34" t="n">
+        <x:v>13963.810000000001</x:v>
+      </x:c>
+      <x:c r="I77" s="26" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J77" s="26" t="n">
+        <x:v>1073</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="26" t="str">
-        <x:v>2025-09</x:v>
+        <x:v>2019-09</x:v>
       </x:c>
       <x:c r="B78" s="35" t="n">
-        <x:v>1135</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="C78" s="34" t="n">
-        <x:v>104107.17999999993</x:v>
+        <x:v>42218.04</x:v>
       </x:c>
       <x:c r="D78" s="34" t="n">
-        <x:v>70536.09000000004</x:v>
+        <x:v>39577.89999999999</x:v>
       </x:c>
       <x:c r="E78" s="34" t="n">
-        <x:v>38085.810000000005</x:v>
-      </x:c>
-      <x:c r="F78" s="26" t="n">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="G78" s="26" t="n">
-        <x:v>683</x:v>
+        <x:v>41970.24</x:v>
+      </x:c>
+      <x:c r="F78" s="34" t="n">
+        <x:v>2392.340000000001</x:v>
+      </x:c>
+      <x:c r="G78" s="34" t="n">
+        <x:v>64847.169999999925</x:v>
+      </x:c>
+      <x:c r="H78" s="34" t="n">
+        <x:v>25839.27</x:v>
+      </x:c>
+      <x:c r="I78" s="26" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="J78" s="26" t="n">
+        <x:v>898</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="26" t="str">
-        <x:v>2025-10</x:v>
+        <x:v>2019-10</x:v>
       </x:c>
       <x:c r="B79" s="35" t="n">
-        <x:v>1451</x:v>
+        <x:v>1756</x:v>
       </x:c>
       <x:c r="C79" s="34" t="n">
-        <x:v>110215.05999999981</x:v>
+        <x:v>37782.11</x:v>
       </x:c>
       <x:c r="D79" s="34" t="n">
-        <x:v>78497.12000000001</x:v>
+        <x:v>49295.78999999994</x:v>
       </x:c>
       <x:c r="E79" s="34" t="n">
-        <x:v>37514.35999999999</x:v>
-      </x:c>
-      <x:c r="F79" s="26" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="G79" s="26" t="n">
-        <x:v>944</x:v>
+        <x:v>51547.32999999996</x:v>
+      </x:c>
+      <x:c r="F79" s="34" t="n">
+        <x:v>2251.5400000000004</x:v>
+      </x:c>
+      <x:c r="G79" s="34" t="n">
+        <x:v>73226.53999999988</x:v>
+      </x:c>
+      <x:c r="H79" s="34" t="n">
+        <x:v>24844.349999999995</x:v>
+      </x:c>
+      <x:c r="I79" s="26" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="J79" s="26" t="n">
+        <x:v>941</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="26" t="str">
-        <x:v>2025-11</x:v>
+        <x:v>2019-11</x:v>
       </x:c>
       <x:c r="B80" s="35" t="n">
-        <x:v>2001</x:v>
+        <x:v>2351</x:v>
       </x:c>
       <x:c r="C80" s="34" t="n">
-        <x:v>119581.76000000021</x:v>
+        <x:v>54892.13</x:v>
       </x:c>
       <x:c r="D80" s="34" t="n">
-        <x:v>89808.17</x:v>
+        <x:v>48554.34999999993</x:v>
       </x:c>
       <x:c r="E80" s="34" t="n">
-        <x:v>35829.27999999999</x:v>
-      </x:c>
-      <x:c r="F80" s="26" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G80" s="26" t="n">
-        <x:v>1419</x:v>
+        <x:v>51596.92999999997</x:v>
+      </x:c>
+      <x:c r="F80" s="34" t="n">
+        <x:v>3042.579999999999</x:v>
+      </x:c>
+      <x:c r="G80" s="34" t="n">
+        <x:v>70843.36999999991</x:v>
+      </x:c>
+      <x:c r="H80" s="34" t="n">
+        <x:v>23276.810000000005</x:v>
+      </x:c>
+      <x:c r="I80" s="26" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J80" s="26" t="n">
+        <x:v>1359</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="26" t="str">
-        <x:v>2025-12</x:v>
+        <x:v>2019-12</x:v>
       </x:c>
       <x:c r="B81" s="35" t="n">
-        <x:v>1395</x:v>
+        <x:v>1940</x:v>
       </x:c>
       <x:c r="C81" s="34" t="n">
-        <x:v>83350.15000000005</x:v>
+        <x:v>53225.62</x:v>
       </x:c>
       <x:c r="D81" s="34" t="n">
-        <x:v>63093.38999999999</x:v>
+        <x:v>50892.24999999993</x:v>
       </x:c>
       <x:c r="E81" s="34" t="n">
-        <x:v>23736.889999999996</x:v>
-      </x:c>
-      <x:c r="F81" s="26" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="G81" s="26" t="n">
-        <x:v>924</x:v>
+        <x:v>53515.20999999996</x:v>
+      </x:c>
+      <x:c r="F81" s="34" t="n">
+        <x:v>2622.9599999999996</x:v>
+      </x:c>
+      <x:c r="G81" s="34" t="n">
+        <x:v>65419.799999999836</x:v>
+      </x:c>
+      <x:c r="H81" s="34" t="n">
+        <x:v>15436.539999999992</x:v>
+      </x:c>
+      <x:c r="I81" s="26" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J81" s="26" t="n">
+        <x:v>1190</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="26" t="str">
-        <x:v>2026-01</x:v>
-      </x:c>
-      <x:c r="B82" s="35" t="n">
-        <x:v>1984</x:v>
-      </x:c>
+        <x:v>2020-01</x:v>
+      </x:c>
+      <x:c r="B82" s="35"/>
       <x:c r="C82" s="34" t="n">
-        <x:v>149100.38</x:v>
-      </x:c>
-      <x:c r="D82" s="34" t="n">
-        <x:v>102160.48000000013</x:v>
-      </x:c>
-      <x:c r="E82" s="34" t="n">
-        <x:v>54476.700000000055</x:v>
-      </x:c>
-      <x:c r="F82" s="26" t="n">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G82" s="26" t="n">
-        <x:v>1383</x:v>
-      </x:c>
+        <x:v>52243.19</x:v>
+      </x:c>
+      <x:c r="D82" s="34"/>
+      <x:c r="E82" s="34"/>
+      <x:c r="F82" s="34"/>
+      <x:c r="G82" s="34"/>
+      <x:c r="H82" s="34"/>
+      <x:c r="I82" s="26"/>
+      <x:c r="J82" s="26"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="26" t="str">
-        <x:v>2026-02</x:v>
-      </x:c>
-      <x:c r="B83" s="35" t="n">
-        <x:v>1419</x:v>
-      </x:c>
+        <x:v>2020-02</x:v>
+      </x:c>
+      <x:c r="B83" s="35"/>
       <x:c r="C83" s="34" t="n">
-        <x:v>138263.76000000013</x:v>
-      </x:c>
-      <x:c r="D83" s="34" t="n">
-        <x:v>93983.34999999993</x:v>
-      </x:c>
-      <x:c r="E83" s="34" t="n">
-        <x:v>49906.04000000006</x:v>
-      </x:c>
-      <x:c r="F83" s="26" t="n">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="G83" s="26" t="n">
-        <x:v>947</x:v>
-      </x:c>
+        <x:v>57234.17</x:v>
+      </x:c>
+      <x:c r="D83" s="34"/>
+      <x:c r="E83" s="34"/>
+      <x:c r="F83" s="34"/>
+      <x:c r="G83" s="34"/>
+      <x:c r="H83" s="34"/>
+      <x:c r="I83" s="26"/>
+      <x:c r="J83" s="26"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="26" t="str">
-        <x:v>2026-03</x:v>
-      </x:c>
-      <x:c r="B84" s="35" t="n">
-        <x:v>1560</x:v>
-      </x:c>
+        <x:v>2020-03</x:v>
+      </x:c>
+      <x:c r="B84" s="35"/>
       <x:c r="C84" s="34" t="n">
-        <x:v>102584.46000000022</x:v>
-      </x:c>
-      <x:c r="D84" s="34" t="n">
-        <x:v>77206.12999999999</x:v>
-      </x:c>
-      <x:c r="E84" s="34" t="n">
-        <x:v>30805.019999999982</x:v>
-      </x:c>
-      <x:c r="F84" s="26" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="G84" s="26" t="n">
-        <x:v>1090</x:v>
-      </x:c>
+        <x:v>19211.36</x:v>
+      </x:c>
+      <x:c r="D84" s="34"/>
+      <x:c r="E84" s="34"/>
+      <x:c r="F84" s="34"/>
+      <x:c r="G84" s="34"/>
+      <x:c r="H84" s="34"/>
+      <x:c r="I84" s="26"/>
+      <x:c r="J84" s="26"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="26" t="str">
-        <x:v>2026-04</x:v>
-      </x:c>
-      <x:c r="B85" s="35" t="n">
-        <x:v>1339</x:v>
-      </x:c>
+        <x:v>2020-04</x:v>
+      </x:c>
+      <x:c r="B85" s="35"/>
       <x:c r="C85" s="34" t="n">
-        <x:v>122029.22999999988</x:v>
-      </x:c>
-      <x:c r="D85" s="34" t="n">
-        <x:v>77013.54000000002</x:v>
-      </x:c>
-      <x:c r="E85" s="34" t="n">
-        <x:v>49566.15000000005</x:v>
-      </x:c>
-      <x:c r="F85" s="26" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="G85" s="26" t="n">
-        <x:v>883</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D85" s="34"/>
+      <x:c r="E85" s="34"/>
+      <x:c r="F85" s="34"/>
+      <x:c r="G85" s="34"/>
+      <x:c r="H85" s="34"/>
+      <x:c r="I85" s="26"/>
+      <x:c r="J85" s="26"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="26" t="str">
-        <x:v>2026-05</x:v>
-      </x:c>
-      <x:c r="B86" s="35" t="n">
-        <x:v>1744</x:v>
-      </x:c>
+        <x:v>2020-05</x:v>
+      </x:c>
+      <x:c r="B86" s="35"/>
       <x:c r="C86" s="34" t="n">
-        <x:v>102583.65999999997</x:v>
-      </x:c>
-      <x:c r="D86" s="34" t="n">
-        <x:v>74749.29999999999</x:v>
-      </x:c>
-      <x:c r="E86" s="34" t="n">
-        <x:v>32273.119999999988</x:v>
-      </x:c>
-      <x:c r="F86" s="26" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G86" s="26" t="n">
-        <x:v>1319</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D86" s="34"/>
+      <x:c r="E86" s="34"/>
+      <x:c r="F86" s="34"/>
+      <x:c r="G86" s="34"/>
+      <x:c r="H86" s="34"/>
+      <x:c r="I86" s="26"/>
+      <x:c r="J86" s="26"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="26" t="str">
-        <x:v>2026-06</x:v>
-      </x:c>
-      <x:c r="B87" s="35" t="n">
-        <x:v>1530</x:v>
-      </x:c>
+        <x:v>2020-06</x:v>
+      </x:c>
+      <x:c r="B87" s="35"/>
       <x:c r="C87" s="34" t="n">
-        <x:v>103851.23999999993</x:v>
-      </x:c>
-      <x:c r="D87" s="34" t="n">
-        <x:v>70398.12000000004</x:v>
-      </x:c>
-      <x:c r="E87" s="34" t="n">
-        <x:v>37944.56000000002</x:v>
-      </x:c>
-      <x:c r="F87" s="26" t="n">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G87" s="26" t="n">
-        <x:v>1065</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D87" s="34"/>
+      <x:c r="E87" s="34"/>
+      <x:c r="F87" s="34"/>
+      <x:c r="G87" s="34"/>
+      <x:c r="H87" s="34"/>
+      <x:c r="I87" s="26"/>
+      <x:c r="J87" s="26"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="26" t="str">
-        <x:v>2026-07</x:v>
-      </x:c>
-      <x:c r="B88" s="35" t="n">
-        <x:v>1983</x:v>
-      </x:c>
+        <x:v>2020-07</x:v>
+      </x:c>
+      <x:c r="B88" s="35"/>
       <x:c r="C88" s="34" t="n">
-        <x:v>106224.69999999998</x:v>
-      </x:c>
-      <x:c r="D88" s="34" t="n">
-        <x:v>70944.62999999999</x:v>
-      </x:c>
-      <x:c r="E88" s="34" t="n">
-        <x:v>39193.270000000004</x:v>
-      </x:c>
-      <x:c r="F88" s="26" t="n">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="G88" s="26" t="n">
-        <x:v>1395</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D88" s="34"/>
+      <x:c r="E88" s="34"/>
+      <x:c r="F88" s="34"/>
+      <x:c r="G88" s="34"/>
+      <x:c r="H88" s="34"/>
+      <x:c r="I88" s="26"/>
+      <x:c r="J88" s="26"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="26" t="str">
+        <x:v>2020-08</x:v>
+      </x:c>
+      <x:c r="B89" s="35"/>
+      <x:c r="C89" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D89" s="34"/>
+      <x:c r="E89" s="34"/>
+      <x:c r="F89" s="34"/>
+      <x:c r="G89" s="34"/>
+      <x:c r="H89" s="34"/>
+      <x:c r="I89" s="26"/>
+      <x:c r="J89" s="26"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="26" t="str">
+        <x:v>2020-09</x:v>
+      </x:c>
+      <x:c r="B90" s="35"/>
+      <x:c r="C90" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D90" s="34"/>
+      <x:c r="E90" s="34"/>
+      <x:c r="F90" s="34"/>
+      <x:c r="G90" s="34"/>
+      <x:c r="H90" s="34"/>
+      <x:c r="I90" s="26"/>
+      <x:c r="J90" s="26"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="26" t="str">
+        <x:v>2020-10</x:v>
+      </x:c>
+      <x:c r="B91" s="35"/>
+      <x:c r="C91" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D91" s="34"/>
+      <x:c r="E91" s="34"/>
+      <x:c r="F91" s="34"/>
+      <x:c r="G91" s="34"/>
+      <x:c r="H91" s="34"/>
+      <x:c r="I91" s="26"/>
+      <x:c r="J91" s="26"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="26" t="str">
+        <x:v>2020-11</x:v>
+      </x:c>
+      <x:c r="B92" s="35"/>
+      <x:c r="C92" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D92" s="34"/>
+      <x:c r="E92" s="34"/>
+      <x:c r="F92" s="34"/>
+      <x:c r="G92" s="34"/>
+      <x:c r="H92" s="34"/>
+      <x:c r="I92" s="26"/>
+      <x:c r="J92" s="26"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="26" t="str">
+        <x:v>2020-12</x:v>
+      </x:c>
+      <x:c r="B93" s="35"/>
+      <x:c r="C93" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D93" s="34"/>
+      <x:c r="E93" s="34"/>
+      <x:c r="F93" s="34"/>
+      <x:c r="G93" s="34"/>
+      <x:c r="H93" s="34"/>
+      <x:c r="I93" s="26"/>
+      <x:c r="J93" s="26"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="26" t="str">
+        <x:v>2021-01</x:v>
+      </x:c>
+      <x:c r="B94" s="35"/>
+      <x:c r="C94" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D94" s="34"/>
+      <x:c r="E94" s="34"/>
+      <x:c r="F94" s="34"/>
+      <x:c r="G94" s="34"/>
+      <x:c r="H94" s="34"/>
+      <x:c r="I94" s="26"/>
+      <x:c r="J94" s="26"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="26" t="str">
+        <x:v>2021-02</x:v>
+      </x:c>
+      <x:c r="B95" s="35"/>
+      <x:c r="C95" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D95" s="34"/>
+      <x:c r="E95" s="34"/>
+      <x:c r="F95" s="34"/>
+      <x:c r="G95" s="34"/>
+      <x:c r="H95" s="34"/>
+      <x:c r="I95" s="26"/>
+      <x:c r="J95" s="26"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="26" t="str">
+        <x:v>2021-03</x:v>
+      </x:c>
+      <x:c r="B96" s="35"/>
+      <x:c r="C96" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D96" s="34"/>
+      <x:c r="E96" s="34"/>
+      <x:c r="F96" s="34"/>
+      <x:c r="G96" s="34"/>
+      <x:c r="H96" s="34"/>
+      <x:c r="I96" s="26"/>
+      <x:c r="J96" s="26"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="26" t="str">
+        <x:v>2021-04</x:v>
+      </x:c>
+      <x:c r="B97" s="35"/>
+      <x:c r="C97" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D97" s="34"/>
+      <x:c r="E97" s="34"/>
+      <x:c r="F97" s="34"/>
+      <x:c r="G97" s="34"/>
+      <x:c r="H97" s="34"/>
+      <x:c r="I97" s="26"/>
+      <x:c r="J97" s="26"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="26" t="str">
+        <x:v>2021-05</x:v>
+      </x:c>
+      <x:c r="B98" s="35"/>
+      <x:c r="C98" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D98" s="34"/>
+      <x:c r="E98" s="34"/>
+      <x:c r="F98" s="34"/>
+      <x:c r="G98" s="34"/>
+      <x:c r="H98" s="34"/>
+      <x:c r="I98" s="26"/>
+      <x:c r="J98" s="26"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="26" t="str">
+        <x:v>2021-06</x:v>
+      </x:c>
+      <x:c r="B99" s="35"/>
+      <x:c r="C99" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D99" s="34"/>
+      <x:c r="E99" s="34"/>
+      <x:c r="F99" s="34"/>
+      <x:c r="G99" s="34"/>
+      <x:c r="H99" s="34"/>
+      <x:c r="I99" s="26"/>
+      <x:c r="J99" s="26"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="26" t="str">
+        <x:v>2021-07</x:v>
+      </x:c>
+      <x:c r="B100" s="35"/>
+      <x:c r="C100" s="34" t="n">
+        <x:v>27983.65</x:v>
+      </x:c>
+      <x:c r="D100" s="34"/>
+      <x:c r="E100" s="34"/>
+      <x:c r="F100" s="34"/>
+      <x:c r="G100" s="34"/>
+      <x:c r="H100" s="34"/>
+      <x:c r="I100" s="26"/>
+      <x:c r="J100" s="26"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="26" t="str">
+        <x:v>2021-08</x:v>
+      </x:c>
+      <x:c r="B101" s="35"/>
+      <x:c r="C101" s="34" t="n">
+        <x:v>39607.48</x:v>
+      </x:c>
+      <x:c r="D101" s="34"/>
+      <x:c r="E101" s="34"/>
+      <x:c r="F101" s="34"/>
+      <x:c r="G101" s="34"/>
+      <x:c r="H101" s="34"/>
+      <x:c r="I101" s="26"/>
+      <x:c r="J101" s="26"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="26" t="str">
+        <x:v>2021-09</x:v>
+      </x:c>
+      <x:c r="B102" s="35"/>
+      <x:c r="C102" s="34" t="n">
+        <x:v>43726.61</x:v>
+      </x:c>
+      <x:c r="D102" s="34"/>
+      <x:c r="E102" s="34"/>
+      <x:c r="F102" s="34"/>
+      <x:c r="G102" s="34"/>
+      <x:c r="H102" s="34"/>
+      <x:c r="I102" s="26"/>
+      <x:c r="J102" s="26"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="26" t="str">
+        <x:v>2021-10</x:v>
+      </x:c>
+      <x:c r="B103" s="35"/>
+      <x:c r="C103" s="34" t="n">
+        <x:v>42424.46</x:v>
+      </x:c>
+      <x:c r="D103" s="34"/>
+      <x:c r="E103" s="34"/>
+      <x:c r="F103" s="34"/>
+      <x:c r="G103" s="34"/>
+      <x:c r="H103" s="34"/>
+      <x:c r="I103" s="26"/>
+      <x:c r="J103" s="26"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="26" t="str">
+        <x:v>2021-11</x:v>
+      </x:c>
+      <x:c r="B104" s="35"/>
+      <x:c r="C104" s="34" t="n">
+        <x:v>52804.11</x:v>
+      </x:c>
+      <x:c r="D104" s="34"/>
+      <x:c r="E104" s="34"/>
+      <x:c r="F104" s="34"/>
+      <x:c r="G104" s="34"/>
+      <x:c r="H104" s="34"/>
+      <x:c r="I104" s="26"/>
+      <x:c r="J104" s="26"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="26" t="str">
+        <x:v>2021-12</x:v>
+      </x:c>
+      <x:c r="B105" s="35"/>
+      <x:c r="C105" s="34" t="n">
+        <x:v>46125.72</x:v>
+      </x:c>
+      <x:c r="D105" s="34"/>
+      <x:c r="E105" s="34"/>
+      <x:c r="F105" s="34"/>
+      <x:c r="G105" s="34"/>
+      <x:c r="H105" s="34"/>
+      <x:c r="I105" s="26"/>
+      <x:c r="J105" s="26"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="26" t="str">
+        <x:v>2022-01</x:v>
+      </x:c>
+      <x:c r="B106" s="35"/>
+      <x:c r="C106" s="34" t="n">
+        <x:v>38598.63</x:v>
+      </x:c>
+      <x:c r="D106" s="34"/>
+      <x:c r="E106" s="34"/>
+      <x:c r="F106" s="34"/>
+      <x:c r="G106" s="34"/>
+      <x:c r="H106" s="34"/>
+      <x:c r="I106" s="26"/>
+      <x:c r="J106" s="26"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="26" t="str">
+        <x:v>2022-02</x:v>
+      </x:c>
+      <x:c r="B107" s="35"/>
+      <x:c r="C107" s="34" t="n">
+        <x:v>44002.91</x:v>
+      </x:c>
+      <x:c r="D107" s="34"/>
+      <x:c r="E107" s="34"/>
+      <x:c r="F107" s="34"/>
+      <x:c r="G107" s="34"/>
+      <x:c r="H107" s="34"/>
+      <x:c r="I107" s="26"/>
+      <x:c r="J107" s="26"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="26" t="str">
+        <x:v>2022-03</x:v>
+      </x:c>
+      <x:c r="B108" s="35"/>
+      <x:c r="C108" s="34" t="n">
+        <x:v>45419.66</x:v>
+      </x:c>
+      <x:c r="D108" s="34"/>
+      <x:c r="E108" s="34"/>
+      <x:c r="F108" s="34"/>
+      <x:c r="G108" s="34"/>
+      <x:c r="H108" s="34"/>
+      <x:c r="I108" s="26"/>
+      <x:c r="J108" s="26"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="26" t="str">
+        <x:v>2022-04</x:v>
+      </x:c>
+      <x:c r="B109" s="35"/>
+      <x:c r="C109" s="34" t="n">
+        <x:v>57246.72</x:v>
+      </x:c>
+      <x:c r="D109" s="34"/>
+      <x:c r="E109" s="34"/>
+      <x:c r="F109" s="34"/>
+      <x:c r="G109" s="34"/>
+      <x:c r="H109" s="34"/>
+      <x:c r="I109" s="26"/>
+      <x:c r="J109" s="26"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="26" t="str">
+        <x:v>2022-05</x:v>
+      </x:c>
+      <x:c r="B110" s="35"/>
+      <x:c r="C110" s="34" t="n">
+        <x:v>55471.19</x:v>
+      </x:c>
+      <x:c r="D110" s="34"/>
+      <x:c r="E110" s="34"/>
+      <x:c r="F110" s="34"/>
+      <x:c r="G110" s="34"/>
+      <x:c r="H110" s="34"/>
+      <x:c r="I110" s="26"/>
+      <x:c r="J110" s="26"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="26" t="str">
+        <x:v>2022-06</x:v>
+      </x:c>
+      <x:c r="B111" s="35"/>
+      <x:c r="C111" s="34" t="n">
+        <x:v>48342.62</x:v>
+      </x:c>
+      <x:c r="D111" s="34"/>
+      <x:c r="E111" s="34"/>
+      <x:c r="F111" s="34"/>
+      <x:c r="G111" s="34"/>
+      <x:c r="H111" s="34"/>
+      <x:c r="I111" s="26"/>
+      <x:c r="J111" s="26"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="26" t="str">
+        <x:v>2022-07</x:v>
+      </x:c>
+      <x:c r="B112" s="35"/>
+      <x:c r="C112" s="34" t="n">
+        <x:v>50473.48</x:v>
+      </x:c>
+      <x:c r="D112" s="34"/>
+      <x:c r="E112" s="34"/>
+      <x:c r="F112" s="34"/>
+      <x:c r="G112" s="34"/>
+      <x:c r="H112" s="34"/>
+      <x:c r="I112" s="26"/>
+      <x:c r="J112" s="26"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="26" t="str">
+        <x:v>2022-08</x:v>
+      </x:c>
+      <x:c r="B113" s="35"/>
+      <x:c r="C113" s="34" t="n">
+        <x:v>46993.93</x:v>
+      </x:c>
+      <x:c r="D113" s="34"/>
+      <x:c r="E113" s="34"/>
+      <x:c r="F113" s="34"/>
+      <x:c r="G113" s="34"/>
+      <x:c r="H113" s="34"/>
+      <x:c r="I113" s="26"/>
+      <x:c r="J113" s="26"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="26" t="str">
+        <x:v>2022-09</x:v>
+      </x:c>
+      <x:c r="B114" s="35"/>
+      <x:c r="C114" s="34" t="n">
+        <x:v>48420.96</x:v>
+      </x:c>
+      <x:c r="D114" s="34"/>
+      <x:c r="E114" s="34"/>
+      <x:c r="F114" s="34"/>
+      <x:c r="G114" s="34"/>
+      <x:c r="H114" s="34"/>
+      <x:c r="I114" s="26"/>
+      <x:c r="J114" s="26"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="26" t="str">
+        <x:v>2022-10</x:v>
+      </x:c>
+      <x:c r="B115" s="35"/>
+      <x:c r="C115" s="34" t="n">
+        <x:v>44148.91</x:v>
+      </x:c>
+      <x:c r="D115" s="34"/>
+      <x:c r="E115" s="34"/>
+      <x:c r="F115" s="34"/>
+      <x:c r="G115" s="34"/>
+      <x:c r="H115" s="34"/>
+      <x:c r="I115" s="26"/>
+      <x:c r="J115" s="26"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="26" t="str">
+        <x:v>2022-11</x:v>
+      </x:c>
+      <x:c r="B116" s="35"/>
+      <x:c r="C116" s="34" t="n">
+        <x:v>38502.71</x:v>
+      </x:c>
+      <x:c r="D116" s="34"/>
+      <x:c r="E116" s="34"/>
+      <x:c r="F116" s="34"/>
+      <x:c r="G116" s="34"/>
+      <x:c r="H116" s="34"/>
+      <x:c r="I116" s="26"/>
+      <x:c r="J116" s="26"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="26" t="str">
+        <x:v>2022-12</x:v>
+      </x:c>
+      <x:c r="B117" s="35"/>
+      <x:c r="C117" s="34" t="n">
+        <x:v>57061.19</x:v>
+      </x:c>
+      <x:c r="D117" s="34"/>
+      <x:c r="E117" s="34"/>
+      <x:c r="F117" s="34"/>
+      <x:c r="G117" s="34"/>
+      <x:c r="H117" s="34"/>
+      <x:c r="I117" s="26"/>
+      <x:c r="J117" s="26"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="26" t="str">
+        <x:v>2023-01</x:v>
+      </x:c>
+      <x:c r="B118" s="35"/>
+      <x:c r="C118" s="34" t="n">
+        <x:v>65471.06</x:v>
+      </x:c>
+      <x:c r="D118" s="34"/>
+      <x:c r="E118" s="34"/>
+      <x:c r="F118" s="34"/>
+      <x:c r="G118" s="34"/>
+      <x:c r="H118" s="34"/>
+      <x:c r="I118" s="26"/>
+      <x:c r="J118" s="26"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="26" t="str">
+        <x:v>2023-02</x:v>
+      </x:c>
+      <x:c r="B119" s="35"/>
+      <x:c r="C119" s="34" t="n">
+        <x:v>49450.61</x:v>
+      </x:c>
+      <x:c r="D119" s="34"/>
+      <x:c r="E119" s="34"/>
+      <x:c r="F119" s="34"/>
+      <x:c r="G119" s="34"/>
+      <x:c r="H119" s="34"/>
+      <x:c r="I119" s="26"/>
+      <x:c r="J119" s="26"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="26" t="str">
+        <x:v>2023-03</x:v>
+      </x:c>
+      <x:c r="B120" s="35"/>
+      <x:c r="C120" s="34" t="n">
+        <x:v>59382.4</x:v>
+      </x:c>
+      <x:c r="D120" s="34"/>
+      <x:c r="E120" s="34"/>
+      <x:c r="F120" s="34"/>
+      <x:c r="G120" s="34"/>
+      <x:c r="H120" s="34"/>
+      <x:c r="I120" s="26"/>
+      <x:c r="J120" s="26"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="26" t="str">
+        <x:v>2023-04</x:v>
+      </x:c>
+      <x:c r="B121" s="35"/>
+      <x:c r="C121" s="34" t="n">
+        <x:v>52384.65</x:v>
+      </x:c>
+      <x:c r="D121" s="34"/>
+      <x:c r="E121" s="34"/>
+      <x:c r="F121" s="34"/>
+      <x:c r="G121" s="34"/>
+      <x:c r="H121" s="34"/>
+      <x:c r="I121" s="26"/>
+      <x:c r="J121" s="26"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="26" t="str">
+        <x:v>2023-05</x:v>
+      </x:c>
+      <x:c r="B122" s="35"/>
+      <x:c r="C122" s="34" t="n">
+        <x:v>47233.95</x:v>
+      </x:c>
+      <x:c r="D122" s="34"/>
+      <x:c r="E122" s="34"/>
+      <x:c r="F122" s="34"/>
+      <x:c r="G122" s="34"/>
+      <x:c r="H122" s="34"/>
+      <x:c r="I122" s="26"/>
+      <x:c r="J122" s="26"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="26" t="str">
+        <x:v>2023-06</x:v>
+      </x:c>
+      <x:c r="B123" s="35"/>
+      <x:c r="C123" s="34" t="n">
+        <x:v>46617.07</x:v>
+      </x:c>
+      <x:c r="D123" s="34"/>
+      <x:c r="E123" s="34"/>
+      <x:c r="F123" s="34"/>
+      <x:c r="G123" s="34"/>
+      <x:c r="H123" s="34"/>
+      <x:c r="I123" s="26"/>
+      <x:c r="J123" s="26"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="26" t="str">
+        <x:v>2023-07</x:v>
+      </x:c>
+      <x:c r="B124" s="35"/>
+      <x:c r="C124" s="34" t="n">
+        <x:v>42925.8</x:v>
+      </x:c>
+      <x:c r="D124" s="34"/>
+      <x:c r="E124" s="34"/>
+      <x:c r="F124" s="34"/>
+      <x:c r="G124" s="34"/>
+      <x:c r="H124" s="34"/>
+      <x:c r="I124" s="26"/>
+      <x:c r="J124" s="26"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="26" t="str">
+        <x:v>2023-08</x:v>
+      </x:c>
+      <x:c r="B125" s="35"/>
+      <x:c r="C125" s="34" t="n">
+        <x:v>48134.28</x:v>
+      </x:c>
+      <x:c r="D125" s="34"/>
+      <x:c r="E125" s="34"/>
+      <x:c r="F125" s="34"/>
+      <x:c r="G125" s="34"/>
+      <x:c r="H125" s="34"/>
+      <x:c r="I125" s="26"/>
+      <x:c r="J125" s="26"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="26" t="str">
+        <x:v>2023-09</x:v>
+      </x:c>
+      <x:c r="B126" s="35"/>
+      <x:c r="C126" s="34" t="n">
+        <x:v>45644.01</x:v>
+      </x:c>
+      <x:c r="D126" s="34"/>
+      <x:c r="E126" s="34"/>
+      <x:c r="F126" s="34"/>
+      <x:c r="G126" s="34"/>
+      <x:c r="H126" s="34"/>
+      <x:c r="I126" s="26"/>
+      <x:c r="J126" s="26"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="26" t="str">
+        <x:v>2023-10</x:v>
+      </x:c>
+      <x:c r="B127" s="35"/>
+      <x:c r="C127" s="34" t="n">
+        <x:v>39293.39</x:v>
+      </x:c>
+      <x:c r="D127" s="34"/>
+      <x:c r="E127" s="34"/>
+      <x:c r="F127" s="34"/>
+      <x:c r="G127" s="34"/>
+      <x:c r="H127" s="34"/>
+      <x:c r="I127" s="26"/>
+      <x:c r="J127" s="26"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="26" t="str">
+        <x:v>2023-11</x:v>
+      </x:c>
+      <x:c r="B128" s="35"/>
+      <x:c r="C128" s="34" t="n">
+        <x:v>43559.7</x:v>
+      </x:c>
+      <x:c r="D128" s="34"/>
+      <x:c r="E128" s="34"/>
+      <x:c r="F128" s="34"/>
+      <x:c r="G128" s="34"/>
+      <x:c r="H128" s="34"/>
+      <x:c r="I128" s="26"/>
+      <x:c r="J128" s="26"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="26" t="str">
+        <x:v>2023-12</x:v>
+      </x:c>
+      <x:c r="B129" s="35"/>
+      <x:c r="C129" s="34" t="n">
+        <x:v>53937.06</x:v>
+      </x:c>
+      <x:c r="D129" s="34"/>
+      <x:c r="E129" s="34"/>
+      <x:c r="F129" s="34"/>
+      <x:c r="G129" s="34"/>
+      <x:c r="H129" s="34"/>
+      <x:c r="I129" s="26"/>
+      <x:c r="J129" s="26"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="26" t="str">
+        <x:v>2024-01</x:v>
+      </x:c>
+      <x:c r="B130" s="35"/>
+      <x:c r="C130" s="34" t="n">
+        <x:v>45101.55</x:v>
+      </x:c>
+      <x:c r="D130" s="34"/>
+      <x:c r="E130" s="34"/>
+      <x:c r="F130" s="34"/>
+      <x:c r="G130" s="34"/>
+      <x:c r="H130" s="34"/>
+      <x:c r="I130" s="26"/>
+      <x:c r="J130" s="26"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="26" t="str">
+        <x:v>2024-02</x:v>
+      </x:c>
+      <x:c r="B131" s="35"/>
+      <x:c r="C131" s="34" t="n">
+        <x:v>37841.7</x:v>
+      </x:c>
+      <x:c r="D131" s="34"/>
+      <x:c r="E131" s="34"/>
+      <x:c r="F131" s="34"/>
+      <x:c r="G131" s="34"/>
+      <x:c r="H131" s="34"/>
+      <x:c r="I131" s="26"/>
+      <x:c r="J131" s="26"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="26" t="str">
+        <x:v>2024-03</x:v>
+      </x:c>
+      <x:c r="B132" s="35"/>
+      <x:c r="C132" s="34" t="n">
+        <x:v>54103.46</x:v>
+      </x:c>
+      <x:c r="D132" s="34"/>
+      <x:c r="E132" s="34"/>
+      <x:c r="F132" s="34"/>
+      <x:c r="G132" s="34"/>
+      <x:c r="H132" s="34"/>
+      <x:c r="I132" s="26"/>
+      <x:c r="J132" s="26"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="26" t="str">
+        <x:v>2024-04</x:v>
+      </x:c>
+      <x:c r="B133" s="35"/>
+      <x:c r="C133" s="34" t="n">
+        <x:v>52305.56</x:v>
+      </x:c>
+      <x:c r="D133" s="34"/>
+      <x:c r="E133" s="34"/>
+      <x:c r="F133" s="34"/>
+      <x:c r="G133" s="34"/>
+      <x:c r="H133" s="34"/>
+      <x:c r="I133" s="26"/>
+      <x:c r="J133" s="26"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="26" t="str">
+        <x:v>2024-05</x:v>
+      </x:c>
+      <x:c r="B134" s="35"/>
+      <x:c r="C134" s="34" t="n">
+        <x:v>35087.16</x:v>
+      </x:c>
+      <x:c r="D134" s="34"/>
+      <x:c r="E134" s="34"/>
+      <x:c r="F134" s="34"/>
+      <x:c r="G134" s="34"/>
+      <x:c r="H134" s="34"/>
+      <x:c r="I134" s="26"/>
+      <x:c r="J134" s="26"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="26" t="str">
+        <x:v>2024-06</x:v>
+      </x:c>
+      <x:c r="B135" s="35"/>
+      <x:c r="C135" s="34" t="n">
+        <x:v>50304.99</x:v>
+      </x:c>
+      <x:c r="D135" s="34"/>
+      <x:c r="E135" s="34"/>
+      <x:c r="F135" s="34"/>
+      <x:c r="G135" s="34"/>
+      <x:c r="H135" s="34"/>
+      <x:c r="I135" s="26"/>
+      <x:c r="J135" s="26"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="26" t="str">
+        <x:v>2024-07</x:v>
+      </x:c>
+      <x:c r="B136" s="35"/>
+      <x:c r="C136" s="34" t="n">
+        <x:v>45182.45</x:v>
+      </x:c>
+      <x:c r="D136" s="34"/>
+      <x:c r="E136" s="34"/>
+      <x:c r="F136" s="34"/>
+      <x:c r="G136" s="34"/>
+      <x:c r="H136" s="34"/>
+      <x:c r="I136" s="26"/>
+      <x:c r="J136" s="26"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="26" t="str">
+        <x:v>2024-08</x:v>
+      </x:c>
+      <x:c r="B137" s="35"/>
+      <x:c r="C137" s="34" t="n">
+        <x:v>47744.9</x:v>
+      </x:c>
+      <x:c r="D137" s="34"/>
+      <x:c r="E137" s="34"/>
+      <x:c r="F137" s="34"/>
+      <x:c r="G137" s="34"/>
+      <x:c r="H137" s="34"/>
+      <x:c r="I137" s="26"/>
+      <x:c r="J137" s="26"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="26" t="str">
+        <x:v>2024-09</x:v>
+      </x:c>
+      <x:c r="B138" s="35"/>
+      <x:c r="C138" s="34" t="n">
+        <x:v>49822.32</x:v>
+      </x:c>
+      <x:c r="D138" s="34"/>
+      <x:c r="E138" s="34"/>
+      <x:c r="F138" s="34"/>
+      <x:c r="G138" s="34"/>
+      <x:c r="H138" s="34"/>
+      <x:c r="I138" s="26"/>
+      <x:c r="J138" s="26"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="26" t="str">
+        <x:v>2024-10</x:v>
+      </x:c>
+      <x:c r="B139" s="35"/>
+      <x:c r="C139" s="34" t="n">
+        <x:v>39943.64</x:v>
+      </x:c>
+      <x:c r="D139" s="34"/>
+      <x:c r="E139" s="34"/>
+      <x:c r="F139" s="34"/>
+      <x:c r="G139" s="34"/>
+      <x:c r="H139" s="34"/>
+      <x:c r="I139" s="26"/>
+      <x:c r="J139" s="26"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="26" t="str">
+        <x:v>2024-11</x:v>
+      </x:c>
+      <x:c r="B140" s="35"/>
+      <x:c r="C140" s="34" t="n">
+        <x:v>69410.62</x:v>
+      </x:c>
+      <x:c r="D140" s="34"/>
+      <x:c r="E140" s="34"/>
+      <x:c r="F140" s="34"/>
+      <x:c r="G140" s="34"/>
+      <x:c r="H140" s="34"/>
+      <x:c r="I140" s="26"/>
+      <x:c r="J140" s="26"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="26" t="str">
+        <x:v>2024-12</x:v>
+      </x:c>
+      <x:c r="B141" s="35"/>
+      <x:c r="C141" s="34" t="n">
+        <x:v>53803.11</x:v>
+      </x:c>
+      <x:c r="D141" s="34"/>
+      <x:c r="E141" s="34"/>
+      <x:c r="F141" s="34"/>
+      <x:c r="G141" s="34"/>
+      <x:c r="H141" s="34"/>
+      <x:c r="I141" s="26"/>
+      <x:c r="J141" s="26"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="26" t="str">
+        <x:v>2025-01</x:v>
+      </x:c>
+      <x:c r="B142" s="35" t="n">
+        <x:v>1390</x:v>
+      </x:c>
+      <x:c r="C142" s="34" t="n">
+        <x:v>58737.16</x:v>
+      </x:c>
+      <x:c r="D142" s="34" t="n">
+        <x:v>69120.66000000003</x:v>
+      </x:c>
+      <x:c r="E142" s="34" t="n">
+        <x:v>70591.29000000002</x:v>
+      </x:c>
+      <x:c r="F142" s="34" t="n">
+        <x:v>1470.6299999999997</x:v>
+      </x:c>
+      <x:c r="G142" s="34" t="n">
+        <x:v>100043.95999999993</x:v>
+      </x:c>
+      <x:c r="H142" s="34" t="n">
+        <x:v>34009.259999999995</x:v>
+      </x:c>
+      <x:c r="I142" s="26" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J142" s="26" t="n">
+        <x:v>817</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="26" t="str">
+        <x:v>2025-02</x:v>
+      </x:c>
+      <x:c r="B143" s="35" t="n">
+        <x:v>1340</x:v>
+      </x:c>
+      <x:c r="C143" s="34" t="n">
+        <x:v>60012.92</x:v>
+      </x:c>
+      <x:c r="D143" s="34" t="n">
+        <x:v>70650.39000000013</x:v>
+      </x:c>
+      <x:c r="E143" s="34" t="n">
+        <x:v>72370.19000000005</x:v>
+      </x:c>
+      <x:c r="F143" s="34" t="n">
+        <x:v>1719.8000000000004</x:v>
+      </x:c>
+      <x:c r="G143" s="34" t="n">
+        <x:v>105039.38999999993</x:v>
+      </x:c>
+      <x:c r="H143" s="34" t="n">
+        <x:v>36972.74</x:v>
+      </x:c>
+      <x:c r="I143" s="26" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J143" s="26" t="n">
+        <x:v>854</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="26" t="str">
+        <x:v>2025-03</x:v>
+      </x:c>
+      <x:c r="B144" s="35" t="n">
+        <x:v>1746</x:v>
+      </x:c>
+      <x:c r="C144" s="34" t="n">
+        <x:v>75285.65</x:v>
+      </x:c>
+      <x:c r="D144" s="34" t="n">
+        <x:v>71793.80000000008</x:v>
+      </x:c>
+      <x:c r="E144" s="34" t="n">
+        <x:v>74212.62000000002</x:v>
+      </x:c>
+      <x:c r="F144" s="34" t="n">
+        <x:v>2418.8199999999997</x:v>
+      </x:c>
+      <x:c r="G144" s="34" t="n">
+        <x:v>100210.16999999991</x:v>
+      </x:c>
+      <x:c r="H144" s="34" t="n">
+        <x:v>30890.780000000002</x:v>
+      </x:c>
+      <x:c r="I144" s="26" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J144" s="26" t="n">
+        <x:v>1247</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="26" t="str">
+        <x:v>2025-04</x:v>
+      </x:c>
+      <x:c r="B145" s="35" t="n">
+        <x:v>1261</x:v>
+      </x:c>
+      <x:c r="C145" s="34" t="n">
+        <x:v>56861.59</x:v>
+      </x:c>
+      <x:c r="D145" s="34" t="n">
+        <x:v>61314.94000000005</x:v>
+      </x:c>
+      <x:c r="E145" s="34" t="n">
+        <x:v>66855.51000000004</x:v>
+      </x:c>
+      <x:c r="F145" s="34" t="n">
+        <x:v>5540.5700000000015</x:v>
+      </x:c>
+      <x:c r="G145" s="34" t="n">
+        <x:v>82392.03</x:v>
+      </x:c>
+      <x:c r="H145" s="34" t="n">
+        <x:v>23890.599999999995</x:v>
+      </x:c>
+      <x:c r="I145" s="26" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J145" s="26" t="n">
+        <x:v>922</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="26" t="str">
+        <x:v>2025-05</x:v>
+      </x:c>
+      <x:c r="B146" s="35" t="n">
+        <x:v>1328</x:v>
+      </x:c>
+      <x:c r="C146" s="34" t="n">
+        <x:v>65343.65</x:v>
+      </x:c>
+      <x:c r="D146" s="34" t="n">
+        <x:v>67074.54000000011</x:v>
+      </x:c>
+      <x:c r="E146" s="34" t="n">
+        <x:v>68913.3400000001</x:v>
+      </x:c>
+      <x:c r="F146" s="34" t="n">
+        <x:v>1838.8000000000002</x:v>
+      </x:c>
+      <x:c r="G146" s="34" t="n">
+        <x:v>95579.69999999998</x:v>
+      </x:c>
+      <x:c r="H146" s="34" t="n">
+        <x:v>31153.629999999997</x:v>
+      </x:c>
+      <x:c r="I146" s="26" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J146" s="26" t="n">
+        <x:v>829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="26" t="str">
+        <x:v>2025-06</x:v>
+      </x:c>
+      <x:c r="B147" s="35" t="n">
+        <x:v>1555</x:v>
+      </x:c>
+      <x:c r="C147" s="34" t="n">
+        <x:v>70212.23</x:v>
+      </x:c>
+      <x:c r="D147" s="34" t="n">
+        <x:v>55890.67000000012</x:v>
+      </x:c>
+      <x:c r="E147" s="34" t="n">
+        <x:v>57309.340000000084</x:v>
+      </x:c>
+      <x:c r="F147" s="34" t="n">
+        <x:v>1418.6700000000008</x:v>
+      </x:c>
+      <x:c r="G147" s="34" t="n">
+        <x:v>80711.41999999991</x:v>
+      </x:c>
+      <x:c r="H147" s="34" t="n">
+        <x:v>26586.11999999999</x:v>
+      </x:c>
+      <x:c r="I147" s="26" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="J147" s="26" t="n">
+        <x:v>1091</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="26" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
+      <x:c r="B148" s="35" t="n">
+        <x:v>1534</x:v>
+      </x:c>
+      <x:c r="C148" s="34" t="n">
+        <x:v>62343.79</x:v>
+      </x:c>
+      <x:c r="D148" s="34" t="n">
+        <x:v>61675.23000000018</x:v>
+      </x:c>
+      <x:c r="E148" s="34" t="n">
+        <x:v>63316.92000000007</x:v>
+      </x:c>
+      <x:c r="F148" s="34" t="n">
+        <x:v>1641.6899999999987</x:v>
+      </x:c>
+      <x:c r="G148" s="34" t="n">
+        <x:v>78359.51999999981</x:v>
+      </x:c>
+      <x:c r="H148" s="34" t="n">
+        <x:v>18990.549999999992</x:v>
+      </x:c>
+      <x:c r="I148" s="26" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="J148" s="26" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="26" t="str">
+        <x:v>2025-08</x:v>
+      </x:c>
+      <x:c r="B149" s="35" t="n">
+        <x:v>1756</x:v>
+      </x:c>
+      <x:c r="C149" s="34" t="n">
+        <x:v>65130.4</x:v>
+      </x:c>
+      <x:c r="D149" s="34" t="n">
+        <x:v>62959.98000000004</x:v>
+      </x:c>
+      <x:c r="E149" s="34" t="n">
+        <x:v>64088.150000000045</x:v>
+      </x:c>
+      <x:c r="F149" s="34" t="n">
+        <x:v>1128.17</x:v>
+      </x:c>
+      <x:c r="G149" s="34" t="n">
+        <x:v>87986.43999999994</x:v>
+      </x:c>
+      <x:c r="H149" s="34" t="n">
+        <x:v>27595.49999999999</x:v>
+      </x:c>
+      <x:c r="I149" s="26" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J149" s="26" t="n">
+        <x:v>1098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="26" t="str">
+        <x:v>2025-09</x:v>
+      </x:c>
+      <x:c r="B150" s="35" t="n">
+        <x:v>1135</x:v>
+      </x:c>
+      <x:c r="C150" s="34" t="n">
+        <x:v>55867.52</x:v>
+      </x:c>
+      <x:c r="D150" s="34" t="n">
+        <x:v>69409.52000000005</x:v>
+      </x:c>
+      <x:c r="E150" s="34" t="n">
+        <x:v>70536.09000000004</x:v>
+      </x:c>
+      <x:c r="F150" s="34" t="n">
+        <x:v>1126.57</x:v>
+      </x:c>
+      <x:c r="G150" s="34" t="n">
+        <x:v>104107.17999999993</x:v>
+      </x:c>
+      <x:c r="H150" s="34" t="n">
+        <x:v>38085.810000000005</x:v>
+      </x:c>
+      <x:c r="I150" s="26" t="n">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="J150" s="26" t="n">
+        <x:v>683</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="26" t="str">
+        <x:v>2025-10</x:v>
+      </x:c>
+      <x:c r="B151" s="35" t="n">
+        <x:v>1451</x:v>
+      </x:c>
+      <x:c r="C151" s="34" t="n">
+        <x:v>73243.68</x:v>
+      </x:c>
+      <x:c r="D151" s="34" t="n">
+        <x:v>77405.99</x:v>
+      </x:c>
+      <x:c r="E151" s="34" t="n">
+        <x:v>78497.12000000001</x:v>
+      </x:c>
+      <x:c r="F151" s="34" t="n">
+        <x:v>1091.1299999999999</x:v>
+      </x:c>
+      <x:c r="G151" s="34" t="n">
+        <x:v>110215.05999999981</x:v>
+      </x:c>
+      <x:c r="H151" s="34" t="n">
+        <x:v>37514.35999999999</x:v>
+      </x:c>
+      <x:c r="I151" s="26" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J151" s="26" t="n">
+        <x:v>944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="26" t="str">
+        <x:v>2025-11</x:v>
+      </x:c>
+      <x:c r="B152" s="35" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="C152" s="34" t="n">
+        <x:v>93390.17</x:v>
+      </x:c>
+      <x:c r="D152" s="34" t="n">
+        <x:v>88205.51000000001</x:v>
+      </x:c>
+      <x:c r="E152" s="34" t="n">
+        <x:v>89808.17</x:v>
+      </x:c>
+      <x:c r="F152" s="34" t="n">
+        <x:v>1602.6600000000003</x:v>
+      </x:c>
+      <x:c r="G152" s="34" t="n">
+        <x:v>119581.76000000021</x:v>
+      </x:c>
+      <x:c r="H152" s="34" t="n">
+        <x:v>35829.27999999999</x:v>
+      </x:c>
+      <x:c r="I152" s="26" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J152" s="26" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="26" t="str">
+        <x:v>2025-12</x:v>
+      </x:c>
+      <x:c r="B153" s="35" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+      <x:c r="C153" s="34" t="n">
+        <x:v>74946.73</x:v>
+      </x:c>
+      <x:c r="D153" s="34" t="n">
+        <x:v>62230.81999999998</x:v>
+      </x:c>
+      <x:c r="E153" s="34" t="n">
+        <x:v>63093.38999999999</x:v>
+      </x:c>
+      <x:c r="F153" s="34" t="n">
+        <x:v>862.5699999999997</x:v>
+      </x:c>
+      <x:c r="G153" s="34" t="n">
+        <x:v>83350.15000000005</x:v>
+      </x:c>
+      <x:c r="H153" s="34" t="n">
+        <x:v>23736.889999999996</x:v>
+      </x:c>
+      <x:c r="I153" s="26" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J153" s="26" t="n">
+        <x:v>924</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="26" t="str">
+        <x:v>2026-01</x:v>
+      </x:c>
+      <x:c r="B154" s="35" t="n">
+        <x:v>1984</x:v>
+      </x:c>
+      <x:c r="C154" s="34" t="n">
+        <x:v>90714.78</x:v>
+      </x:c>
+      <x:c r="D154" s="34" t="n">
+        <x:v>100037.61000000018</x:v>
+      </x:c>
+      <x:c r="E154" s="34" t="n">
+        <x:v>102160.48000000013</x:v>
+      </x:c>
+      <x:c r="F154" s="34" t="n">
+        <x:v>2122.870000000001</x:v>
+      </x:c>
+      <x:c r="G154" s="34" t="n">
+        <x:v>149100.38</x:v>
+      </x:c>
+      <x:c r="H154" s="34" t="n">
+        <x:v>54476.700000000055</x:v>
+      </x:c>
+      <x:c r="I154" s="26" t="n">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J154" s="26" t="n">
+        <x:v>1383</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="26" t="str">
+        <x:v>2026-02</x:v>
+      </x:c>
+      <x:c r="B155" s="35" t="n">
+        <x:v>1419</x:v>
+      </x:c>
+      <x:c r="C155" s="34" t="n">
+        <x:v>73355.41</x:v>
+      </x:c>
+      <x:c r="D155" s="34" t="n">
+        <x:v>93011.81999999998</x:v>
+      </x:c>
+      <x:c r="E155" s="34" t="n">
+        <x:v>93983.34999999993</x:v>
+      </x:c>
+      <x:c r="F155" s="34" t="n">
+        <x:v>971.5299999999999</x:v>
+      </x:c>
+      <x:c r="G155" s="34" t="n">
+        <x:v>138263.76000000013</x:v>
+      </x:c>
+      <x:c r="H155" s="34" t="n">
+        <x:v>49906.04000000006</x:v>
+      </x:c>
+      <x:c r="I155" s="26" t="n">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="J155" s="26" t="n">
+        <x:v>947</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="26" t="str">
+        <x:v>2026-03</x:v>
+      </x:c>
+      <x:c r="B156" s="35" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="C156" s="34" t="n">
+        <x:v>76859.81</x:v>
+      </x:c>
+      <x:c r="D156" s="34" t="n">
+        <x:v>75628.53999999998</x:v>
+      </x:c>
+      <x:c r="E156" s="34" t="n">
+        <x:v>77206.12999999999</x:v>
+      </x:c>
+      <x:c r="F156" s="34" t="n">
+        <x:v>1577.59</x:v>
+      </x:c>
+      <x:c r="G156" s="34" t="n">
+        <x:v>102584.46000000022</x:v>
+      </x:c>
+      <x:c r="H156" s="34" t="n">
+        <x:v>30805.019999999982</x:v>
+      </x:c>
+      <x:c r="I156" s="26" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="J156" s="26" t="n">
+        <x:v>1090</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="26" t="str">
+        <x:v>2026-04</x:v>
+      </x:c>
+      <x:c r="B157" s="35" t="n">
+        <x:v>1339</x:v>
+      </x:c>
+      <x:c r="C157" s="34" t="n">
+        <x:v>68859.93</x:v>
+      </x:c>
+      <x:c r="D157" s="34" t="n">
+        <x:v>75752.30000000003</x:v>
+      </x:c>
+      <x:c r="E157" s="34" t="n">
+        <x:v>77013.54000000002</x:v>
+      </x:c>
+      <x:c r="F157" s="34" t="n">
+        <x:v>1261.2399999999998</x:v>
+      </x:c>
+      <x:c r="G157" s="34" t="n">
+        <x:v>122029.22999999988</x:v>
+      </x:c>
+      <x:c r="H157" s="34" t="n">
+        <x:v>49566.15000000005</x:v>
+      </x:c>
+      <x:c r="I157" s="26" t="n">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="J157" s="26" t="n">
+        <x:v>883</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="26" t="str">
+        <x:v>2026-05</x:v>
+      </x:c>
+      <x:c r="B158" s="35" t="n">
+        <x:v>1744</x:v>
+      </x:c>
+      <x:c r="C158" s="34" t="n">
+        <x:v>86575.36</x:v>
+      </x:c>
+      <x:c r="D158" s="34" t="n">
+        <x:v>73408.78999999998</x:v>
+      </x:c>
+      <x:c r="E158" s="34" t="n">
+        <x:v>74749.29999999999</x:v>
+      </x:c>
+      <x:c r="F158" s="34" t="n">
+        <x:v>1340.51</x:v>
+      </x:c>
+      <x:c r="G158" s="34" t="n">
+        <x:v>102583.65999999997</x:v>
+      </x:c>
+      <x:c r="H158" s="34" t="n">
+        <x:v>32273.119999999988</x:v>
+      </x:c>
+      <x:c r="I158" s="26" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="J158" s="26" t="n">
+        <x:v>1319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="26" t="str">
+        <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="B159" s="35" t="n">
+        <x:v>1530</x:v>
+      </x:c>
+      <x:c r="C159" s="34" t="n">
+        <x:v>77399.09</x:v>
+      </x:c>
+      <x:c r="D159" s="34" t="n">
+        <x:v>69134.64000000001</x:v>
+      </x:c>
+      <x:c r="E159" s="34" t="n">
+        <x:v>70398.12000000004</x:v>
+      </x:c>
+      <x:c r="F159" s="34" t="n">
+        <x:v>1263.48</x:v>
+      </x:c>
+      <x:c r="G159" s="34" t="n">
+        <x:v>103851.23999999993</x:v>
+      </x:c>
+      <x:c r="H159" s="34" t="n">
+        <x:v>37944.56000000002</x:v>
+      </x:c>
+      <x:c r="I159" s="26" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J159" s="26" t="n">
+        <x:v>1065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="26" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="B160" s="35" t="n">
+        <x:v>1983</x:v>
+      </x:c>
+      <x:c r="C160" s="34" t="n">
+        <x:v>77329.75</x:v>
+      </x:c>
+      <x:c r="D160" s="34" t="n">
+        <x:v>69874.35999999999</x:v>
+      </x:c>
+      <x:c r="E160" s="34" t="n">
+        <x:v>70944.62999999999</x:v>
+      </x:c>
+      <x:c r="F160" s="34" t="n">
+        <x:v>1070.27</x:v>
+      </x:c>
+      <x:c r="G160" s="34" t="n">
+        <x:v>106224.69999999998</x:v>
+      </x:c>
+      <x:c r="H160" s="34" t="n">
+        <x:v>39193.270000000004</x:v>
+      </x:c>
+      <x:c r="I160" s="26" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J160" s="26" t="n">
+        <x:v>1395</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="26" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="B89" s="35" t="n">
+      <x:c r="B161" s="35" t="n">
         <x:v>1515</x:v>
       </x:c>
-      <x:c r="C89" s="34" t="n">
+      <x:c r="C161" s="34" t="n">
+        <x:v>73182.63</x:v>
+      </x:c>
+      <x:c r="D161" s="34" t="n">
+        <x:v>48264.65</x:v>
+      </x:c>
+      <x:c r="E161" s="34" t="n">
+        <x:v>49903.659999999996</x:v>
+      </x:c>
+      <x:c r="F161" s="34" t="n">
+        <x:v>1639.01</x:v>
+      </x:c>
+      <x:c r="G161" s="34" t="n">
         <x:v>90997.97999999997</x:v>
       </x:c>
-      <x:c r="D89" s="34" t="n">
-        <x:v>49903.659999999996</x:v>
-      </x:c>
-      <x:c r="E89" s="34" t="n">
+      <x:c r="H161" s="34" t="n">
         <x:v>44044.72000000004</x:v>
       </x:c>
-      <x:c r="F89" s="26" t="n">
+      <x:c r="I161" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="G89" s="26" t="n">
+      <x:c r="J161" s="26" t="n">
         <x:v>963</x:v>
       </x:c>
     </x:row>
@@ -45684,57 +48362,85 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="28" t="str">
-        <x:v>Payments on orders*</x:v>
+        <x:v>PCS revenue</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>Sum of totalPayments recorded on archived order snapshots.</x:v>
+        <x:v>Total payments taken month over month.</x:v>
       </x:c>
       <x:c r="C7" s="28" t="str">
-        <x:v>API order detail</x:v>
+        <x:v>PCS Revenue By Month report</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
-        <x:v>No payment/refund transaction-date allocation yet.</x:v>
+        <x:v>Current report runs through August 27, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="28" t="str">
-        <x:v>Issue queue</x:v>
+        <x:v>Archived net payments*</x:v>
       </x:c>
       <x:c r="B8" s="28" t="str">
-        <x:v>Cancelled orders with non-zero balance are review candidates.</x:v>
+        <x:v>Payments less refunds recorded on archived order snapshots; unpaid orders contribute $0.</x:v>
       </x:c>
       <x:c r="C8" s="28" t="str">
-        <x:v>Validation output</x:v>
+        <x:v>API order detail</x:v>
       </x:c>
       <x:c r="D8" s="28" t="str">
-        <x:v>Fix in PCS, re-export, then mark verified.</x:v>
+        <x:v>Grouped by order month; diagnostic only, not PCS revenue.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="28" t="str">
-        <x:v>Sales by Product</x:v>
+        <x:v>Payments on orders*</x:v>
       </x:c>
       <x:c r="B9" s="28" t="str">
-        <x:v>PCS cash accounting allocates payment/refund activity with additional order-date rules.</x:v>
+        <x:v>Sum of totalPayments recorded on archived order snapshots.</x:v>
       </x:c>
       <x:c r="C9" s="28" t="str">
-        <x:v>PCS report definition</x:v>
+        <x:v>API order detail</x:v>
       </x:c>
       <x:c r="D9" s="28" t="str">
-        <x:v>Needs payment transaction dates and allocation model.</x:v>
+        <x:v>No payment/refund transaction-date allocation yet.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="28" t="str">
+        <x:v>Issue queue</x:v>
+      </x:c>
+      <x:c r="B10" s="28" t="str">
+        <x:v>Cancelled orders with non-zero balance are review candidates.</x:v>
+      </x:c>
+      <x:c r="C10" s="28" t="str">
+        <x:v>Validation output</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="str">
+        <x:v>Fix in PCS, re-export, then mark verified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="28" t="str">
+        <x:v>Sales by Product</x:v>
+      </x:c>
+      <x:c r="B11" s="28" t="str">
+        <x:v>PCS cash accounting allocates payment/refund activity with additional order-date rules.</x:v>
+      </x:c>
+      <x:c r="C11" s="28" t="str">
+        <x:v>PCS report definition</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="str">
+        <x:v>Needs payment transaction dates and allocation model.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="28" t="str">
         <x:v>Sales Analysis</x:v>
       </x:c>
-      <x:c r="B10" s="28" t="str">
+      <x:c r="B12" s="28" t="str">
         <x:v>Requires order data plus user and tag mappings.</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="str">
+      <x:c r="C12" s="28" t="str">
         <x:v>PCS report definition</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="str">
+      <x:c r="D12" s="28" t="str">
         <x:v>User/tag mappings still need collection.</x:v>
       </x:c>
     </x:row>

--- a/dashboard-output/PCS Archive Dashboard.xlsx
+++ b/dashboard-output/PCS Archive Dashboard.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R05a4b6ee39464a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" r:id="Rfb466ff09ffd4206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Orders" sheetId="3" r:id="R92856029ec3c4121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" r:id="R8ff697a30a5f411f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" r:id="R2f93abb85a234684"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbf736c4507e34eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="2" r:id="Rddd3051266454639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Orders" sheetId="3" r:id="R0320906ce09841e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issues" sheetId="4" r:id="R4f43bae3efe844e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="5" r:id="Rdb2b42743a3f43da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -546,7 +546,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra8f06949d1374f87"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6dcd1a4b08f4548"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -576,7 +576,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38fc9fe3494b46d9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81bc6db42d88465e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -792,7 +792,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>PCS ARCHIVE — v1.3</x:v>
+        <x:v>PCS ARCHIVE — v1.4</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -829,7 +829,7 @@
         <x:v>Archived orders</x:v>
       </x:c>
       <x:c r="B5" s="20" t="n">
-        <x:v>253216</x:v>
+        <x:v>258090</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
         <x:v>Open issues</x:v>
@@ -854,7 +854,7 @@
         <x:v>Customer snapshot</x:v>
       </x:c>
       <x:c r="B7" s="20" t="n">
-        <x:v>97209</x:v>
+        <x:v>97236</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
         <x:v>Product snapshot</x:v>
@@ -1808,7 +1808,9 @@
       <x:c r="A98" t="str">
         <x:v>2020-01</x:v>
       </x:c>
-      <x:c r="B98" s="21"/>
+      <x:c r="B98" s="21" t="n">
+        <x:v>1895</x:v>
+      </x:c>
       <x:c r="C98" s="29" t="n">
         <x:v>52243.19</x:v>
       </x:c>
@@ -1817,7 +1819,9 @@
       <x:c r="A99" t="str">
         <x:v>2020-02</x:v>
       </x:c>
-      <x:c r="B99" s="21"/>
+      <x:c r="B99" s="21" t="n">
+        <x:v>1987</x:v>
+      </x:c>
       <x:c r="C99" s="29" t="n">
         <x:v>57234.17</x:v>
       </x:c>
@@ -1826,7 +1830,9 @@
       <x:c r="A100" t="str">
         <x:v>2020-03</x:v>
       </x:c>
-      <x:c r="B100" s="21"/>
+      <x:c r="B100" s="21" t="n">
+        <x:v>989</x:v>
+      </x:c>
       <x:c r="C100" s="29" t="n">
         <x:v>19211.36</x:v>
       </x:c>
@@ -1835,7 +1841,9 @@
       <x:c r="A101" t="str">
         <x:v>2020-04</x:v>
       </x:c>
-      <x:c r="B101" s="21"/>
+      <x:c r="B101" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C101" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1853,7 +1861,9 @@
       <x:c r="A103" t="str">
         <x:v>2020-06</x:v>
       </x:c>
-      <x:c r="B103" s="21"/>
+      <x:c r="B103" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C103" s="29" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2594,7 +2604,7 @@
     <x:mergeCell ref="A179:H180"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2746d3b588bd4f0f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd4f834109af4e2a"/>
 </x:worksheet>
 </file>
 
@@ -2799,16 +2809,22 @@
         <x:v>2020</x:v>
       </x:c>
       <x:c r="B9" s="26" t="str">
-        <x:v>Not collected</x:v>
-      </x:c>
-      <x:c r="C9" s="26" t="str"/>
-      <x:c r="D9" s="26" t="str"/>
+        <x:v>Complete year</x:v>
+      </x:c>
+      <x:c r="C9" s="26" t="str">
+        <x:v>2020-01-01</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>2020-12-31</x:v>
+      </x:c>
       <x:c r="E9" s="26" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="26" t="str"/>
+        <x:v>4874</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="str">
+        <x:v>year-2020-through-2020-12-31</x:v>
+      </x:c>
       <x:c r="G9" s="26" t="str">
-        <x:v>Awaiting export</x:v>
+        <x:v>Complete calendar-year export</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5472,65 +5488,129 @@
       <x:c r="A82" s="26" t="str">
         <x:v>2020-01</x:v>
       </x:c>
-      <x:c r="B82" s="35"/>
+      <x:c r="B82" s="35" t="n">
+        <x:v>1895</x:v>
+      </x:c>
       <x:c r="C82" s="34" t="n">
         <x:v>52243.19</x:v>
       </x:c>
-      <x:c r="D82" s="34"/>
-      <x:c r="E82" s="34"/>
-      <x:c r="F82" s="34"/>
-      <x:c r="G82" s="34"/>
-      <x:c r="H82" s="34"/>
-      <x:c r="I82" s="26"/>
-      <x:c r="J82" s="26"/>
+      <x:c r="D82" s="34" t="n">
+        <x:v>54512.919999999955</x:v>
+      </x:c>
+      <x:c r="E82" s="34" t="n">
+        <x:v>57907.20999999994</x:v>
+      </x:c>
+      <x:c r="F82" s="34" t="n">
+        <x:v>3394.29</x:v>
+      </x:c>
+      <x:c r="G82" s="34" t="n">
+        <x:v>82410.57999999965</x:v>
+      </x:c>
+      <x:c r="H82" s="34" t="n">
+        <x:v>29232.66000000001</x:v>
+      </x:c>
+      <x:c r="I82" s="26" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J82" s="26" t="n">
+        <x:v>1246</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="26" t="str">
         <x:v>2020-02</x:v>
       </x:c>
-      <x:c r="B83" s="35"/>
+      <x:c r="B83" s="35" t="n">
+        <x:v>1987</x:v>
+      </x:c>
       <x:c r="C83" s="34" t="n">
         <x:v>57234.17</x:v>
       </x:c>
-      <x:c r="D83" s="34"/>
-      <x:c r="E83" s="34"/>
-      <x:c r="F83" s="34"/>
-      <x:c r="G83" s="34"/>
-      <x:c r="H83" s="34"/>
-      <x:c r="I83" s="26"/>
-      <x:c r="J83" s="26"/>
+      <x:c r="D83" s="34" t="n">
+        <x:v>47800.63999999992</x:v>
+      </x:c>
+      <x:c r="E83" s="34" t="n">
+        <x:v>52384.200000000004</x:v>
+      </x:c>
+      <x:c r="F83" s="34" t="n">
+        <x:v>4583.559999999996</x:v>
+      </x:c>
+      <x:c r="G83" s="34" t="n">
+        <x:v>71354.56999999976</x:v>
+      </x:c>
+      <x:c r="H83" s="34" t="n">
+        <x:v>24538.930000000004</x:v>
+      </x:c>
+      <x:c r="I83" s="26" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J83" s="26" t="n">
+        <x:v>1287</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="26" t="str">
         <x:v>2020-03</x:v>
       </x:c>
-      <x:c r="B84" s="35"/>
+      <x:c r="B84" s="35" t="n">
+        <x:v>989</x:v>
+      </x:c>
       <x:c r="C84" s="34" t="n">
         <x:v>19211.36</x:v>
       </x:c>
-      <x:c r="D84" s="34"/>
-      <x:c r="E84" s="34"/>
-      <x:c r="F84" s="34"/>
-      <x:c r="G84" s="34"/>
-      <x:c r="H84" s="34"/>
-      <x:c r="I84" s="26"/>
-      <x:c r="J84" s="26"/>
+      <x:c r="D84" s="34" t="n">
+        <x:v>18053.300000000025</x:v>
+      </x:c>
+      <x:c r="E84" s="34" t="n">
+        <x:v>19438.930000000015</x:v>
+      </x:c>
+      <x:c r="F84" s="34" t="n">
+        <x:v>1385.63</x:v>
+      </x:c>
+      <x:c r="G84" s="34" t="n">
+        <x:v>24788.81</x:v>
+      </x:c>
+      <x:c r="H84" s="34" t="n">
+        <x:v>6875.510000000002</x:v>
+      </x:c>
+      <x:c r="I84" s="26" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J84" s="26" t="n">
+        <x:v>674</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="26" t="str">
         <x:v>2020-04</x:v>
       </x:c>
-      <x:c r="B85" s="35"/>
+      <x:c r="B85" s="35" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="C85" s="34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D85" s="34"/>
-      <x:c r="E85" s="34"/>
-      <x:c r="F85" s="34"/>
-      <x:c r="G85" s="34"/>
-      <x:c r="H85" s="34"/>
-      <x:c r="I85" s="26"/>
-      <x:c r="J85" s="26"/>
+      <x:c r="D85" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E85" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F85" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G85" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H85" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I85" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J85" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="26" t="str">
@@ -5552,17 +5632,33 @@
       <x:c r="A87" s="26" t="str">
         <x:v>2020-06</x:v>
       </x:c>
-      <x:c r="B87" s="35"/>
+      <x:c r="B87" s="35" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="C87" s="34" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D87" s="34"/>
-      <x:c r="E87" s="34"/>
-      <x:c r="F87" s="34"/>
-      <x:c r="G87" s="34"/>
-      <x:c r="H87" s="34"/>
-      <x:c r="I87" s="26"/>
-      <x:c r="J87" s="26"/>
+      <x:c r="D87" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E87" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F87" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G87" s="34" t="n">
+        <x:v>480.88</x:v>
+      </x:c>
+      <x:c r="H87" s="34" t="n">
+        <x:v>480.88</x:v>
+      </x:c>
+      <x:c r="I87" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J87" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="26" t="str">
